--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -26,13 +26,13 @@
     <t>PreDraft$</t>
   </si>
   <si>
-    <t>VALUE</t>
-  </si>
-  <si>
     <t>Final Price</t>
   </si>
   <si>
     <t>Mine?</t>
+  </si>
+  <si>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -149,10 +149,10 @@
     <t>Arvell Reese</t>
   </si>
   <si>
-    <t>Inflation Factor</t>
+    <t>Round 2</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Inflation Factor</t>
   </si>
   <si>
     <t>Ty Simpson</t>
@@ -167,6 +167,9 @@
     <t>Round 3</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
@@ -176,10 +179,10 @@
     <t>League Spent %</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Jacob Rodriguez</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
@@ -197,10 +200,10 @@
     <t>Chris Bell</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Germie Bernard</t>
   </si>
   <si>
-    <t>Germie Bernard</t>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -219,9 +222,6 @@
   </si>
   <si>
     <t>Emmett Johnson</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Chris Brazzell</t>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y148" s="6" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="6" t="s">
         <v>146</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y155" s="6" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y156" s="6" t="s">
         <v>145</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="6" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="6" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="6" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="6" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y168" s="6" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="6" t="s">
         <v>141</v>
@@ -37453,10 +37453,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="8">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="8">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -47,13 +47,13 @@
     <t>EnforceUpTo</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>Value vs Fair</t>
   </si>
   <si>
     <t>Settings</t>
-  </si>
-  <si>
-    <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
@@ -110,9 +110,6 @@
     <t>My Spent</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Sonny Styles</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t>Other Teams Remaining</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>Jadarian Price</t>
@@ -149,9 +149,6 @@
     <t>Arvell Reese</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Inflation Factor</t>
   </si>
   <si>
@@ -164,13 +161,10 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
-    <t>Caleb Downs</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -180,9 +174,6 @@
   </si>
   <si>
     <t>Jacob Rodriguez</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
@@ -203,13 +194,13 @@
     <t>Germie Bernard</t>
   </si>
   <si>
-    <t>Round 6</t>
-  </si>
-  <si>
     <t>Nicholas Singleton</t>
   </si>
   <si>
     <t>Mike Washington</t>
+  </si>
+  <si>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -236,6 +227,9 @@
     <t>De'Zhaun Stribling</t>
   </si>
   <si>
+    <t>Round 4</t>
+  </si>
+  <si>
     <t>Malachi Fields</t>
   </si>
   <si>
@@ -260,6 +254,9 @@
     <t>Josiah Trotter</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Dani Dennis-Sutton</t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>Demond Claiborne</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Malachi Lawrence</t>
@@ -627,10 +627,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -923,15 +923,15 @@
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="6">
         <v>2025.0</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="6">
         <v>2024.0</v>
       </c>
       <c r="H1" s="9">
@@ -949,52 +949,52 @@
       <c r="L1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="7">
+      <c r="M1" s="6">
         <v>12.0</v>
       </c>
       <c r="N1" s="12"/>
       <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="7">
+      <c r="P1" s="6">
         <v>1.0</v>
       </c>
-      <c r="Q1" s="7">
+      <c r="Q1" s="6">
         <v>2.0</v>
       </c>
-      <c r="R1" s="7">
+      <c r="R1" s="6">
         <v>3.0</v>
       </c>
-      <c r="S1" s="7">
+      <c r="S1" s="6">
         <v>4.0</v>
       </c>
-      <c r="T1" s="7">
+      <c r="T1" s="6">
         <v>5.0</v>
       </c>
-      <c r="U1" s="7">
+      <c r="U1" s="6">
         <v>6.0</v>
       </c>
-      <c r="V1" s="7">
+      <c r="V1" s="6">
         <v>7.0</v>
       </c>
-      <c r="W1" s="7">
+      <c r="W1" s="6">
         <v>8.0</v>
       </c>
-      <c r="X1" s="7">
+      <c r="X1" s="6">
         <v>9.0</v>
       </c>
-      <c r="Y1" s="7">
+      <c r="Y1" s="6">
         <v>10.0</v>
       </c>
-      <c r="Z1" s="7">
+      <c r="Z1" s="6">
         <v>11.0</v>
       </c>
-      <c r="AA1" s="7">
+      <c r="AA1" s="6">
         <v>12.0</v>
       </c>
       <c r="AB1" s="10"/>
       <c r="AC1" s="10"/>
-      <c r="AD1" s="7">
+      <c r="AD1" s="6">
         <f>1200 / SUM($P$2:$AA$7)</f>
         <v>1</v>
       </c>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <v>1.0</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="Q30" s="12"/>
-      <c r="R30" s="7">
+      <c r="R30" s="6">
         <v>12.0</v>
       </c>
       <c r="S30" s="12"/>
@@ -3160,7 +3160,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
-      <c r="X30" s="6"/>
+      <c r="X30" s="7"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
         <v>0|</v>
@@ -3217,14 +3217,14 @@
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <v>2.0</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>123</v>
       </c>
       <c r="Q31" s="12"/>
-      <c r="R31" s="7">
+      <c r="R31" s="6">
         <v>11.0</v>
       </c>
       <c r="S31" s="12"/>
@@ -3234,8 +3234,8 @@
       </c>
       <c r="U31" s="12"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
       <c r="Y31" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3292,14 +3292,14 @@
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <v>3.0</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>124</v>
       </c>
       <c r="Q32" s="12"/>
-      <c r="R32" s="7">
+      <c r="R32" s="6">
         <v>10.0</v>
       </c>
       <c r="S32" s="12"/>
@@ -3309,8 +3309,8 @@
       </c>
       <c r="U32" s="12"/>
       <c r="V32" s="9"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3367,14 +3367,14 @@
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
-      <c r="O33" s="7">
+      <c r="O33" s="6">
         <v>4.0</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>125</v>
       </c>
       <c r="Q33" s="12"/>
-      <c r="R33" s="7">
+      <c r="R33" s="6">
         <v>9.0</v>
       </c>
       <c r="S33" s="12"/>
@@ -3384,8 +3384,8 @@
       </c>
       <c r="U33" s="12"/>
       <c r="V33" s="9"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <v>5.0</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>126</v>
       </c>
       <c r="Q34" s="12"/>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <v>8.0</v>
       </c>
       <c r="S34" s="12"/>
@@ -3459,8 +3459,8 @@
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
       <c r="Y34" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3517,14 +3517,14 @@
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>6.0</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>127</v>
       </c>
       <c r="Q35" s="12"/>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>7.0</v>
       </c>
       <c r="S35" s="12"/>
@@ -3534,8 +3534,8 @@
       </c>
       <c r="U35" s="12"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
       <c r="Y35" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3592,14 +3592,14 @@
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <v>7.0</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>128</v>
       </c>
       <c r="Q36" s="12"/>
-      <c r="R36" s="7">
+      <c r="R36" s="6">
         <v>6.0</v>
       </c>
       <c r="S36" s="12"/>
@@ -3609,8 +3609,8 @@
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
       <c r="Y36" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <v>8.0</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>129</v>
       </c>
       <c r="Q37" s="12"/>
-      <c r="R37" s="7">
+      <c r="R37" s="6">
         <v>5.0</v>
       </c>
       <c r="S37" s="12"/>
@@ -3684,8 +3684,8 @@
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
       <c r="Y37" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
-      <c r="O38" s="7">
+      <c r="O38" s="6">
         <v>9.0</v>
       </c>
       <c r="P38" s="10" t="s">
         <v>130</v>
       </c>
       <c r="Q38" s="12"/>
-      <c r="R38" s="7">
+      <c r="R38" s="6">
         <v>4.0</v>
       </c>
       <c r="S38" s="12"/>
@@ -3759,8 +3759,8 @@
       </c>
       <c r="U38" s="12"/>
       <c r="V38" s="9"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
       <c r="Y38" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3817,14 +3817,14 @@
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <v>10.0</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>131</v>
       </c>
       <c r="Q39" s="12"/>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <v>3.0</v>
       </c>
       <c r="S39" s="12"/>
@@ -3834,8 +3834,8 @@
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="9"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
       <c r="Y39" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3892,14 +3892,14 @@
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <v>11.0</v>
       </c>
       <c r="P40" s="10" t="s">
         <v>132</v>
       </c>
       <c r="Q40" s="12"/>
-      <c r="R40" s="7">
+      <c r="R40" s="6">
         <v>2.0</v>
       </c>
       <c r="S40" s="12"/>
@@ -3909,8 +3909,8 @@
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="9"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
       <c r="Y40" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3967,14 +3967,14 @@
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <v>12.0</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Q41" s="12"/>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <v>1.0</v>
       </c>
       <c r="S41" s="12"/>
@@ -3984,8 +3984,8 @@
       </c>
       <c r="U41" s="12"/>
       <c r="V41" s="9"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
       <c r="Y41" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4050,8 +4050,8 @@
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
       <c r="V42" s="9"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
       <c r="Y42" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4116,8 +4116,8 @@
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
       <c r="Y43" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4190,8 +4190,8 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="6"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
       <c r="Y44" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4280,8 +4280,8 @@
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
       <c r="Y45" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4358,8 +4358,8 @@
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
       <c r="Y46" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4436,8 +4436,8 @@
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
       <c r="Y47" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4514,8 +4514,8 @@
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
       <c r="Y48" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4592,8 +4592,8 @@
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
       <c r="Y49" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4670,8 +4670,8 @@
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7"/>
       <c r="Y50" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4748,8 +4748,8 @@
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
       <c r="Y51" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4826,8 +4826,8 @@
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7"/>
       <c r="Y52" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4904,8 +4904,8 @@
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
       <c r="V53" s="9"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
       <c r="Y53" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4982,8 +4982,8 @@
       <c r="T54" s="12"/>
       <c r="U54" s="12"/>
       <c r="V54" s="9"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
       <c r="Y54" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5060,8 +5060,8 @@
       <c r="T55" s="12"/>
       <c r="U55" s="12"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
       <c r="Y55" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5138,8 +5138,8 @@
       <c r="T56" s="12"/>
       <c r="U56" s="12"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
+      <c r="W56" s="7"/>
+      <c r="X56" s="7"/>
       <c r="Y56" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5216,8 +5216,8 @@
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="6"/>
-      <c r="X57" s="6"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
       <c r="Y57" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5295,7 +5295,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="23"/>
       <c r="W58" s="23"/>
-      <c r="X58" s="6"/>
+      <c r="X58" s="7"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5373,7 +5373,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="23"/>
       <c r="W59" s="23"/>
-      <c r="X59" s="6"/>
+      <c r="X59" s="7"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5451,7 +5451,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="23"/>
       <c r="W60" s="23"/>
-      <c r="X60" s="6"/>
+      <c r="X60" s="7"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5528,8 +5528,8 @@
       <c r="T61" s="12"/>
       <c r="U61" s="12"/>
       <c r="V61" s="9"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="6"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
       <c r="Y61" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5609,9 +5609,9 @@
       <c r="U62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="6"/>
+      <c r="V62" s="7"/>
+      <c r="W62" s="7"/>
+      <c r="X62" s="7"/>
       <c r="Y62" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5692,9 +5692,9 @@
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>180</v>
       </c>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
       <c r="Y63" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="V64" s="23"/>
       <c r="W64" s="23"/>
-      <c r="X64" s="6"/>
+      <c r="X64" s="7"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5858,9 +5858,9 @@
         <f t="shared" si="22"/>
         <v>132.5</v>
       </c>
-      <c r="V65" s="6"/>
-      <c r="W65" s="6"/>
-      <c r="X65" s="6"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
       <c r="Y65" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5942,8 +5942,8 @@
         <v>117.5</v>
       </c>
       <c r="V66" s="9"/>
-      <c r="W66" s="6"/>
-      <c r="X66" s="6"/>
+      <c r="W66" s="7"/>
+      <c r="X66" s="7"/>
       <c r="Y66" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6025,8 +6025,8 @@
         <v>109.5</v>
       </c>
       <c r="V67" s="9"/>
-      <c r="W67" s="6"/>
-      <c r="X67" s="6"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
       <c r="Y67" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6108,8 +6108,8 @@
         <v>99.5</v>
       </c>
       <c r="V68" s="9"/>
-      <c r="W68" s="6"/>
-      <c r="X68" s="6"/>
+      <c r="W68" s="7"/>
+      <c r="X68" s="7"/>
       <c r="Y68" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="V69" s="23"/>
       <c r="W69" s="23"/>
-      <c r="X69" s="6"/>
+      <c r="X69" s="7"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5"/>
-      <c r="B75" s="6"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5"/>
-      <c r="B77" s="6"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5"/>
-      <c r="B80" s="6"/>
+      <c r="B80" s="7"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5"/>
-      <c r="B81" s="6"/>
+      <c r="B81" s="7"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5"/>
-      <c r="B82" s="6"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="83">
       <c r="A83" s="12"/>
-      <c r="B83" s="6"/>
+      <c r="B83" s="7"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="84">
       <c r="A84" s="12"/>
-      <c r="B84" s="6"/>
+      <c r="B84" s="7"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="86">
       <c r="A86" s="12"/>
-      <c r="B86" s="6"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="12"/>
-      <c r="B87" s="6"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="88">
       <c r="A88" s="12"/>
-      <c r="B88" s="6"/>
+      <c r="B88" s="7"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="89">
       <c r="A89" s="12"/>
-      <c r="B89" s="6"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5"/>
-      <c r="B90" s="6"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5"/>
-      <c r="B91" s="6"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5"/>
-      <c r="B92" s="6"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="12"/>
-      <c r="B94" s="6"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="95">
       <c r="A95" s="12"/>
-      <c r="B95" s="6"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="96">
       <c r="A96" s="12"/>
-      <c r="B96" s="6"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="97">
       <c r="A97" s="12"/>
-      <c r="B97" s="6"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="12"/>
-      <c r="B98" s="6"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="99">
       <c r="A99" s="12"/>
-      <c r="B99" s="6"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="100">
       <c r="A100" s="12"/>
-      <c r="B100" s="6"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5"/>
-      <c r="B101" s="6"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5"/>
-      <c r="B102" s="6"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
@@ -9146,7 +9146,7 @@
       <c r="W137" s="12"/>
       <c r="X137" s="12"/>
       <c r="Y137" s="12"/>
-      <c r="Z137" s="6" t="s">
+      <c r="Z137" s="7" t="s">
         <v>137</v>
       </c>
       <c r="AA137" s="12"/>
@@ -9180,7 +9180,7 @@
       <c r="W138" s="12"/>
       <c r="X138" s="12"/>
       <c r="Y138" s="12"/>
-      <c r="Z138" s="6">
+      <c r="Z138" s="7">
         <v>6817.0</v>
       </c>
       <c r="AA138" s="12"/>
@@ -9211,16 +9211,16 @@
       <c r="T139" s="12"/>
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
-      <c r="W139" s="6" t="s">
+      <c r="W139" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="X139" s="6" t="s">
+      <c r="X139" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="Y139" s="6" t="s">
+      <c r="Y139" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="Z139" s="6">
+      <c r="Z139" s="7">
         <v>5203.0</v>
       </c>
       <c r="AA139" s="12"/>
@@ -9251,16 +9251,16 @@
       <c r="T140" s="12"/>
       <c r="U140" s="12"/>
       <c r="V140" s="12"/>
-      <c r="W140" s="6">
+      <c r="W140" s="7">
         <v>1.0</v>
       </c>
-      <c r="X140" s="6" t="s">
+      <c r="X140" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Y140" s="6" t="s">
+      <c r="Y140" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z140" s="6">
+      <c r="Z140" s="7">
         <v>5103.0</v>
       </c>
       <c r="AA140" s="12"/>
@@ -9291,16 +9291,16 @@
       <c r="T141" s="12"/>
       <c r="U141" s="12"/>
       <c r="V141" s="12"/>
-      <c r="W141" s="6">
+      <c r="W141" s="7">
         <v>3.0</v>
       </c>
-      <c r="X141" s="6" t="s">
+      <c r="X141" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Y141" s="6" t="s">
+      <c r="Y141" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z141" s="6">
+      <c r="Z141" s="7">
         <v>5020.0</v>
       </c>
       <c r="AA141" s="12"/>
@@ -9331,16 +9331,16 @@
       <c r="T142" s="12"/>
       <c r="U142" s="12"/>
       <c r="V142" s="12"/>
-      <c r="W142" s="6">
+      <c r="W142" s="7">
         <v>4.0</v>
       </c>
-      <c r="X142" s="6" t="s">
+      <c r="X142" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Y142" s="6" t="s">
+      <c r="Y142" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z142" s="6">
+      <c r="Z142" s="7">
         <v>4517.0</v>
       </c>
       <c r="AA142" s="12"/>
@@ -9371,16 +9371,16 @@
       <c r="T143" s="12"/>
       <c r="U143" s="12"/>
       <c r="V143" s="12"/>
-      <c r="W143" s="6">
+      <c r="W143" s="7">
         <v>5.0</v>
       </c>
-      <c r="X143" s="6" t="s">
+      <c r="X143" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Y143" s="6" t="s">
+      <c r="Y143" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z143" s="6">
+      <c r="Z143" s="7">
         <v>4164.0</v>
       </c>
       <c r="AA143" s="12"/>
@@ -9411,16 +9411,16 @@
       <c r="T144" s="12"/>
       <c r="U144" s="12"/>
       <c r="V144" s="12"/>
-      <c r="W144" s="6">
+      <c r="W144" s="7">
         <v>6.0</v>
       </c>
-      <c r="X144" s="6" t="s">
+      <c r="X144" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Y144" s="6" t="s">
+      <c r="Y144" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z144" s="6">
+      <c r="Z144" s="7">
         <v>4025.0</v>
       </c>
       <c r="AA144" s="12"/>
@@ -9451,16 +9451,16 @@
       <c r="T145" s="12"/>
       <c r="U145" s="12"/>
       <c r="V145" s="12"/>
-      <c r="W145" s="6">
+      <c r="W145" s="7">
         <v>7.0</v>
       </c>
-      <c r="X145" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y145" s="6" t="s">
+      <c r="X145" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y145" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z145" s="6">
+      <c r="Z145" s="7">
         <v>3650.0</v>
       </c>
       <c r="AA145" s="12"/>
@@ -9491,16 +9491,16 @@
       <c r="T146" s="12"/>
       <c r="U146" s="12"/>
       <c r="V146" s="12"/>
-      <c r="W146" s="6">
+      <c r="W146" s="7">
         <v>8.0</v>
       </c>
-      <c r="X146" s="6" t="s">
+      <c r="X146" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Y146" s="6" t="s">
+      <c r="Y146" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z146" s="6">
+      <c r="Z146" s="7">
         <v>3611.0</v>
       </c>
       <c r="AA146" s="12"/>
@@ -9531,16 +9531,16 @@
       <c r="T147" s="12"/>
       <c r="U147" s="12"/>
       <c r="V147" s="12"/>
-      <c r="W147" s="6">
+      <c r="W147" s="7">
         <v>9.0</v>
       </c>
-      <c r="X147" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y147" s="6" t="s">
+      <c r="X147" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y147" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z147" s="6">
+      <c r="Z147" s="7">
         <v>3608.0</v>
       </c>
       <c r="AA147" s="12"/>
@@ -9571,16 +9571,16 @@
       <c r="T148" s="12"/>
       <c r="U148" s="12"/>
       <c r="V148" s="12"/>
-      <c r="W148" s="6">
+      <c r="W148" s="7">
         <v>10.0</v>
       </c>
-      <c r="X148" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y148" s="6" t="s">
+      <c r="X148" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y148" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z148" s="6">
+      <c r="Z148" s="7">
         <v>3596.0</v>
       </c>
       <c r="AA148" s="12"/>
@@ -9611,16 +9611,16 @@
       <c r="T149" s="12"/>
       <c r="U149" s="12"/>
       <c r="V149" s="12"/>
-      <c r="W149" s="6">
+      <c r="W149" s="7">
         <v>11.0</v>
       </c>
-      <c r="X149" s="6" t="s">
+      <c r="X149" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Y149" s="6" t="s">
+      <c r="Y149" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z149" s="6">
+      <c r="Z149" s="7">
         <v>3426.0</v>
       </c>
       <c r="AA149" s="12"/>
@@ -9651,16 +9651,16 @@
       <c r="T150" s="12"/>
       <c r="U150" s="12"/>
       <c r="V150" s="12"/>
-      <c r="W150" s="6">
+      <c r="W150" s="7">
         <v>12.0</v>
       </c>
-      <c r="X150" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y150" s="6" t="s">
+      <c r="X150" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y150" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z150" s="6">
+      <c r="Z150" s="7">
         <v>3264.0</v>
       </c>
       <c r="AA150" s="12"/>
@@ -9691,16 +9691,16 @@
       <c r="T151" s="12"/>
       <c r="U151" s="12"/>
       <c r="V151" s="12"/>
-      <c r="W151" s="6">
+      <c r="W151" s="7">
         <v>13.0</v>
       </c>
-      <c r="X151" s="6" t="s">
+      <c r="X151" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Y151" s="6" t="s">
+      <c r="Y151" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z151" s="6">
+      <c r="Z151" s="7">
         <v>3179.0</v>
       </c>
       <c r="AA151" s="12"/>
@@ -9731,16 +9731,16 @@
       <c r="T152" s="12"/>
       <c r="U152" s="12"/>
       <c r="V152" s="12"/>
-      <c r="W152" s="6">
+      <c r="W152" s="7">
         <v>14.0</v>
       </c>
-      <c r="X152" s="6" t="s">
+      <c r="X152" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="Y152" s="6" t="s">
+      <c r="Y152" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z152" s="6">
+      <c r="Z152" s="7">
         <v>3162.0</v>
       </c>
       <c r="AA152" s="12"/>
@@ -9771,16 +9771,16 @@
       <c r="T153" s="12"/>
       <c r="U153" s="12"/>
       <c r="V153" s="12"/>
-      <c r="W153" s="6">
+      <c r="W153" s="7">
         <v>15.0</v>
       </c>
-      <c r="X153" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y153" s="6" t="s">
+      <c r="X153" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y153" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z153" s="6">
+      <c r="Z153" s="7">
         <v>3125.0</v>
       </c>
       <c r="AA153" s="12"/>
@@ -9811,16 +9811,16 @@
       <c r="T154" s="12"/>
       <c r="U154" s="12"/>
       <c r="V154" s="12"/>
-      <c r="W154" s="6">
+      <c r="W154" s="7">
         <v>16.0</v>
       </c>
-      <c r="X154" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y154" s="6" t="s">
+      <c r="X154" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y154" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z154" s="6">
+      <c r="Z154" s="7">
         <v>2971.0</v>
       </c>
       <c r="AA154" s="12"/>
@@ -9851,16 +9851,16 @@
       <c r="T155" s="12"/>
       <c r="U155" s="12"/>
       <c r="V155" s="12"/>
-      <c r="W155" s="6">
+      <c r="W155" s="7">
         <v>17.0</v>
       </c>
-      <c r="X155" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y155" s="6" t="s">
+      <c r="X155" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y155" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z155" s="6">
+      <c r="Z155" s="7">
         <v>2963.0</v>
       </c>
       <c r="AA155" s="12"/>
@@ -9891,16 +9891,16 @@
       <c r="T156" s="12"/>
       <c r="U156" s="12"/>
       <c r="V156" s="12"/>
-      <c r="W156" s="6">
+      <c r="W156" s="7">
         <v>18.0</v>
       </c>
-      <c r="X156" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y156" s="6" t="s">
+      <c r="X156" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y156" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z156" s="6">
+      <c r="Z156" s="7">
         <v>2953.0</v>
       </c>
       <c r="AA156" s="12"/>
@@ -9931,16 +9931,16 @@
       <c r="T157" s="12"/>
       <c r="U157" s="12"/>
       <c r="V157" s="12"/>
-      <c r="W157" s="6">
+      <c r="W157" s="7">
         <v>19.0</v>
       </c>
-      <c r="X157" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y157" s="6" t="s">
+      <c r="X157" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y157" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="Z157" s="6">
+      <c r="Z157" s="7">
         <v>2807.0</v>
       </c>
       <c r="AA157" s="12"/>
@@ -9971,16 +9971,16 @@
       <c r="T158" s="12"/>
       <c r="U158" s="12"/>
       <c r="V158" s="12"/>
-      <c r="W158" s="6">
+      <c r="W158" s="7">
         <v>20.0</v>
       </c>
-      <c r="X158" s="6" t="s">
+      <c r="X158" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Y158" s="6" t="s">
+      <c r="Y158" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z158" s="6">
+      <c r="Z158" s="7">
         <v>2696.0</v>
       </c>
       <c r="AA158" s="12"/>
@@ -10011,16 +10011,16 @@
       <c r="T159" s="12"/>
       <c r="U159" s="12"/>
       <c r="V159" s="12"/>
-      <c r="W159" s="6">
+      <c r="W159" s="7">
         <v>21.0</v>
       </c>
-      <c r="X159" s="6" t="s">
+      <c r="X159" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="Y159" s="6" t="s">
+      <c r="Y159" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z159" s="6">
+      <c r="Z159" s="7">
         <v>2672.0</v>
       </c>
       <c r="AA159" s="12"/>
@@ -10051,16 +10051,16 @@
       <c r="T160" s="12"/>
       <c r="U160" s="12"/>
       <c r="V160" s="12"/>
-      <c r="W160" s="6">
+      <c r="W160" s="7">
         <v>22.0</v>
       </c>
-      <c r="X160" s="6" t="s">
+      <c r="X160" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Y160" s="6" t="s">
+      <c r="Y160" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z160" s="6">
+      <c r="Z160" s="7">
         <v>2480.0</v>
       </c>
       <c r="AA160" s="12"/>
@@ -10091,16 +10091,16 @@
       <c r="T161" s="12"/>
       <c r="U161" s="12"/>
       <c r="V161" s="12"/>
-      <c r="W161" s="6">
+      <c r="W161" s="7">
         <v>23.0</v>
       </c>
-      <c r="X161" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y161" s="6" t="s">
+      <c r="X161" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y161" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z161" s="6">
+      <c r="Z161" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA161" s="12"/>
@@ -10131,16 +10131,16 @@
       <c r="T162" s="12"/>
       <c r="U162" s="12"/>
       <c r="V162" s="12"/>
-      <c r="W162" s="6">
+      <c r="W162" s="7">
         <v>24.0</v>
       </c>
-      <c r="X162" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y162" s="6" t="s">
+      <c r="X162" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y162" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z162" s="6">
+      <c r="Z162" s="7">
         <v>2416.0</v>
       </c>
       <c r="AA162" s="12"/>
@@ -10171,16 +10171,16 @@
       <c r="T163" s="12"/>
       <c r="U163" s="12"/>
       <c r="V163" s="12"/>
-      <c r="W163" s="6">
+      <c r="W163" s="7">
         <v>25.0</v>
       </c>
-      <c r="X163" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y163" s="6" t="s">
+      <c r="X163" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y163" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z163" s="6">
+      <c r="Z163" s="7">
         <v>2109.0</v>
       </c>
       <c r="AA163" s="12"/>
@@ -10211,16 +10211,16 @@
       <c r="T164" s="12"/>
       <c r="U164" s="12"/>
       <c r="V164" s="12"/>
-      <c r="W164" s="6">
+      <c r="W164" s="7">
         <v>26.0</v>
       </c>
-      <c r="X164" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y164" s="6" t="s">
+      <c r="X164" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y164" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z164" s="6">
+      <c r="Z164" s="7">
         <v>2106.0</v>
       </c>
       <c r="AA164" s="12"/>
@@ -10251,16 +10251,16 @@
       <c r="T165" s="12"/>
       <c r="U165" s="12"/>
       <c r="V165" s="12"/>
-      <c r="W165" s="6">
+      <c r="W165" s="7">
         <v>27.0</v>
       </c>
-      <c r="X165" s="6" t="s">
+      <c r="X165" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="Y165" s="6" t="s">
+      <c r="Y165" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z165" s="6">
+      <c r="Z165" s="7">
         <v>2098.0</v>
       </c>
       <c r="AA165" s="12"/>
@@ -10291,16 +10291,16 @@
       <c r="T166" s="12"/>
       <c r="U166" s="12"/>
       <c r="V166" s="12"/>
-      <c r="W166" s="6">
+      <c r="W166" s="7">
         <v>28.0</v>
       </c>
-      <c r="X166" s="6" t="s">
+      <c r="X166" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="Y166" s="6" t="s">
+      <c r="Y166" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z166" s="6">
+      <c r="Z166" s="7">
         <v>2078.0</v>
       </c>
       <c r="AA166" s="12"/>
@@ -10331,16 +10331,16 @@
       <c r="T167" s="12"/>
       <c r="U167" s="12"/>
       <c r="V167" s="12"/>
-      <c r="W167" s="6">
+      <c r="W167" s="7">
         <v>29.0</v>
       </c>
-      <c r="X167" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y167" s="6" t="s">
+      <c r="X167" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y167" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z167" s="6">
+      <c r="Z167" s="7">
         <v>2074.0</v>
       </c>
       <c r="AA167" s="12"/>
@@ -10371,16 +10371,16 @@
       <c r="T168" s="12"/>
       <c r="U168" s="12"/>
       <c r="V168" s="12"/>
-      <c r="W168" s="6">
+      <c r="W168" s="7">
         <v>30.0</v>
       </c>
-      <c r="X168" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y168" s="6" t="s">
+      <c r="X168" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y168" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z168" s="6">
+      <c r="Z168" s="7">
         <v>2066.0</v>
       </c>
       <c r="AA168" s="12"/>
@@ -10411,16 +10411,16 @@
       <c r="T169" s="12"/>
       <c r="U169" s="12"/>
       <c r="V169" s="12"/>
-      <c r="W169" s="6">
+      <c r="W169" s="7">
         <v>31.0</v>
       </c>
-      <c r="X169" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y169" s="6" t="s">
+      <c r="X169" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y169" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z169" s="6">
+      <c r="Z169" s="7">
         <v>2045.0</v>
       </c>
       <c r="AA169" s="12"/>
@@ -10451,16 +10451,16 @@
       <c r="T170" s="12"/>
       <c r="U170" s="12"/>
       <c r="V170" s="12"/>
-      <c r="W170" s="6">
+      <c r="W170" s="7">
         <v>32.0</v>
       </c>
-      <c r="X170" s="6" t="s">
+      <c r="X170" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="Y170" s="6" t="s">
+      <c r="Y170" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z170" s="6">
+      <c r="Z170" s="7">
         <v>1977.0</v>
       </c>
       <c r="AA170" s="12"/>
@@ -10491,16 +10491,16 @@
       <c r="T171" s="12"/>
       <c r="U171" s="12"/>
       <c r="V171" s="12"/>
-      <c r="W171" s="6">
+      <c r="W171" s="7">
         <v>33.0</v>
       </c>
-      <c r="X171" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y171" s="6" t="s">
+      <c r="X171" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y171" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z171" s="6">
+      <c r="Z171" s="7">
         <v>1967.0</v>
       </c>
       <c r="AA171" s="12"/>
@@ -10531,16 +10531,16 @@
       <c r="T172" s="12"/>
       <c r="U172" s="12"/>
       <c r="V172" s="12"/>
-      <c r="W172" s="6">
+      <c r="W172" s="7">
         <v>34.0</v>
       </c>
-      <c r="X172" s="6" t="s">
+      <c r="X172" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="Y172" s="6" t="s">
+      <c r="Y172" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="Z172" s="6">
+      <c r="Z172" s="7">
         <v>1962.0</v>
       </c>
       <c r="AA172" s="12"/>
@@ -10571,16 +10571,16 @@
       <c r="T173" s="12"/>
       <c r="U173" s="12"/>
       <c r="V173" s="12"/>
-      <c r="W173" s="6">
+      <c r="W173" s="7">
         <v>35.0</v>
       </c>
-      <c r="X173" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y173" s="6" t="s">
+      <c r="X173" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y173" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z173" s="6">
+      <c r="Z173" s="7">
         <v>1961.0</v>
       </c>
       <c r="AA173" s="12"/>
@@ -10611,16 +10611,16 @@
       <c r="T174" s="12"/>
       <c r="U174" s="12"/>
       <c r="V174" s="12"/>
-      <c r="W174" s="6">
+      <c r="W174" s="7">
         <v>36.0</v>
       </c>
-      <c r="X174" s="6" t="s">
+      <c r="X174" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Y174" s="6" t="s">
+      <c r="Y174" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z174" s="6">
+      <c r="Z174" s="7">
         <v>1910.0</v>
       </c>
       <c r="AA174" s="12"/>
@@ -10651,16 +10651,16 @@
       <c r="T175" s="12"/>
       <c r="U175" s="12"/>
       <c r="V175" s="12"/>
-      <c r="W175" s="6">
+      <c r="W175" s="7">
         <v>37.0</v>
       </c>
-      <c r="X175" s="6" t="s">
+      <c r="X175" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="Y175" s="6" t="s">
+      <c r="Y175" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Z175" s="6">
+      <c r="Z175" s="7">
         <v>1873.0</v>
       </c>
       <c r="AA175" s="12"/>
@@ -10691,16 +10691,16 @@
       <c r="T176" s="12"/>
       <c r="U176" s="12"/>
       <c r="V176" s="12"/>
-      <c r="W176" s="6">
+      <c r="W176" s="7">
         <v>38.0</v>
       </c>
-      <c r="X176" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y176" s="6" t="s">
+      <c r="X176" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y176" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z176" s="6">
+      <c r="Z176" s="7">
         <v>1822.0</v>
       </c>
       <c r="AA176" s="12"/>
@@ -10731,16 +10731,16 @@
       <c r="T177" s="12"/>
       <c r="U177" s="12"/>
       <c r="V177" s="12"/>
-      <c r="W177" s="6">
+      <c r="W177" s="7">
         <v>39.0</v>
       </c>
-      <c r="X177" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y177" s="6" t="s">
+      <c r="X177" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y177" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z177" s="6">
+      <c r="Z177" s="7">
         <v>1741.0</v>
       </c>
       <c r="AA177" s="12"/>
@@ -10771,16 +10771,16 @@
       <c r="T178" s="12"/>
       <c r="U178" s="12"/>
       <c r="V178" s="12"/>
-      <c r="W178" s="6">
+      <c r="W178" s="7">
         <v>40.0</v>
       </c>
-      <c r="X178" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y178" s="6" t="s">
+      <c r="X178" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y178" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z178" s="6">
+      <c r="Z178" s="7">
         <v>1724.0</v>
       </c>
       <c r="AA178" s="12"/>
@@ -10811,16 +10811,16 @@
       <c r="T179" s="12"/>
       <c r="U179" s="12"/>
       <c r="V179" s="12"/>
-      <c r="W179" s="6">
+      <c r="W179" s="7">
         <v>41.0</v>
       </c>
-      <c r="X179" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y179" s="6" t="s">
+      <c r="X179" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y179" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z179" s="6">
+      <c r="Z179" s="7">
         <v>1660.0</v>
       </c>
       <c r="AA179" s="12"/>
@@ -10851,16 +10851,16 @@
       <c r="T180" s="12"/>
       <c r="U180" s="12"/>
       <c r="V180" s="12"/>
-      <c r="W180" s="6">
+      <c r="W180" s="7">
         <v>42.0</v>
       </c>
-      <c r="X180" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y180" s="6" t="s">
+      <c r="X180" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y180" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z180" s="6">
+      <c r="Z180" s="7">
         <v>1640.0</v>
       </c>
       <c r="AA180" s="12"/>
@@ -10891,16 +10891,16 @@
       <c r="T181" s="12"/>
       <c r="U181" s="12"/>
       <c r="V181" s="12"/>
-      <c r="W181" s="6">
+      <c r="W181" s="7">
         <v>43.0</v>
       </c>
-      <c r="X181" s="6" t="s">
+      <c r="X181" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Y181" s="6" t="s">
+      <c r="Y181" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z181" s="6">
+      <c r="Z181" s="7">
         <v>1577.0</v>
       </c>
       <c r="AA181" s="12"/>
@@ -10931,16 +10931,16 @@
       <c r="T182" s="12"/>
       <c r="U182" s="12"/>
       <c r="V182" s="12"/>
-      <c r="W182" s="6">
+      <c r="W182" s="7">
         <v>44.0</v>
       </c>
-      <c r="X182" s="6" t="s">
+      <c r="X182" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Y182" s="6" t="s">
+      <c r="Y182" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z182" s="6">
+      <c r="Z182" s="7">
         <v>1565.0</v>
       </c>
       <c r="AA182" s="12"/>
@@ -10971,16 +10971,16 @@
       <c r="T183" s="12"/>
       <c r="U183" s="12"/>
       <c r="V183" s="12"/>
-      <c r="W183" s="6">
+      <c r="W183" s="7">
         <v>45.0</v>
       </c>
-      <c r="X183" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y183" s="6" t="s">
+      <c r="X183" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y183" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z183" s="6">
+      <c r="Z183" s="7">
         <v>1552.0</v>
       </c>
       <c r="AA183" s="12"/>
@@ -11011,16 +11011,16 @@
       <c r="T184" s="12"/>
       <c r="U184" s="12"/>
       <c r="V184" s="12"/>
-      <c r="W184" s="6">
+      <c r="W184" s="7">
         <v>46.0</v>
       </c>
-      <c r="X184" s="6" t="s">
+      <c r="X184" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Y184" s="6" t="s">
+      <c r="Y184" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z184" s="6">
+      <c r="Z184" s="7">
         <v>1404.0</v>
       </c>
       <c r="AA184" s="12"/>
@@ -11051,16 +11051,16 @@
       <c r="T185" s="12"/>
       <c r="U185" s="12"/>
       <c r="V185" s="12"/>
-      <c r="W185" s="6">
+      <c r="W185" s="7">
         <v>47.0</v>
       </c>
-      <c r="X185" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y185" s="6" t="s">
+      <c r="X185" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y185" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z185" s="6">
+      <c r="Z185" s="7">
         <v>1351.0</v>
       </c>
       <c r="AA185" s="12"/>
@@ -11091,16 +11091,16 @@
       <c r="T186" s="12"/>
       <c r="U186" s="12"/>
       <c r="V186" s="12"/>
-      <c r="W186" s="6">
+      <c r="W186" s="7">
         <v>48.0</v>
       </c>
-      <c r="X186" s="6" t="s">
+      <c r="X186" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="Y186" s="6" t="s">
+      <c r="Y186" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z186" s="6">
+      <c r="Z186" s="7">
         <v>1344.0</v>
       </c>
       <c r="AA186" s="12"/>
@@ -11131,16 +11131,16 @@
       <c r="T187" s="12"/>
       <c r="U187" s="12"/>
       <c r="V187" s="12"/>
-      <c r="W187" s="6">
+      <c r="W187" s="7">
         <v>49.0</v>
       </c>
-      <c r="X187" s="6" t="s">
+      <c r="X187" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="Y187" s="6" t="s">
+      <c r="Y187" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z187" s="6">
+      <c r="Z187" s="7">
         <v>1299.0</v>
       </c>
       <c r="AA187" s="12"/>
@@ -11171,16 +11171,16 @@
       <c r="T188" s="12"/>
       <c r="U188" s="12"/>
       <c r="V188" s="12"/>
-      <c r="W188" s="6">
+      <c r="W188" s="7">
         <v>50.0</v>
       </c>
-      <c r="X188" s="6" t="s">
+      <c r="X188" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="Y188" s="6" t="s">
+      <c r="Y188" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z188" s="6">
+      <c r="Z188" s="7">
         <v>1261.0</v>
       </c>
       <c r="AA188" s="12"/>
@@ -11211,16 +11211,16 @@
       <c r="T189" s="12"/>
       <c r="U189" s="12"/>
       <c r="V189" s="12"/>
-      <c r="W189" s="6">
+      <c r="W189" s="7">
         <v>51.0</v>
       </c>
-      <c r="X189" s="6" t="s">
+      <c r="X189" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Y189" s="6" t="s">
+      <c r="Y189" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z189" s="6">
+      <c r="Z189" s="7">
         <v>1247.0</v>
       </c>
       <c r="AA189" s="12"/>
@@ -11251,16 +11251,16 @@
       <c r="T190" s="12"/>
       <c r="U190" s="12"/>
       <c r="V190" s="12"/>
-      <c r="W190" s="6">
+      <c r="W190" s="7">
         <v>52.0</v>
       </c>
-      <c r="X190" s="6" t="s">
+      <c r="X190" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="6" t="s">
+      <c r="Y190" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z190" s="6">
+      <c r="Z190" s="7">
         <v>1226.0</v>
       </c>
       <c r="AA190" s="12"/>
@@ -11291,16 +11291,16 @@
       <c r="T191" s="12"/>
       <c r="U191" s="12"/>
       <c r="V191" s="12"/>
-      <c r="W191" s="6">
+      <c r="W191" s="7">
         <v>53.0</v>
       </c>
-      <c r="X191" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y191" s="6" t="s">
+      <c r="X191" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y191" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z191" s="6">
+      <c r="Z191" s="7">
         <v>1211.0</v>
       </c>
       <c r="AA191" s="12"/>
@@ -11331,16 +11331,16 @@
       <c r="T192" s="12"/>
       <c r="U192" s="12"/>
       <c r="V192" s="12"/>
-      <c r="W192" s="6">
+      <c r="W192" s="7">
         <v>54.0</v>
       </c>
-      <c r="X192" s="6" t="s">
+      <c r="X192" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Y192" s="6" t="s">
+      <c r="Y192" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z192" s="6">
+      <c r="Z192" s="7">
         <v>1197.0</v>
       </c>
       <c r="AA192" s="12"/>
@@ -11371,16 +11371,16 @@
       <c r="T193" s="12"/>
       <c r="U193" s="12"/>
       <c r="V193" s="12"/>
-      <c r="W193" s="6">
+      <c r="W193" s="7">
         <v>55.0</v>
       </c>
-      <c r="X193" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y193" s="6" t="s">
+      <c r="X193" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y193" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z193" s="6">
+      <c r="Z193" s="7">
         <v>1184.0</v>
       </c>
       <c r="AA193" s="12"/>
@@ -11411,16 +11411,16 @@
       <c r="T194" s="12"/>
       <c r="U194" s="12"/>
       <c r="V194" s="12"/>
-      <c r="W194" s="6">
+      <c r="W194" s="7">
         <v>56.0</v>
       </c>
-      <c r="X194" s="6" t="s">
+      <c r="X194" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Y194" s="6" t="s">
+      <c r="Y194" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z194" s="6">
+      <c r="Z194" s="7">
         <v>1157.0</v>
       </c>
       <c r="AA194" s="12"/>
@@ -11451,16 +11451,16 @@
       <c r="T195" s="12"/>
       <c r="U195" s="12"/>
       <c r="V195" s="12"/>
-      <c r="W195" s="6">
+      <c r="W195" s="7">
         <v>57.0</v>
       </c>
-      <c r="X195" s="6" t="s">
+      <c r="X195" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="Y195" s="6" t="s">
+      <c r="Y195" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z195" s="6">
+      <c r="Z195" s="7">
         <v>1143.0</v>
       </c>
       <c r="AA195" s="12"/>
@@ -11491,16 +11491,16 @@
       <c r="T196" s="12"/>
       <c r="U196" s="12"/>
       <c r="V196" s="12"/>
-      <c r="W196" s="6">
+      <c r="W196" s="7">
         <v>58.0</v>
       </c>
-      <c r="X196" s="6" t="s">
+      <c r="X196" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="Y196" s="6" t="s">
+      <c r="Y196" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z196" s="6">
+      <c r="Z196" s="7">
         <v>1078.0</v>
       </c>
       <c r="AA196" s="12"/>
@@ -11531,16 +11531,16 @@
       <c r="T197" s="12"/>
       <c r="U197" s="12"/>
       <c r="V197" s="12"/>
-      <c r="W197" s="6">
+      <c r="W197" s="7">
         <v>59.0</v>
       </c>
-      <c r="X197" s="6" t="s">
+      <c r="X197" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="Y197" s="6" t="s">
+      <c r="Y197" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z197" s="6">
+      <c r="Z197" s="7">
         <v>1069.0</v>
       </c>
       <c r="AA197" s="12"/>
@@ -11571,16 +11571,16 @@
       <c r="T198" s="12"/>
       <c r="U198" s="12"/>
       <c r="V198" s="12"/>
-      <c r="W198" s="6">
+      <c r="W198" s="7">
         <v>60.0</v>
       </c>
-      <c r="X198" s="6" t="s">
+      <c r="X198" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="Y198" s="6" t="s">
+      <c r="Y198" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z198" s="6">
+      <c r="Z198" s="7">
         <v>1000.0</v>
       </c>
       <c r="AA198" s="12"/>
@@ -11611,16 +11611,16 @@
       <c r="T199" s="12"/>
       <c r="U199" s="12"/>
       <c r="V199" s="12"/>
-      <c r="W199" s="6">
+      <c r="W199" s="7">
         <v>61.0</v>
       </c>
-      <c r="X199" s="6" t="s">
+      <c r="X199" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="Y199" s="6" t="s">
+      <c r="Y199" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z199" s="6">
+      <c r="Z199" s="7">
         <v>987.0</v>
       </c>
       <c r="AA199" s="12"/>
@@ -11651,16 +11651,16 @@
       <c r="T200" s="12"/>
       <c r="U200" s="12"/>
       <c r="V200" s="12"/>
-      <c r="W200" s="6">
+      <c r="W200" s="7">
         <v>62.0</v>
       </c>
-      <c r="X200" s="6" t="s">
+      <c r="X200" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Y200" s="6" t="s">
+      <c r="Y200" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z200" s="6">
+      <c r="Z200" s="7">
         <v>952.0</v>
       </c>
       <c r="AA200" s="12"/>
@@ -11691,16 +11691,16 @@
       <c r="T201" s="12"/>
       <c r="U201" s="12"/>
       <c r="V201" s="12"/>
-      <c r="W201" s="6">
+      <c r="W201" s="7">
         <v>63.0</v>
       </c>
-      <c r="X201" s="6" t="s">
+      <c r="X201" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y201" s="6" t="s">
+      <c r="Y201" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z201" s="6">
+      <c r="Z201" s="7">
         <v>913.0</v>
       </c>
       <c r="AA201" s="12"/>
@@ -11731,16 +11731,16 @@
       <c r="T202" s="12"/>
       <c r="U202" s="12"/>
       <c r="V202" s="12"/>
-      <c r="W202" s="6">
+      <c r="W202" s="7">
         <v>64.0</v>
       </c>
-      <c r="X202" s="6" t="s">
+      <c r="X202" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Y202" s="6" t="s">
+      <c r="Y202" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z202" s="6">
+      <c r="Z202" s="7">
         <v>905.0</v>
       </c>
       <c r="AA202" s="12"/>
@@ -11771,16 +11771,16 @@
       <c r="T203" s="12"/>
       <c r="U203" s="12"/>
       <c r="V203" s="12"/>
-      <c r="W203" s="6">
+      <c r="W203" s="7">
         <v>65.0</v>
       </c>
-      <c r="X203" s="6" t="s">
+      <c r="X203" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="Y203" s="6" t="s">
+      <c r="Y203" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z203" s="6">
+      <c r="Z203" s="7">
         <v>842.0</v>
       </c>
       <c r="AA203" s="12"/>
@@ -11811,16 +11811,16 @@
       <c r="T204" s="12"/>
       <c r="U204" s="12"/>
       <c r="V204" s="12"/>
-      <c r="W204" s="6">
+      <c r="W204" s="7">
         <v>66.0</v>
       </c>
-      <c r="X204" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y204" s="6" t="s">
+      <c r="X204" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y204" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z204" s="6">
+      <c r="Z204" s="7">
         <v>823.0</v>
       </c>
       <c r="AA204" s="12"/>
@@ -11851,16 +11851,16 @@
       <c r="T205" s="12"/>
       <c r="U205" s="12"/>
       <c r="V205" s="12"/>
-      <c r="W205" s="6">
+      <c r="W205" s="7">
         <v>67.0</v>
       </c>
-      <c r="X205" s="6" t="s">
+      <c r="X205" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Y205" s="6" t="s">
+      <c r="Y205" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z205" s="6">
+      <c r="Z205" s="7">
         <v>820.0</v>
       </c>
       <c r="AA205" s="12"/>
@@ -11891,16 +11891,16 @@
       <c r="T206" s="12"/>
       <c r="U206" s="12"/>
       <c r="V206" s="12"/>
-      <c r="W206" s="6">
+      <c r="W206" s="7">
         <v>68.0</v>
       </c>
-      <c r="X206" s="6" t="s">
+      <c r="X206" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Y206" s="6" t="s">
+      <c r="Y206" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Z206" s="6">
+      <c r="Z206" s="7">
         <v>805.0</v>
       </c>
       <c r="AA206" s="12"/>
@@ -11931,16 +11931,16 @@
       <c r="T207" s="12"/>
       <c r="U207" s="12"/>
       <c r="V207" s="12"/>
-      <c r="W207" s="6">
+      <c r="W207" s="7">
         <v>69.0</v>
       </c>
-      <c r="X207" s="6" t="s">
+      <c r="X207" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="Y207" s="6" t="s">
+      <c r="Y207" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="Z207" s="6">
+      <c r="Z207" s="7">
         <v>782.0</v>
       </c>
       <c r="AA207" s="12"/>
@@ -11971,16 +11971,16 @@
       <c r="T208" s="12"/>
       <c r="U208" s="12"/>
       <c r="V208" s="12"/>
-      <c r="W208" s="6">
+      <c r="W208" s="7">
         <v>70.0</v>
       </c>
-      <c r="X208" s="6" t="s">
+      <c r="X208" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="Y208" s="6" t="s">
+      <c r="Y208" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z208" s="6">
+      <c r="Z208" s="7">
         <v>736.0</v>
       </c>
       <c r="AA208" s="12"/>
@@ -12011,16 +12011,16 @@
       <c r="T209" s="12"/>
       <c r="U209" s="12"/>
       <c r="V209" s="12"/>
-      <c r="W209" s="6">
+      <c r="W209" s="7">
         <v>71.0</v>
       </c>
-      <c r="X209" s="6" t="s">
+      <c r="X209" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="Y209" s="6" t="s">
+      <c r="Y209" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z209" s="6">
+      <c r="Z209" s="7">
         <v>733.0</v>
       </c>
       <c r="AA209" s="12"/>
@@ -12051,16 +12051,16 @@
       <c r="T210" s="12"/>
       <c r="U210" s="12"/>
       <c r="V210" s="12"/>
-      <c r="W210" s="6">
+      <c r="W210" s="7">
         <v>72.0</v>
       </c>
-      <c r="X210" s="6" t="s">
+      <c r="X210" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="Y210" s="6" t="s">
+      <c r="Y210" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z210" s="6">
+      <c r="Z210" s="7">
         <v>700.0</v>
       </c>
       <c r="AA210" s="12"/>
@@ -12091,16 +12091,16 @@
       <c r="T211" s="12"/>
       <c r="U211" s="12"/>
       <c r="V211" s="12"/>
-      <c r="W211" s="6">
+      <c r="W211" s="7">
         <v>73.0</v>
       </c>
-      <c r="X211" s="6" t="s">
+      <c r="X211" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="Y211" s="6" t="s">
+      <c r="Y211" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z211" s="6">
+      <c r="Z211" s="7">
         <v>649.0</v>
       </c>
       <c r="AA211" s="12"/>
@@ -12131,16 +12131,16 @@
       <c r="T212" s="12"/>
       <c r="U212" s="12"/>
       <c r="V212" s="12"/>
-      <c r="W212" s="6">
+      <c r="W212" s="7">
         <v>74.0</v>
       </c>
-      <c r="X212" s="6" t="s">
+      <c r="X212" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="Y212" s="6" t="s">
+      <c r="Y212" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z212" s="6">
+      <c r="Z212" s="7">
         <v>636.0</v>
       </c>
       <c r="AA212" s="12"/>
@@ -12171,16 +12171,16 @@
       <c r="T213" s="12"/>
       <c r="U213" s="12"/>
       <c r="V213" s="12"/>
-      <c r="W213" s="6">
+      <c r="W213" s="7">
         <v>75.0</v>
       </c>
-      <c r="X213" s="6" t="s">
+      <c r="X213" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="Y213" s="6" t="s">
+      <c r="Y213" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z213" s="6">
+      <c r="Z213" s="7">
         <v>528.0</v>
       </c>
       <c r="AA213" s="12"/>
@@ -12211,16 +12211,16 @@
       <c r="T214" s="12"/>
       <c r="U214" s="12"/>
       <c r="V214" s="12"/>
-      <c r="W214" s="6">
+      <c r="W214" s="7">
         <v>76.0</v>
       </c>
-      <c r="X214" s="6" t="s">
+      <c r="X214" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="Y214" s="6" t="s">
+      <c r="Y214" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="Z214" s="6">
+      <c r="Z214" s="7">
         <v>473.0</v>
       </c>
       <c r="AA214" s="12"/>
@@ -12251,16 +12251,16 @@
       <c r="T215" s="12"/>
       <c r="U215" s="12"/>
       <c r="V215" s="12"/>
-      <c r="W215" s="6">
+      <c r="W215" s="7">
         <v>78.0</v>
       </c>
-      <c r="X215" s="6" t="s">
+      <c r="X215" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Y215" s="6" t="s">
+      <c r="Y215" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="Z215" s="6">
+      <c r="Z215" s="7">
         <v>435.0</v>
       </c>
       <c r="AA215" s="12"/>
@@ -12291,13 +12291,13 @@
       <c r="T216" s="12"/>
       <c r="U216" s="12"/>
       <c r="V216" s="12"/>
-      <c r="W216" s="6">
+      <c r="W216" s="7">
         <v>79.0</v>
       </c>
-      <c r="X216" s="6" t="s">
+      <c r="X216" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Y216" s="6" t="s">
+      <c r="Y216" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z216" s="12"/>
@@ -12329,13 +12329,13 @@
       <c r="T217" s="12"/>
       <c r="U217" s="12"/>
       <c r="V217" s="12"/>
-      <c r="W217" s="6">
+      <c r="W217" s="7">
         <v>80.0</v>
       </c>
-      <c r="X217" s="6" t="s">
+      <c r="X217" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="Y217" s="6" t="s">
+      <c r="Y217" s="7" t="s">
         <v>140</v>
       </c>
       <c r="Z217" s="12"/>
@@ -37468,17 +37468,17 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="8">
@@ -37533,7 +37533,7 @@
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="8">
@@ -37575,7 +37575,7 @@
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="8">
@@ -37613,7 +37613,7 @@
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="8">
@@ -37651,7 +37651,7 @@
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="8">
@@ -37689,7 +37689,7 @@
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="8">
@@ -37726,8 +37726,8 @@
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>33</v>
+      <c r="B8" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="8">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="8">
         <f>L4-L7
@@ -37764,8 +37764,8 @@
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>35</v>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>53.0</v>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L9" s="8">
         <f>L6-L8
@@ -37802,7 +37802,7 @@
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="8">
@@ -37839,7 +37839,7 @@
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="8">
@@ -37876,7 +37876,7 @@
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="8">
@@ -37906,7 +37906,7 @@
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="8">
@@ -37943,7 +37943,7 @@
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="8">
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37980,8 +37980,8 @@
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>47</v>
+      <c r="B15" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38010,8 +38010,8 @@
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>48</v>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C16" s="8">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38057,8 +38057,8 @@
       <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>52</v>
+      <c r="B17" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38087,8 +38087,8 @@
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>53</v>
+      <c r="B18" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38124,8 +38124,8 @@
       <c r="A19" s="1">
         <v>18.0</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>55</v>
+      <c r="B19" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C19" s="8">
         <v>18.5</v>
@@ -38154,8 +38154,8 @@
       <c r="A20" s="1">
         <v>19.0</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>57</v>
+      <c r="B20" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C20" s="8">
         <v>16.5</v>
@@ -38184,8 +38184,8 @@
       <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>58</v>
+      <c r="B21" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38214,8 +38214,8 @@
       <c r="A22" s="1">
         <v>21.0</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>59</v>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="8">
         <v>13.5</v>
@@ -38244,8 +38244,8 @@
       <c r="A23" s="1">
         <v>22.0</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>60</v>
+      <c r="B23" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38274,8 +38274,8 @@
       <c r="A24" s="1">
         <v>23.0</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>61</v>
+      <c r="B24" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38304,8 +38304,8 @@
       <c r="A25" s="1">
         <v>24.0</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>62</v>
+      <c r="B25" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38334,8 +38334,8 @@
       <c r="A26" s="1">
         <v>25.0</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>64</v>
+      <c r="B26" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38364,8 +38364,8 @@
       <c r="A27" s="1">
         <v>26.0</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>65</v>
+      <c r="B27" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38400,8 +38400,8 @@
       <c r="A28" s="1">
         <v>27.0</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>67</v>
+      <c r="B28" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38430,8 +38430,8 @@
       <c r="A29" s="1">
         <v>28.0</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>68</v>
+      <c r="B29" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38460,8 +38460,8 @@
       <c r="A30" s="1">
         <v>29.0</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>69</v>
+      <c r="B30" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38490,8 +38490,8 @@
       <c r="A31" s="1">
         <v>30.0</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>70</v>
+      <c r="B31" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="8">
         <v>6.0</v>
@@ -38520,8 +38520,8 @@
       <c r="A32" s="1">
         <v>31.0</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>71</v>
+      <c r="B32" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="C32" s="8">
         <v>5.5</v>
@@ -38550,8 +38550,8 @@
       <c r="A33" s="1">
         <v>32.0</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>72</v>
+      <c r="B33" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="C33" s="8">
         <v>5.0</v>
@@ -38580,8 +38580,8 @@
       <c r="A34" s="1">
         <v>33.0</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>73</v>
+      <c r="B34" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="C34" s="8">
         <v>4.5</v>
@@ -38610,8 +38610,8 @@
       <c r="A35" s="1">
         <v>34.0</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>74</v>
+      <c r="B35" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="C35" s="8">
         <v>4.5</v>
@@ -38640,8 +38640,8 @@
       <c r="A36" s="1">
         <v>35.0</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>75</v>
+      <c r="B36" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C36" s="8">
         <v>4.0</v>
@@ -38670,8 +38670,8 @@
       <c r="A37" s="1">
         <v>36.0</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>76</v>
+      <c r="B37" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="C37" s="8">
         <v>4.0</v>
@@ -38700,8 +38700,8 @@
       <c r="A38" s="1">
         <v>37.0</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>77</v>
+      <c r="B38" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="C38" s="8">
         <v>3.5</v>
@@ -38730,8 +38730,8 @@
       <c r="A39" s="1">
         <v>38.0</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>78</v>
+      <c r="B39" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="C39" s="8">
         <v>3.5</v>
@@ -38760,8 +38760,8 @@
       <c r="A40" s="1">
         <v>39.0</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>79</v>
+      <c r="B40" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="C40" s="8">
         <v>3.0</v>
@@ -38790,8 +38790,8 @@
       <c r="A41" s="1">
         <v>40.0</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>80</v>
+      <c r="B41" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C41" s="8">
         <v>3.0</v>
@@ -38820,8 +38820,8 @@
       <c r="A42" s="1">
         <v>41.0</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>81</v>
+      <c r="B42" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="C42" s="8">
         <v>2.5</v>
@@ -38850,8 +38850,8 @@
       <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>82</v>
+      <c r="B43" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="C43" s="8">
         <v>2.5</v>
@@ -38880,8 +38880,8 @@
       <c r="A44" s="1">
         <v>43.0</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>83</v>
+      <c r="B44" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C44" s="8">
         <v>2.5</v>
@@ -38910,8 +38910,8 @@
       <c r="A45" s="1">
         <v>44.0</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>84</v>
+      <c r="B45" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C45" s="8">
         <v>2.5</v>
@@ -38940,8 +38940,8 @@
       <c r="A46" s="1">
         <v>45.0</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>85</v>
+      <c r="B46" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="C46" s="8">
         <v>2.0</v>
@@ -38970,8 +38970,8 @@
       <c r="A47" s="1">
         <v>46.0</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>86</v>
+      <c r="B47" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="C47" s="8">
         <v>2.0</v>
@@ -39000,8 +39000,8 @@
       <c r="A48" s="1">
         <v>47.0</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>87</v>
+      <c r="B48" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="C48" s="8">
         <v>2.0</v>
@@ -39030,7 +39030,7 @@
       <c r="A49" s="1">
         <v>48.0</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="8">
@@ -39060,7 +39060,7 @@
       <c r="A50" s="1">
         <v>49.0</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="8">
@@ -39090,7 +39090,7 @@
       <c r="A51" s="1">
         <v>50.0</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="8">
@@ -39120,7 +39120,7 @@
       <c r="A52" s="1">
         <v>51.0</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C52" s="8">
@@ -39150,7 +39150,7 @@
       <c r="A53" s="1">
         <v>52.0</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C53" s="8">
@@ -39180,7 +39180,7 @@
       <c r="A54" s="1">
         <v>53.0</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C54" s="8">
@@ -39210,7 +39210,7 @@
       <c r="A55" s="1">
         <v>54.0</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C55" s="8">
@@ -39240,7 +39240,7 @@
       <c r="A56" s="1">
         <v>55.0</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="8">
@@ -39270,7 +39270,7 @@
       <c r="A57" s="1">
         <v>56.0</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="8">
@@ -39300,7 +39300,7 @@
       <c r="A58" s="1">
         <v>57.0</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="8">
@@ -39330,7 +39330,7 @@
       <c r="A59" s="1">
         <v>58.0</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="8">
@@ -39360,7 +39360,7 @@
       <c r="A60" s="1">
         <v>59.0</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="8">
@@ -39390,7 +39390,7 @@
       <c r="A61" s="1">
         <v>60.0</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="8">
@@ -39420,7 +39420,7 @@
       <c r="A62" s="1">
         <v>61.0</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="7" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="8">
@@ -39450,7 +39450,7 @@
       <c r="A63" s="1">
         <v>62.0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="8">
@@ -39480,7 +39480,7 @@
       <c r="A64" s="1">
         <v>63.0</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="8">
@@ -39510,7 +39510,7 @@
       <c r="A65" s="1">
         <v>64.0</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="8">
@@ -39540,7 +39540,7 @@
       <c r="A66" s="1">
         <v>65.0</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="8">
@@ -39570,7 +39570,7 @@
       <c r="A67" s="1">
         <v>66.0</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C67" s="8">
@@ -39600,7 +39600,7 @@
       <c r="A68" s="1">
         <v>67.0</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C68" s="8">
@@ -39630,7 +39630,7 @@
       <c r="A69" s="1">
         <v>68.0</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="8">
@@ -39660,7 +39660,7 @@
       <c r="A70" s="1">
         <v>69.0</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="8">
@@ -39690,7 +39690,7 @@
       <c r="A71" s="1">
         <v>70.0</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>110</v>
       </c>
       <c r="C71" s="8">
@@ -39720,7 +39720,7 @@
       <c r="A72" s="1">
         <v>71.0</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C72" s="8">

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -116,10 +116,10 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>My Remaining</t>
   </si>
   <si>
-    <t>My Remaining</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>KC Concepcion</t>
@@ -131,10 +131,10 @@
     <t>Jadarian Price</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Avg $ per Other Team</t>
   </si>
   <si>
-    <t>Avg $ per Other Team</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Eli Stowers</t>
@@ -143,10 +143,10 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Omar Cooper</t>
   </si>
   <si>
-    <t>Omar Cooper</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>CJ Allen</t>
@@ -272,33 +272,6 @@
     <t>Oscar Delp</t>
   </si>
   <si>
-    <t>Michael Trigg</t>
-  </si>
-  <si>
-    <t>Demond Claiborne</t>
-  </si>
-  <si>
-    <t>Malachi Lawrence</t>
-  </si>
-  <si>
-    <t>CJ Donaldson</t>
-  </si>
-  <si>
-    <t>T.J. Parker</t>
-  </si>
-  <si>
-    <t>Cashius Howell</t>
-  </si>
-  <si>
-    <t>Keldric Faulk</t>
-  </si>
-  <si>
-    <t>Akheem Mesidor</t>
-  </si>
-  <si>
-    <t>Justin Joly</t>
-  </si>
-  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -326,19 +299,58 @@
     <t>Key</t>
   </si>
   <si>
+    <t>Michael Trigg</t>
+  </si>
+  <si>
+    <t>Demond Claiborne</t>
+  </si>
+  <si>
+    <t>Ed</t>
+  </si>
+  <si>
+    <t>Malachi Lawrence</t>
+  </si>
+  <si>
+    <t>CJ Donaldson</t>
+  </si>
+  <si>
+    <t>T.J. Parker</t>
+  </si>
+  <si>
+    <t>Cashius Howell</t>
+  </si>
+  <si>
+    <t>Keldric Faulk</t>
+  </si>
+  <si>
+    <t>Brent</t>
+  </si>
+  <si>
+    <t>Akheem Mesidor</t>
+  </si>
+  <si>
+    <t>Justin Joly</t>
+  </si>
+  <si>
+    <t>Joey</t>
+  </si>
+  <si>
     <t>Eli Raridon</t>
   </si>
   <si>
     <t>DJ Rogers</t>
   </si>
   <si>
+    <t>MaKayla</t>
+  </si>
+  <si>
     <t>Lake McRee</t>
   </si>
   <si>
-    <t>Ed</t>
+    <t>Cade Klubnik</t>
   </si>
   <si>
-    <t>Cade Klubnik</t>
+    <t>Ty</t>
   </si>
   <si>
     <t>Drew Allar</t>
@@ -350,7 +362,13 @@
     <t>Joe Royer</t>
   </si>
   <si>
+    <t>Kich</t>
+  </si>
+  <si>
     <t>Sam Roush</t>
+  </si>
+  <si>
+    <t>Eric</t>
   </si>
   <si>
     <t>Tanner Koziol</t>
@@ -359,13 +377,16 @@
     <t>Jack Endries</t>
   </si>
   <si>
+    <t>Collin</t>
+  </si>
+  <si>
     <t>Matthew Hibner</t>
   </si>
   <si>
     <t>Tyren Montgomery</t>
   </si>
   <si>
-    <t>Brent</t>
+    <t>Roy</t>
   </si>
   <si>
     <t>Bryce Lance</t>
@@ -374,10 +395,10 @@
     <t>Kevin Coleman</t>
   </si>
   <si>
-    <t>Garrett Nussmeier</t>
+    <t>Jason</t>
   </si>
   <si>
-    <t>Joey</t>
+    <t>Garrett Nussmeier</t>
   </si>
   <si>
     <t>Nate Boerkircher</t>
@@ -386,31 +407,10 @@
     <t>Will Kacmarek</t>
   </si>
   <si>
-    <t>Noah Whittington</t>
+    <t>Blaine</t>
   </si>
   <si>
-    <t>MaKayla</t>
-  </si>
-  <si>
-    <t>Ty</t>
-  </si>
-  <si>
-    <t>Kich</t>
-  </si>
-  <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>Collin</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
-    <t>Jason</t>
-  </si>
-  <si>
-    <t>Blaine</t>
+    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Joel</t>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="15">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" s="15">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P5" s="15">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="S29" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="U29" s="8"/>
       <c r="V29" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="X29" s="6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
@@ -3146,7 +3146,7 @@
         <v>1.0</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="4">
@@ -3221,7 +3221,7 @@
         <v>2.0</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="Q31" s="8"/>
       <c r="R31" s="4">
@@ -3296,7 +3296,7 @@
         <v>3.0</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="Q32" s="8"/>
       <c r="R32" s="4">
@@ -3371,7 +3371,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="4">
@@ -3446,7 +3446,7 @@
         <v>5.0</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="Q34" s="8"/>
       <c r="R34" s="4">
@@ -3521,7 +3521,7 @@
         <v>6.0</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="Q35" s="8"/>
       <c r="R35" s="4">
@@ -3596,7 +3596,7 @@
         <v>7.0</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="8"/>
       <c r="R36" s="4">
@@ -3671,7 +3671,7 @@
         <v>8.0</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="Q37" s="8"/>
       <c r="R37" s="4">
@@ -3746,7 +3746,7 @@
         <v>9.0</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="Q38" s="8"/>
       <c r="R38" s="4">
@@ -3821,7 +3821,7 @@
         <v>10.0</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="8"/>
       <c r="R39" s="4">
@@ -3896,7 +3896,7 @@
         <v>11.0</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q40" s="8"/>
       <c r="R40" s="4">
@@ -4175,7 +4175,7 @@
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
       <c r="O44" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>9</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="S44" s="8"/>
       <c r="T44" s="8"/>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="S64" s="8"/>
       <c r="T64" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U64" s="15">
         <f t="shared" si="22"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="S65" s="8"/>
       <c r="T65" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="U65" s="15">
         <f t="shared" si="22"/>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="S66" s="8"/>
       <c r="T66" s="8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="U66" s="15">
         <f t="shared" si="22"/>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="S67" s="8"/>
       <c r="T67" s="8" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="U67" s="15">
         <f t="shared" si="22"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="S68" s="8"/>
       <c r="T68" s="8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="U68" s="15">
         <f t="shared" si="22"/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="S69" s="8"/>
       <c r="T69" s="8" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="U69" s="15">
         <f t="shared" si="22"/>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="S70" s="8"/>
       <c r="T70" s="8" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="U70" s="15">
         <f t="shared" si="22"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="S71" s="8"/>
       <c r="T71" s="8" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="U71" s="15">
         <f t="shared" si="22"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="S72" s="8"/>
       <c r="T72" s="8" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="U72" s="15">
         <f t="shared" si="22"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S73" s="8"/>
       <c r="T73" s="8" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="U73" s="15">
         <f t="shared" si="22"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="S74" s="8"/>
       <c r="T74" s="8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="U74" s="15">
         <f t="shared" si="22"/>
@@ -10535,7 +10535,7 @@
         <v>34.0</v>
       </c>
       <c r="X172" s="11" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y172" s="11" t="s">
         <v>146</v>
@@ -10615,7 +10615,7 @@
         <v>36.0</v>
       </c>
       <c r="X174" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Y174" s="11" t="s">
         <v>144</v>
@@ -10895,7 +10895,7 @@
         <v>43.0</v>
       </c>
       <c r="X181" s="11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Y181" s="11" t="s">
         <v>144</v>
@@ -10935,7 +10935,7 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="Y182" s="11" t="s">
         <v>142</v>
@@ -10975,7 +10975,7 @@
         <v>45.0</v>
       </c>
       <c r="X183" s="11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="Y183" s="11" t="s">
         <v>140</v>
@@ -11015,7 +11015,7 @@
         <v>46.0</v>
       </c>
       <c r="X184" s="11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="Y184" s="11" t="s">
         <v>141</v>
@@ -11175,7 +11175,7 @@
         <v>50.0</v>
       </c>
       <c r="X188" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Y188" s="11" t="s">
         <v>142</v>
@@ -11295,7 +11295,7 @@
         <v>53.0</v>
       </c>
       <c r="X191" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="Y191" s="11" t="s">
         <v>144</v>
@@ -11575,7 +11575,7 @@
         <v>60.0</v>
       </c>
       <c r="X198" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Y198" s="11" t="s">
         <v>144</v>
@@ -11655,7 +11655,7 @@
         <v>62.0</v>
       </c>
       <c r="X200" s="11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="Y200" s="11" t="s">
         <v>144</v>
@@ -11775,7 +11775,7 @@
         <v>65.0</v>
       </c>
       <c r="X203" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Y203" s="11" t="s">
         <v>142</v>
@@ -12135,7 +12135,7 @@
         <v>74.0</v>
       </c>
       <c r="X212" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Y212" s="11" t="s">
         <v>142</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L8" s="12">
         <f>L4-L7
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L10" s="12">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="12">
         <v>39.0</v>
@@ -38971,7 +38971,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C47" s="12">
         <v>2.0</v>
@@ -39001,7 +39001,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C48" s="12">
         <v>2.0</v>
@@ -39031,7 +39031,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C49" s="12">
         <v>2.0</v>
@@ -39061,7 +39061,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C50" s="12">
         <v>2.0</v>
@@ -39091,7 +39091,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C51" s="12">
         <v>2.0</v>
@@ -39121,7 +39121,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C52" s="12">
         <v>2.0</v>
@@ -39151,7 +39151,7 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C53" s="12">
         <v>2.0</v>
@@ -39181,7 +39181,7 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C54" s="12">
         <v>2.0</v>
@@ -39211,7 +39211,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C55" s="12">
         <v>2.0</v>
@@ -39241,7 +39241,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C56" s="12">
         <v>2.0</v>
@@ -39271,7 +39271,7 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C57" s="12">
         <v>2.0</v>
@@ -39301,7 +39301,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C58" s="12">
         <v>2.0</v>
@@ -39331,7 +39331,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C59" s="12">
         <v>2.0</v>
@@ -39361,7 +39361,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C60" s="12">
         <v>2.0</v>
@@ -39391,7 +39391,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C61" s="12">
         <v>2.0</v>
@@ -39421,7 +39421,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C62" s="12">
         <v>1.0</v>
@@ -39451,7 +39451,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C63" s="12">
         <v>1.0</v>
@@ -39481,7 +39481,7 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C64" s="12">
         <v>1.0</v>
@@ -39511,7 +39511,7 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C65" s="12">
         <v>1.0</v>
@@ -39541,7 +39541,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C66" s="12">
         <v>1.0</v>
@@ -39571,7 +39571,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C67" s="12">
         <v>1.0</v>
@@ -39601,7 +39601,7 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C68" s="12">
         <v>1.0</v>
@@ -39631,7 +39631,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C69" s="12">
         <v>1.0</v>
@@ -39661,7 +39661,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C70" s="12">
         <v>1.0</v>
@@ -39691,7 +39691,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C71" s="12">
         <v>1.0</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C72" s="12">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C73" s="12">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -110,13 +110,13 @@
     <t>My Spent</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>Sonny Styles</t>
   </si>
   <si>
     <t>My Remaining</t>
+  </si>
+  <si>
+    <t>Round 1</t>
   </si>
   <si>
     <t>KC Concepcion</t>
@@ -149,9 +149,6 @@
     <t>Arvell Reese</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Inflation Factor</t>
   </si>
   <si>
@@ -164,13 +161,10 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Caleb Downs</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -191,7 +185,7 @@
     <t>Dillon Thieneman</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Rueben Bain</t>
@@ -209,13 +203,13 @@
     <t>Mike Washington</t>
   </si>
   <si>
-    <t>Round 6</t>
-  </si>
-  <si>
     <t>Enforce % of Fair</t>
   </si>
   <si>
     <t>Antonio Williams</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -231,6 +225,9 @@
   </si>
   <si>
     <t>Zachariah Branch</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>De'Zhaun Stribling</t>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>Anthony Hill</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Skyler Bell</t>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y145" s="7" t="s">
         <v>143</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y147" s="7" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Y169" s="7" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y171" s="7" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Y177" s="7" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y178" s="7" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Y179" s="7" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y180" s="7" t="s">
         <v>140</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y193" s="7" t="s">
         <v>141</v>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="9">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="9">
         <f>L4-L7
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="9">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C26" s="9">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C27" s="9">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C28" s="9">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" s="9">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="9">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="9">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C32" s="9">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C33" s="9">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="9">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="9">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="9">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C37" s="9">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C38" s="9">
         <v>3.5</v>
@@ -38731,7 +38731,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C39" s="9">
         <v>3.5</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -50,10 +50,10 @@
     <t>Settings</t>
   </si>
   <si>
-    <t>Jeremiyah Love</t>
+    <t>Decay</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>New Values</t>
@@ -104,13 +104,13 @@
     <t>Remaining Leage $</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Kenyon Sadiq</t>
   </si>
   <si>
     <t>My Spent</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>Sonny Styles</t>
@@ -137,6 +137,9 @@
     <t>Budget Advantage Factor</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Omar Cooper</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Undrafted Predraft$</t>
+  </si>
+  <si>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -155,16 +161,19 @@
     <t>Ty Simpson</t>
   </si>
   <si>
-    <t>Denzel Boston</t>
+    <t>Round 4</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Denzel Boston</t>
   </si>
   <si>
     <t>Aggression</t>
   </si>
   <si>
     <t>Caleb Downs</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -176,13 +185,13 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Round 3</t>
-  </si>
-  <si>
     <t>Jonah Coleman</t>
   </si>
   <si>
     <t>Jake Golday</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Dillon Thieneman</t>
@@ -201,9 +210,6 @@
   </si>
   <si>
     <t>Mike Washington</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -227,9 +233,6 @@
     <t>Zachariah Branch</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>De'Zhaun Stribling</t>
   </si>
   <si>
@@ -243,9 +246,6 @@
   </si>
   <si>
     <t>Ja'Kobi Lane</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Anthony Hill</t>
@@ -920,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>14</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y140" s="6" t="s">
         <v>140</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="6" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y147" s="6" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y148" s="6" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y149" s="6" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y150" s="6" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="6" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Y155" s="6" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="6" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="6" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="6" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="6" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="6" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="6" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="6" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="6" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="6" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="6" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="6" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="6" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="6" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="6" t="s">
         <v>140</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="6" t="s">
         <v>141</v>
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="7">
         <v>139.0</v>
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="7">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" s="7">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="7">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C16" s="7">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C19" s="7">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="7">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" s="7">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="7">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="7">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" s="7">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="7">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="7">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C27" s="7">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="7">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="7">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" s="7">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C31" s="7">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C32" s="7">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="7">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="7">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="7">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C36" s="7">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="7">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="7">
         <v>3.5</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -38,10 +38,10 @@
     <t>Mine?</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Inflated Fair Price</t>
   </si>
   <si>
-    <t>Inflated Fair Price</t>
+    <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
@@ -56,16 +56,16 @@
     <t>Value vs Fair</t>
   </si>
   <si>
+    <t>Settings</t>
+  </si>
+  <si>
     <t>Floors</t>
   </si>
   <si>
-    <t>Settings</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Fractions</t>
-  </si>
-  <si>
-    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Monotone Rounded</t>
@@ -98,13 +98,13 @@
     <t>Total Spent $</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Makai Lemon</t>
   </si>
   <si>
     <t>Remaining Leage $</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>Kenyon Sadiq</t>
@@ -143,10 +143,10 @@
     <t>CJ Allen</t>
   </si>
   <si>
-    <t>Undrafted Predraft$</t>
+    <t>Round 2</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>Undrafted Predraft$</t>
   </si>
   <si>
     <t>Arvell Reese</t>
@@ -176,13 +176,13 @@
     <t>League Spent %</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Jacob Rodriguez</t>
   </si>
   <si>
     <t>Jonah Coleman</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>Chris Bell</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Germie Bernard</t>
@@ -215,7 +212,7 @@
     <t>Antonio Williams</t>
   </si>
   <si>
-    <t>Round 6</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Elijah Sarratt</t>
@@ -237,6 +234,9 @@
   </si>
   <si>
     <t>Malachi Fields</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Kaytron Allen</t>
@@ -347,6 +347,12 @@
     <t>Nate Boerkircher</t>
   </si>
   <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
+  </si>
+  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -368,16 +374,10 @@
     <t>Original Owner</t>
   </si>
   <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
     <t>New Owner</t>
   </si>
   <si>
     <t>Key</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Ed</t>
@@ -923,7 +923,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>10</v>
@@ -938,10 +938,10 @@
         <v>2026.0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>18</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P44" s="8" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y140" s="9" t="s">
         <v>140</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y143" s="9" t="s">
         <v>141</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y162" s="9" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y163" s="9" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y169" s="9" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y171" s="9" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y176" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -37459,7 +37459,7 @@
         <v>7</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>11</v>
@@ -37471,7 +37471,7 @@
         <v>13</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="10">
         <v>139.0</v>
@@ -37652,7 +37652,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="10">
         <v>76.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="10">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="10">
         <v>16.5</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="10">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="10">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="10">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28" s="10">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29" s="10">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" s="10">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="10">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="10">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33" s="10">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34" s="10">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="10">
         <v>4.5</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C72" s="10">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C73" s="10">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -29,10 +29,10 @@
     <t>Final Price</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Mine?</t>
   </si>
   <si>
-    <t>Mine?</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
@@ -47,16 +47,16 @@
     <t>EnforceUpTo</t>
   </si>
   <si>
+    <t>New Values</t>
+  </si>
+  <si>
     <t>Value vs Fair</t>
   </si>
   <si>
-    <t>New Values</t>
+    <t>Spine</t>
   </si>
   <si>
     <t>Settings</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Jeremiyah Love</t>
@@ -146,6 +146,9 @@
     <t>Undrafted Predraft$</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Arvell Reese</t>
   </si>
   <si>
@@ -155,19 +158,19 @@
     <t>Ty Simpson</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Denzel Boston</t>
   </si>
   <si>
     <t>Aggression</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>David Bailey</t>
@@ -179,10 +182,16 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
+    <t>Round 5</t>
+  </si>
+  <si>
     <t>Jonah Coleman</t>
   </si>
   <si>
     <t>Jake Golday</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Dillon Thieneman</t>
@@ -221,9 +230,6 @@
     <t>Max Klare</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Zachariah Branch</t>
   </si>
   <si>
@@ -245,9 +251,6 @@
     <t>Anthony Hill</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Skyler Bell</t>
   </si>
   <si>
@@ -261,9 +264,6 @@
   </si>
   <si>
     <t>Emmanuel McNeil-Warren</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>R Mason Thomas</t>
@@ -350,9 +350,6 @@
     <t>Will Kacmarek</t>
   </si>
   <si>
-    <t>Noah Whittington</t>
-  </si>
-  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Ed</t>
@@ -917,16 +917,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="P29" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="S29" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="T29" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="T29" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="W29" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="W29" s="10" t="s">
+      <c r="X29" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X29" s="10" t="s">
+      <c r="Y29" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="Y29" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P44" s="10" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y148" s="7" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y149" s="7" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="7" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y154" s="7" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Y155" s="7" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="7" t="s">
         <v>145</v>
@@ -9935,7 +9935,7 @@
         <v>19.0</v>
       </c>
       <c r="X157" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y157" s="7" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y161" s="7" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="7" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="7" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="7" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="7" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="7" t="s">
         <v>141</v>
@@ -10415,7 +10415,7 @@
         <v>31.0</v>
       </c>
       <c r="X169" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y169" s="7" t="s">
         <v>141</v>
@@ -10495,7 +10495,7 @@
         <v>33.0</v>
       </c>
       <c r="X171" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y171" s="7" t="s">
         <v>141</v>
@@ -10575,7 +10575,7 @@
         <v>35.0</v>
       </c>
       <c r="X173" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y173" s="7" t="s">
         <v>143</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="7" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="7" t="s">
         <v>144</v>
@@ -10775,7 +10775,7 @@
         <v>40.0</v>
       </c>
       <c r="X178" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y178" s="7" t="s">
         <v>141</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="7" t="s">
         <v>141</v>
@@ -10855,7 +10855,7 @@
         <v>42.0</v>
       </c>
       <c r="X180" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Y180" s="7" t="s">
         <v>140</v>
@@ -11055,7 +11055,7 @@
         <v>47.0</v>
       </c>
       <c r="X185" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Y185" s="7" t="s">
         <v>141</v>
@@ -11375,7 +11375,7 @@
         <v>55.0</v>
       </c>
       <c r="X193" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Y193" s="7" t="s">
         <v>141</v>
@@ -37456,7 +37456,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>7</v>
@@ -37468,10 +37468,10 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8">
         <v>27.5</v>
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="8">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="8">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="8">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="8">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" s="8">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="8">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="8">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" s="8">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="8">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="8">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C27" s="8">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C28" s="8">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C29" s="8">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C30" s="8">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C31" s="8">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C32" s="8">
         <v>5.5</v>
@@ -38551,7 +38551,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="8">
         <v>5.0</v>
@@ -38581,7 +38581,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" s="8">
         <v>4.5</v>
@@ -38611,7 +38611,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="8">
         <v>4.5</v>
@@ -38641,7 +38641,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="8">
         <v>4.0</v>
@@ -38671,7 +38671,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" s="8">
         <v>4.0</v>
@@ -38701,7 +38701,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8">
         <v>3.5</v>
@@ -38731,7 +38731,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C39" s="8">
         <v>3.5</v>
@@ -38761,7 +38761,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="8">
         <v>3.0</v>
@@ -38791,7 +38791,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="8">
         <v>3.0</v>
@@ -38821,7 +38821,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C42" s="8">
         <v>2.5</v>
@@ -38851,7 +38851,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="8">
         <v>2.5</v>
@@ -38881,7 +38881,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="8">
         <v>2.5</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C73" s="8">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
-    <t>Rank</t>
+    <t>PICK</t>
   </si>
   <si>
-    <t>PICK</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>PLAYER NAME</t>
@@ -98,6 +98,9 @@
     <t>Total Spent $</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Makai Lemon</t>
   </si>
   <si>
@@ -116,9 +119,6 @@
     <t>My Remaining</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
     <t>KC Concepcion</t>
   </si>
   <si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Jadarian Price</t>
+  </si>
+  <si>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Avg $ per Other Team</t>
@@ -140,6 +143,9 @@
     <t>Omar Cooper</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>CJ Allen</t>
   </si>
   <si>
@@ -149,13 +155,13 @@
     <t>Arvell Reese</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>Inflation Factor</t>
   </si>
   <si>
     <t>Ty Simpson</t>
+  </si>
+  <si>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Denzel Boston</t>
@@ -164,7 +170,7 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Caleb Downs</t>
@@ -179,10 +185,10 @@
     <t>Jacob Rodriguez</t>
   </si>
   <si>
-    <t>Round 4</t>
+    <t>Jonah Coleman</t>
   </si>
   <si>
-    <t>Jonah Coleman</t>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -198,9 +204,6 @@
   </si>
   <si>
     <t>Germie Bernard</t>
-  </si>
-  <si>
-    <t>Round 5</t>
   </si>
   <si>
     <t>Nicholas Singleton</t>
@@ -225,9 +228,6 @@
   </si>
   <si>
     <t>Max Klare</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Zachariah Branch</t>
@@ -347,13 +347,10 @@
     <t>Nate Boerkircher</t>
   </si>
   <si>
-    <t>Will Kacmarek</t>
+    <t>Standings</t>
   </si>
   <si>
-    <t>Noah Whittington</t>
-  </si>
-  <si>
-    <t>Standings</t>
+    <t>Will Kacmarek</t>
   </si>
   <si>
     <t>Owner</t>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Ed</t>
@@ -914,7 +914,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
@@ -1071,7 +1071,7 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P2" s="16">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="P3" s="16">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="P7" s="16">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S29" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="S29" s="8" t="s">
+      <c r="T29" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="T29" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="W29" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="W29" s="8" t="s">
+      <c r="X29" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="X29" s="8" t="s">
+      <c r="Y29" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="Y29" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P44" s="8" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -9212,7 +9212,7 @@
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
       <c r="W139" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="9" t="s">
         <v>138</v>
@@ -9375,7 +9375,7 @@
         <v>5.0</v>
       </c>
       <c r="X143" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y143" s="9" t="s">
         <v>141</v>
@@ -9455,7 +9455,7 @@
         <v>7.0</v>
       </c>
       <c r="X145" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y145" s="9" t="s">
         <v>143</v>
@@ -9495,7 +9495,7 @@
         <v>8.0</v>
       </c>
       <c r="X146" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y146" s="9" t="s">
         <v>144</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y147" s="9" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Y148" s="9" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y149" s="9" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Y156" s="9" t="s">
         <v>145</v>
@@ -10055,7 +10055,7 @@
         <v>22.0</v>
       </c>
       <c r="X160" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y160" s="9" t="s">
         <v>144</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="9" t="s">
         <v>142</v>
@@ -10135,7 +10135,7 @@
         <v>24.0</v>
       </c>
       <c r="X162" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y162" s="9" t="s">
         <v>141</v>
@@ -10175,7 +10175,7 @@
         <v>25.0</v>
       </c>
       <c r="X163" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y163" s="9" t="s">
         <v>140</v>
@@ -10215,7 +10215,7 @@
         <v>26.0</v>
       </c>
       <c r="X164" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y164" s="9" t="s">
         <v>140</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Y167" s="9" t="s">
         <v>143</v>
@@ -10375,7 +10375,7 @@
         <v>30.0</v>
       </c>
       <c r="X168" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y168" s="9" t="s">
         <v>141</v>
@@ -10695,7 +10695,7 @@
         <v>38.0</v>
       </c>
       <c r="X176" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y176" s="9" t="s">
         <v>141</v>
@@ -10735,7 +10735,7 @@
         <v>39.0</v>
       </c>
       <c r="X177" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y177" s="9" t="s">
         <v>144</v>
@@ -10815,7 +10815,7 @@
         <v>41.0</v>
       </c>
       <c r="X179" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y179" s="9" t="s">
         <v>141</v>
@@ -37444,7 +37444,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -37652,7 +37652,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="10">
         <v>76.0</v>
@@ -37677,7 +37677,7 @@
         <v/>
       </c>
       <c r="K6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" s="17">
         <f>L2-L5
@@ -37690,7 +37690,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="10">
         <v>66.5</v>
@@ -37715,7 +37715,7 @@
         <v/>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="17">
         <f>SUMIF($E$2:$E$500,TRUE,$D$2:$D$500)</f>
@@ -37727,7 +37727,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10">
         <v>57.5</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="10">
         <f>L4-L7
@@ -37828,7 +37828,7 @@
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="10">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37840,7 +37840,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="10">
         <v>43.0</v>
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37877,7 +37877,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="10">
         <v>39.0</v>
@@ -37907,7 +37907,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="10">
         <v>34.0</v>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L13" s="17">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" s="10">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="10">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="10">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="10">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" s="10">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="10">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="10">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="10">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" s="10">
         <v>13.5</v>
@@ -38245,7 +38245,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="10">
         <v>12.0</v>
@@ -38275,7 +38275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10">
         <v>11.0</v>
@@ -38305,7 +38305,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" s="10">
         <v>10.0</v>
@@ -38335,7 +38335,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="10">
         <v>9.5</v>
@@ -38365,7 +38365,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="10">
         <v>8.5</v>
@@ -38390,7 +38390,7 @@
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38401,7 +38401,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="10">
         <v>8.0</v>
@@ -38431,7 +38431,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="10">
         <v>7.0</v>
@@ -38461,7 +38461,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="10">
         <v>6.5</v>
@@ -38491,7 +38491,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="10">
         <v>6.0</v>
@@ -38521,7 +38521,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="10">
         <v>5.5</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C72" s="10">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C73" s="10">
         <v>1.0</v>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -14,13 +14,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
+    <t>PICK</t>
+  </si>
+  <si>
     <t>Rank</t>
   </si>
   <si>
-    <t>PICK</t>
+    <t>PLAYER NAME</t>
   </si>
   <si>
-    <t>PLAYER NAME</t>
+    <t>VALUE</t>
   </si>
   <si>
     <t>PreDraft$</t>
@@ -29,31 +32,28 @@
     <t>Final Price</t>
   </si>
   <si>
-    <t>VALUE</t>
+    <t>Mine?</t>
   </si>
   <si>
-    <t>Mine?</t>
+    <t>Decay</t>
   </si>
   <si>
     <t>Inflated Fair Price</t>
   </si>
   <si>
-    <t>Decay</t>
+    <t>New Values</t>
   </si>
   <si>
     <t>My Max Bid</t>
   </si>
   <si>
+    <t>Spine</t>
+  </si>
+  <si>
     <t>EnforceUpTo</t>
   </si>
   <si>
-    <t>New Values</t>
-  </si>
-  <si>
     <t>Value vs Fair</t>
-  </si>
-  <si>
-    <t>Spine</t>
   </si>
   <si>
     <t>Settings</t>
@@ -110,6 +110,9 @@
     <t>My Spent</t>
   </si>
   <si>
+    <t>Round 1</t>
+  </si>
+  <si>
     <t>Sonny Styles</t>
   </si>
   <si>
@@ -126,9 +129,6 @@
   </si>
   <si>
     <t>Avg $ per Other Team</t>
-  </si>
-  <si>
-    <t>Round 1</t>
   </si>
   <si>
     <t>Eli Stowers</t>
@@ -149,6 +149,9 @@
     <t>Arvell Reese</t>
   </si>
   <si>
+    <t>Round 2</t>
+  </si>
+  <si>
     <t>Inflation Factor</t>
   </si>
   <si>
@@ -161,13 +164,16 @@
     <t>Aggression</t>
   </si>
   <si>
+    <t>Round 3</t>
+  </si>
+  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
-    <t>Round 2</t>
+    <t>David Bailey</t>
   </si>
   <si>
-    <t>David Bailey</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>League Spent %</t>
@@ -177,6 +183,9 @@
   </si>
   <si>
     <t>Jonah Coleman</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>Jake Golday</t>
@@ -197,10 +206,10 @@
     <t>Nicholas Singleton</t>
   </si>
   <si>
-    <t>Mike Washington</t>
+    <t>Round 6</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Mike Washington</t>
   </si>
   <si>
     <t>Enforce % of Fair</t>
@@ -227,9 +236,6 @@
     <t>De'Zhaun Stribling</t>
   </si>
   <si>
-    <t>Round 4</t>
-  </si>
-  <si>
     <t>Malachi Fields</t>
   </si>
   <si>
@@ -251,9 +257,6 @@
     <t>A.J. Haulcy</t>
   </si>
   <si>
-    <t>Round 5</t>
-  </si>
-  <si>
     <t>Josiah Trotter</t>
   </si>
   <si>
@@ -270,9 +273,6 @@
   </si>
   <si>
     <t>Michael Trigg</t>
-  </si>
-  <si>
-    <t>Round 6</t>
   </si>
   <si>
     <t>Demond Claiborne</t>
@@ -630,10 +630,10 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -651,11 +651,11 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -914,19 +914,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -934,7 +934,7 @@
       <c r="G1" s="6">
         <v>2024.0</v>
       </c>
-      <c r="H1" s="8">
+      <c r="H1" s="7">
         <v>2026.0</v>
       </c>
       <c r="I1" s="10" t="s">
@@ -1006,7 +1006,7 @@
       <c r="B2" s="5">
         <v>7580.0</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="15">
         <f t="shared" ref="C2:C73" si="2">1 + --(INT((ROW()-ROW($B$2))/12)=4)
   + (1200-84) * (
       0.6 *
@@ -1026,7 +1026,7 @@
 </f>
         <v>133.317836</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="15">
         <f t="shared" ref="D2:D73" si="3">( K2
    + IF(
        ROW()-ROW($K$2) &lt; $M$1,
@@ -1038,29 +1038,29 @@
 </f>
         <v>134.5</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <f t="shared" ref="E2:E73" si="4">(MEDIAN(F2:H2)+AVERAGE(F2:H2))/2
 </f>
         <v>126.4166667</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>125.5</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="15">
         <v>122.5</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>134.0</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="15">
         <f t="shared" ref="I2:I73" si="5">ROUNDDOWN(C2*2,0)</f>
         <v>266</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="15">
         <f t="shared" ref="J2:J73" si="6">C2*2 - I2</f>
         <v>0.6356720614</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="15">
         <f>I2 + --(RANK(J2,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73))</f>
         <v>267</v>
       </c>
@@ -1071,57 +1071,57 @@
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="16">
+        <v>32</v>
+      </c>
+      <c r="P2" s="15">
         <f t="shared" ref="P2:AA2" si="1">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>134.5</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="15">
         <f t="shared" si="1"/>
         <v>100.5</v>
       </c>
-      <c r="R2" s="16">
+      <c r="R2" s="15">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="S2" s="16">
+      <c r="S2" s="15">
         <f t="shared" si="1"/>
         <v>80.5</v>
       </c>
-      <c r="T2" s="16">
+      <c r="T2" s="15">
         <f t="shared" si="1"/>
         <v>75.5</v>
       </c>
-      <c r="U2" s="16">
+      <c r="U2" s="15">
         <f t="shared" si="1"/>
         <v>68.5</v>
       </c>
-      <c r="V2" s="16">
+      <c r="V2" s="15">
         <f t="shared" si="1"/>
         <v>54.5</v>
       </c>
-      <c r="W2" s="16">
+      <c r="W2" s="15">
         <f t="shared" si="1"/>
         <v>53.5</v>
       </c>
-      <c r="X2" s="16">
+      <c r="X2" s="15">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="Y2" s="16">
+      <c r="Y2" s="15">
         <f t="shared" si="1"/>
         <v>44.5</v>
       </c>
-      <c r="Z2" s="16">
+      <c r="Z2" s="15">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="AA2" s="16">
+      <c r="AA2" s="15">
         <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
-      <c r="AB2" s="16">
+      <c r="AB2" s="15">
         <f t="shared" ref="AB2:AB7" si="9">SUM(P2:AA2)</f>
         <v>827.5</v>
       </c>
@@ -1135,36 +1135,36 @@
       <c r="B3" s="5">
         <v>5598.5</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <f t="shared" si="2"/>
         <v>99.38361855</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <f t="shared" si="3"/>
         <v>100.5</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <f t="shared" si="4"/>
         <v>103.0833333</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <v>95.0</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <v>113.5</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>102.5</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <f t="shared" si="5"/>
         <v>198</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <f t="shared" si="6"/>
         <v>0.7672370964</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="15">
         <f t="shared" ref="K3:K73" si="10">MIN(
   I3 + --(RANK(J3,$J$2:$J$73,0) &lt;= 1200*2 - SUM($I$2:$I$73)),
   IF(INT((ROW()-ROW($C$2))/12)=4, 4, IF(INT((ROW()-ROW($C$2))/12)=5, 2, 10^9)),
@@ -1180,57 +1180,57 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="16">
+        <v>45</v>
+      </c>
+      <c r="P3" s="15">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>29.5</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <f t="shared" si="8"/>
         <v>28.5</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="15">
         <f t="shared" si="8"/>
         <v>26.5</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="15">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="15">
         <f t="shared" si="8"/>
         <v>21.5</v>
       </c>
-      <c r="U3" s="16">
+      <c r="U3" s="15">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V3" s="16">
+      <c r="V3" s="15">
         <f t="shared" si="8"/>
         <v>17.5</v>
       </c>
-      <c r="W3" s="16">
+      <c r="W3" s="15">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="X3" s="16">
+      <c r="X3" s="15">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="Y3" s="16">
+      <c r="Y3" s="15">
         <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
-      <c r="Z3" s="16">
+      <c r="Z3" s="15">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="AA3" s="16">
+      <c r="AA3" s="15">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="AB3" s="16">
+      <c r="AB3" s="15">
         <f t="shared" si="9"/>
         <v>231</v>
       </c>
@@ -1244,36 +1244,36 @@
       <c r="B4" s="5">
         <v>5649.0</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <f t="shared" si="2"/>
         <v>91.80264821</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="15">
         <f t="shared" si="4"/>
         <v>90.66666667</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <v>85.5</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <v>91.5</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="15">
         <v>92.5</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="15">
         <f t="shared" si="5"/>
         <v>183</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="15">
         <f t="shared" si="6"/>
         <v>0.6052964259</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="15">
         <f t="shared" si="10"/>
         <v>184</v>
       </c>
@@ -1284,57 +1284,57 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="P4" s="16">
+        <v>50</v>
+      </c>
+      <c r="P4" s="15">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>9.5</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="15">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="15">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="S4" s="16">
+      <c r="S4" s="15">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="T4" s="16">
+      <c r="T4" s="15">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="U4" s="16">
+      <c r="U4" s="15">
         <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
-      <c r="V4" s="16">
+      <c r="V4" s="15">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="W4" s="16">
+      <c r="W4" s="15">
         <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
-      <c r="X4" s="16">
+      <c r="X4" s="15">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="Y4" s="16">
+      <c r="Y4" s="15">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="Z4" s="16">
+      <c r="Z4" s="15">
         <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
-      <c r="AA4" s="16">
+      <c r="AA4" s="15">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="AB4" s="16">
+      <c r="AB4" s="15">
         <f t="shared" si="9"/>
         <v>74</v>
       </c>
@@ -1348,36 +1348,36 @@
       <c r="B5" s="5">
         <v>5074.5</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <f t="shared" si="2"/>
         <v>79.37165519</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <f t="shared" si="3"/>
         <v>80.5</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <f t="shared" si="4"/>
         <v>80.66666667</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>77.5</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>84.5</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>80.5</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="15">
         <f t="shared" si="5"/>
         <v>158</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="15">
         <f t="shared" si="6"/>
         <v>0.7433103774</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="15">
         <f t="shared" si="10"/>
         <v>159</v>
       </c>
@@ -1388,57 +1388,57 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="P5" s="16">
+        <v>53</v>
+      </c>
+      <c r="P5" s="15">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>3.5</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="15">
         <f t="shared" si="12"/>
         <v>3.5</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="S5" s="16">
+      <c r="S5" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="T5" s="16">
+      <c r="T5" s="15">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="U5" s="16">
+      <c r="U5" s="15">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="V5" s="16">
+      <c r="V5" s="15">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="W5" s="16">
+      <c r="W5" s="15">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="X5" s="16">
+      <c r="X5" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="Y5" s="16">
+      <c r="Y5" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="Z5" s="16">
+      <c r="Z5" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AA5" s="16">
+      <c r="AA5" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AB5" s="16">
+      <c r="AB5" s="15">
         <f t="shared" si="9"/>
         <v>31.5</v>
       </c>
@@ -1452,36 +1452,36 @@
       <c r="B6" s="5">
         <v>5076.0</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="15">
         <f t="shared" si="2"/>
         <v>74.3655612</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <f t="shared" si="3"/>
         <v>75.5</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="15">
         <f t="shared" si="4"/>
         <v>75.08333333</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>73.0</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>79.5</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>74.5</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="15">
         <f t="shared" si="5"/>
         <v>148</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <f t="shared" si="6"/>
         <v>0.7311223994</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="15">
         <f t="shared" si="10"/>
         <v>149</v>
       </c>
@@ -1492,57 +1492,57 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="16">
+        <v>57</v>
+      </c>
+      <c r="P6" s="15">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="U6" s="16">
+      <c r="U6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="V6" s="16">
+      <c r="V6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="W6" s="16">
+      <c r="W6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="Y6" s="16">
+      <c r="Y6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="Z6" s="16">
+      <c r="Z6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="AA6" s="16">
+      <c r="AA6" s="15">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="AB6" s="16">
+      <c r="AB6" s="15">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
@@ -1556,36 +1556,36 @@
       <c r="B7" s="5">
         <v>4965.0</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <f t="shared" si="2"/>
         <v>67.755402</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <f t="shared" si="3"/>
         <v>68.5</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <f t="shared" si="4"/>
         <v>67.58333333</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>67.5</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>67.5</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>68.0</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <f t="shared" si="5"/>
         <v>135</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <f t="shared" si="6"/>
         <v>0.5108040066</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <f t="shared" si="10"/>
         <v>136</v>
       </c>
@@ -1596,57 +1596,57 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="P7" s="16">
+        <v>64</v>
+      </c>
+      <c r="P7" s="15">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
         <v>1</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="S7" s="16">
+      <c r="S7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="T7" s="16">
+      <c r="T7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="U7" s="16">
+      <c r="U7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="V7" s="16">
+      <c r="V7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="W7" s="16">
+      <c r="W7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Y7" s="16">
+      <c r="Y7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Z7" s="16">
+      <c r="Z7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AA7" s="16">
+      <c r="AA7" s="15">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="AB7" s="16">
+      <c r="AB7" s="15">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
@@ -1660,36 +1660,36 @@
       <c r="B8" s="5">
         <v>4014.5</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <f t="shared" si="2"/>
         <v>54.14386456</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <f t="shared" si="3"/>
         <v>54.5</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>62.0</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <v>57.5</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>56.0</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <f t="shared" si="5"/>
         <v>108</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <f t="shared" si="6"/>
         <v>0.2877291223</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <f t="shared" si="10"/>
         <v>108</v>
       </c>
@@ -1700,55 +1700,55 @@
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="16">
+      <c r="P8" s="15">
         <f t="shared" ref="P8:AB8" si="15">SUM(P2:P7)</f>
         <v>180</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="15">
         <f t="shared" si="15"/>
         <v>144.5</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="15">
         <f t="shared" si="15"/>
         <v>132.5</v>
       </c>
-      <c r="S8" s="16">
+      <c r="S8" s="15">
         <f t="shared" si="15"/>
         <v>117.5</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="15">
         <f t="shared" si="15"/>
         <v>109.5</v>
       </c>
-      <c r="U8" s="16">
+      <c r="U8" s="15">
         <f t="shared" si="15"/>
         <v>99.5</v>
       </c>
-      <c r="V8" s="16">
+      <c r="V8" s="15">
         <f t="shared" si="15"/>
         <v>83</v>
       </c>
-      <c r="W8" s="16">
+      <c r="W8" s="15">
         <f t="shared" si="15"/>
         <v>80.5</v>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="15">
         <f t="shared" si="15"/>
         <v>69.5</v>
       </c>
-      <c r="Y8" s="16">
+      <c r="Y8" s="15">
         <f t="shared" si="15"/>
         <v>67.5</v>
       </c>
-      <c r="Z8" s="16">
+      <c r="Z8" s="15">
         <f t="shared" si="15"/>
         <v>61.5</v>
       </c>
-      <c r="AA8" s="16">
+      <c r="AA8" s="15">
         <f t="shared" si="15"/>
         <v>54.5</v>
       </c>
-      <c r="AB8" s="16">
+      <c r="AB8" s="15">
         <f t="shared" si="15"/>
         <v>1200</v>
       </c>
@@ -1762,36 +1762,36 @@
       <c r="B9" s="5">
         <v>4308.0</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <f t="shared" si="2"/>
         <v>52.77059949</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <f t="shared" si="3"/>
         <v>53.5</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <f t="shared" si="4"/>
         <v>54.33333333</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>57.0</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <v>53.0</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>54.0</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <f t="shared" si="5"/>
         <v>105</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <f t="shared" si="6"/>
         <v>0.5411989831</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="15">
         <f t="shared" si="10"/>
         <v>106</v>
       </c>
@@ -1825,36 +1825,36 @@
       <c r="B10" s="5">
         <v>3869.0</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <f t="shared" si="2"/>
         <v>45.5279227</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <f t="shared" si="4"/>
         <v>48.58333333</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>52.5</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <v>48.0</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <v>47.0</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="15">
         <f t="shared" si="6"/>
         <v>0.05584540002</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <f t="shared" si="10"/>
         <v>91</v>
       </c>
@@ -1865,8 +1865,8 @@
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
@@ -1888,36 +1888,36 @@
       <c r="B11" s="5">
         <v>4169.0</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <f t="shared" si="2"/>
         <v>43.91121089</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <f t="shared" si="3"/>
         <v>44.5</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <f t="shared" si="4"/>
         <v>44.25</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>45.0</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>42.5</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>44.5</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="15">
         <f t="shared" si="6"/>
         <v>0.8224217757</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="15">
         <f t="shared" si="10"/>
         <v>88</v>
       </c>
@@ -1928,8 +1928,8 @@
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="4"/>
@@ -1951,36 +1951,36 @@
       <c r="B12" s="5">
         <v>4164.0</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <f t="shared" si="2"/>
         <v>40.67669146</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <f t="shared" si="4"/>
         <v>40.66666667</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>41.0</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <v>39.0</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>41.0</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="15">
         <f t="shared" si="6"/>
         <v>0.3533829233</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="15">
         <f t="shared" si="10"/>
         <v>81</v>
       </c>
@@ -1991,8 +1991,8 @@
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="4"/>
@@ -2014,36 +2014,36 @@
       <c r="B13" s="5">
         <v>3809.5</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <f t="shared" si="2"/>
         <v>35.11775951</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <f t="shared" si="3"/>
         <v>35.5</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <f t="shared" si="4"/>
         <v>35.66666667</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>37.5</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>34.5</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>35.5</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="15">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="15">
         <f t="shared" si="6"/>
         <v>0.2355190156</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="15">
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
@@ -2054,8 +2054,8 @@
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="4"/>
@@ -2077,36 +2077,36 @@
       <c r="B14" s="5">
         <v>3397.5</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <f t="shared" si="2"/>
         <v>29.5432517</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <f t="shared" si="3"/>
         <v>29.5</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <f t="shared" si="4"/>
         <v>30.41666667</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>33.0</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>30.0</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>29.5</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="15">
         <f t="shared" si="6"/>
         <v>0.08650340414</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="15">
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
@@ -2117,8 +2117,8 @@
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
       <c r="T14" s="4"/>
@@ -2140,36 +2140,36 @@
       <c r="B15" s="5">
         <v>3611.0</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="15">
         <f t="shared" si="2"/>
         <v>28.42496232</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <f t="shared" si="3"/>
         <v>28.5</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <f t="shared" si="4"/>
         <v>28.16666667</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>30.0</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <v>27.0</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="15">
         <v>28.0</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="15">
         <f t="shared" si="5"/>
         <v>56</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="15">
         <f t="shared" si="6"/>
         <v>0.8499246445</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="15">
         <f t="shared" si="10"/>
         <v>57</v>
       </c>
@@ -2180,8 +2180,8 @@
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
@@ -2203,36 +2203,36 @@
       <c r="B16" s="5">
         <v>3605.0</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <f t="shared" si="2"/>
         <v>26.33603784</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <f t="shared" si="3"/>
         <v>26.5</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>27.0</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="15">
         <v>25.0</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <v>26.0</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="15">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="15">
         <f t="shared" si="6"/>
         <v>0.6720756822</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="15">
         <f t="shared" si="10"/>
         <v>53</v>
       </c>
@@ -2243,8 +2243,8 @@
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
       <c r="O16" s="12"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
@@ -2266,36 +2266,36 @@
       <c r="B17" s="5">
         <v>3603.0</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="15">
         <f t="shared" si="2"/>
         <v>24.0808176</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="15">
         <f t="shared" si="4"/>
         <v>23.16666667</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>23.0</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="15">
         <v>23.0</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="15">
         <v>24.0</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="15">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="15">
         <f t="shared" si="6"/>
         <v>0.1616351939</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="15">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
@@ -2329,36 +2329,36 @@
       <c r="B18" s="5">
         <v>3440.5</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <f t="shared" si="2"/>
         <v>21.41140042</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <f t="shared" si="3"/>
         <v>21.5</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <f t="shared" si="4"/>
         <v>20.58333333</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>20.5</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <v>20.5</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>21.0</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="15">
         <f t="shared" si="6"/>
         <v>0.822800843</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="15">
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
@@ -2392,36 +2392,36 @@
       <c r="B19" s="5">
         <v>3220.0</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="15">
         <f t="shared" si="2"/>
         <v>19.1008101</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="15">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>19.0</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <v>19.0</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="15">
         <v>19.0</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="15">
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="15">
         <f t="shared" si="6"/>
         <v>0.2016202047</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="15">
         <f t="shared" si="10"/>
         <v>38</v>
       </c>
@@ -2455,36 +2455,36 @@
       <c r="B20" s="5">
         <v>3200.0</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <f t="shared" si="2"/>
         <v>17.59752889</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <f t="shared" si="4"/>
         <v>17.41666667</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>17.5</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="15">
         <v>17.0</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <v>17.5</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="15">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="15">
         <f t="shared" si="6"/>
         <v>0.1950577773</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="15">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
@@ -2518,36 +2518,36 @@
       <c r="B21" s="5">
         <v>3127.0</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="15">
         <f t="shared" si="2"/>
         <v>16.03902814</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="15">
         <f t="shared" si="4"/>
         <v>15.91666667</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>16.0</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <v>15.5</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="15">
         <v>16.0</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="15">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="15">
         <f t="shared" si="6"/>
         <v>0.07805628365</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="15">
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
@@ -2581,36 +2581,36 @@
       <c r="B22" s="5">
         <v>2943.0</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="15">
         <f t="shared" si="2"/>
         <v>14.10063305</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="15">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="15">
         <v>14.0</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="15">
         <v>14.0</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="15">
         <v>14.0</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="15">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="15">
         <f t="shared" si="6"/>
         <v>0.2012660994</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="15">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
@@ -2644,36 +2644,36 @@
       <c r="B23" s="5">
         <v>3020.0</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <f t="shared" si="2"/>
         <v>13.23457043</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <f t="shared" si="3"/>
         <v>13.5</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="15">
         <f t="shared" si="4"/>
         <v>12.83333333</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="15">
         <v>13.0</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <v>12.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="15">
         <v>13.0</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="15">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="15">
         <f t="shared" si="6"/>
         <v>0.4691408519</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="15">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
@@ -2707,36 +2707,36 @@
       <c r="B24" s="5">
         <v>2537.5</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <f t="shared" si="2"/>
         <v>10.89260152</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <f t="shared" si="4"/>
         <v>11.16666667</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>12.0</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <v>11.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <v>11.0</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="15">
         <f t="shared" si="6"/>
         <v>0.7852030339</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="15">
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
@@ -2770,36 +2770,36 @@
       <c r="B25" s="5">
         <v>2406.0</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="15">
         <f t="shared" si="2"/>
         <v>9.905835639</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="15">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="15">
         <f t="shared" si="4"/>
         <v>10.5</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <v>11.0</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <v>10.5</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <v>10.0</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="15">
         <f t="shared" si="6"/>
         <v>0.8116712781</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="15">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
@@ -2833,36 +2833,36 @@
       <c r="B26" s="5">
         <v>2671.0</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="15">
         <f t="shared" si="2"/>
         <v>9.676955496</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="15">
         <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="15">
         <f t="shared" si="4"/>
         <v>9.583333333</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="15">
         <v>10.0</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="15">
         <v>9.5</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="15">
         <v>9.5</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="15">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="15">
         <f t="shared" si="6"/>
         <v>0.3539109913</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="15">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
@@ -2896,36 +2896,36 @@
       <c r="B27" s="5">
         <v>2628.0</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="15">
         <f t="shared" si="2"/>
         <v>8.968058117</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="15">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="15">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="15">
         <v>9.0</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="15">
         <v>9.0</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="15">
         <v>9.0</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="15">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="15">
         <f t="shared" si="6"/>
         <v>0.9361162335</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="15">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
@@ -2959,36 +2959,36 @@
       <c r="B28" s="5">
         <v>1998.5</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="15">
         <f t="shared" si="2"/>
         <v>7.113608108</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="15">
         <f t="shared" si="4"/>
         <v>7.916666667</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="15">
         <v>8.5</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="15">
         <v>8.0</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="15">
         <v>7.0</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="15">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="15">
         <f t="shared" si="6"/>
         <v>0.227216216</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="15">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
@@ -3022,36 +3022,36 @@
       <c r="B29" s="5">
         <v>2202.5</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="15">
         <f t="shared" si="2"/>
         <v>6.977042416</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <f t="shared" si="4"/>
         <v>7.416666667</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="15">
         <v>7.5</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="15">
         <v>7.5</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="15">
         <v>7.0</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="15">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="15">
         <f t="shared" si="6"/>
         <v>0.9540848326</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="15">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
@@ -3103,36 +3103,36 @@
       <c r="B30" s="5">
         <v>2252.5</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="15">
         <f t="shared" si="2"/>
         <v>6.589638694</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="15">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="15">
         <f t="shared" si="4"/>
         <v>6.916666667</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="15">
         <v>7.0</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="15">
         <v>7.0</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="15">
         <v>6.5</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="15">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="15">
         <f t="shared" si="6"/>
         <v>0.1792773885</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="15">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
@@ -3160,7 +3160,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
-      <c r="X30" s="7"/>
+      <c r="X30" s="8"/>
       <c r="Y30" s="12" t="str">
         <f t="shared" ref="Y30:Y81" si="17">TEXT(V30,"0")&amp;"|"&amp;TRIM(W30)</f>
         <v>0|</v>
@@ -3178,36 +3178,36 @@
       <c r="B31" s="5">
         <v>2458.0</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="15">
         <f t="shared" si="2"/>
         <v>6.450624078</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="15">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="15">
         <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="15">
         <v>6.5</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="15">
         <v>6.5</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="15">
         <v>6.5</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="15">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="15">
         <f t="shared" si="6"/>
         <v>0.9012481555</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="15">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
@@ -3233,9 +3233,9 @@
         <v>Brent</v>
       </c>
       <c r="U31" s="12"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
       <c r="Y31" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3253,36 +3253,36 @@
       <c r="B32" s="5">
         <v>2332.5</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="15">
         <f t="shared" si="2"/>
         <v>5.683565019</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="15">
         <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="15">
         <f t="shared" si="4"/>
         <v>5.583333333</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="15">
         <v>6.0</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="15">
         <v>5.5</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="15">
         <v>5.5</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="15">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="15">
         <f t="shared" si="6"/>
         <v>0.3671300387</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="15">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
@@ -3308,9 +3308,9 @@
         <v>Joey</v>
       </c>
       <c r="U32" s="12"/>
-      <c r="V32" s="8"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="8"/>
+      <c r="X32" s="8"/>
       <c r="Y32" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3328,36 +3328,36 @@
       <c r="B33" s="5">
         <v>2331.0</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="15">
         <f t="shared" si="2"/>
         <v>5.264829603</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="15">
         <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="15">
         <f t="shared" si="4"/>
         <v>5.083333333</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="15">
         <v>5.5</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="15">
         <v>5.0</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="15">
         <v>5.0</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="15">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="15">
         <f t="shared" si="6"/>
         <v>0.5296592069</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="15">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
@@ -3383,9 +3383,9 @@
         <v>MaKayla</v>
       </c>
       <c r="U33" s="12"/>
-      <c r="V33" s="8"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8"/>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3403,36 +3403,36 @@
       <c r="B34" s="5">
         <v>1991.0</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="15">
         <f t="shared" si="2"/>
         <v>4.508206737</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="15">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="15">
         <f t="shared" si="4"/>
         <v>4.583333333</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="15">
         <v>5.0</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="15">
         <v>4.5</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="15">
         <v>4.5</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="15">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="15">
         <f t="shared" si="6"/>
         <v>0.01641347439</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="15">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
@@ -3458,9 +3458,9 @@
         <v>Ty</v>
       </c>
       <c r="U34" s="12"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
       <c r="Y34" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3478,36 +3478,36 @@
       <c r="B35" s="5">
         <v>2180.5</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="15">
         <f t="shared" si="2"/>
         <v>4.49906056</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="15">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <f t="shared" si="4"/>
         <v>4.5</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="15">
         <v>4.5</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="15">
         <v>4.5</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="15">
         <v>4.5</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="15">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="15">
         <f t="shared" si="6"/>
         <v>0.9981211193</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="15">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
@@ -3533,9 +3533,9 @@
         <v>Kich</v>
       </c>
       <c r="U35" s="12"/>
-      <c r="V35" s="8"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8"/>
       <c r="Y35" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3553,36 +3553,36 @@
       <c r="B36" s="5">
         <v>2432.0</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="15">
         <f t="shared" si="2"/>
         <v>4.397062142</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="15">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="15">
         <f t="shared" si="4"/>
         <v>4.083333333</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>4.0</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="15">
         <v>4.0</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="15">
         <v>4.5</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="15">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="15">
         <f t="shared" si="6"/>
         <v>0.7941242844</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="15">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
@@ -3608,9 +3608,9 @@
         <v>Eric</v>
       </c>
       <c r="U36" s="12"/>
-      <c r="V36" s="8"/>
-      <c r="W36" s="7"/>
-      <c r="X36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
       <c r="Y36" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3628,36 +3628,36 @@
       <c r="B37" s="5">
         <v>2014.0</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="15">
         <f t="shared" si="2"/>
         <v>3.85271165</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="15">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="15">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="15">
         <v>4.0</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="15">
         <v>4.0</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="15">
         <v>4.0</v>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="15">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="15">
         <f t="shared" si="6"/>
         <v>0.7054232997</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="15">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
@@ -3683,9 +3683,9 @@
         <v>Collin</v>
       </c>
       <c r="U37" s="12"/>
-      <c r="V37" s="8"/>
-      <c r="W37" s="7"/>
-      <c r="X37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="8"/>
+      <c r="X37" s="8"/>
       <c r="Y37" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3703,36 +3703,36 @@
       <c r="B38" s="5">
         <v>1907.0</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="15">
         <f t="shared" si="2"/>
         <v>3.445464994</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="15">
         <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="15">
         <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="15">
         <v>3.5</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="15">
         <v>3.5</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="15">
         <v>3.5</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="15">
         <f t="shared" si="6"/>
         <v>0.8909299877</v>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="15">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
@@ -3758,9 +3758,9 @@
         <v>Roy</v>
       </c>
       <c r="U38" s="12"/>
-      <c r="V38" s="8"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="8"/>
+      <c r="X38" s="8"/>
       <c r="Y38" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3778,36 +3778,36 @@
       <c r="B39" s="5">
         <v>2089.0</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="15">
         <f t="shared" si="2"/>
         <v>3.462208651</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="15">
         <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="15">
         <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="15">
         <v>3.5</v>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="15">
         <v>3.5</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="15">
         <v>3.5</v>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="15">
         <f t="shared" si="6"/>
         <v>0.9244173029</v>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="15">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
@@ -3833,9 +3833,9 @@
         <v>Jason</v>
       </c>
       <c r="U39" s="12"/>
-      <c r="V39" s="8"/>
-      <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="8"/>
+      <c r="X39" s="8"/>
       <c r="Y39" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3853,36 +3853,36 @@
       <c r="B40" s="5">
         <v>2080.0</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="15">
         <f t="shared" si="2"/>
         <v>3.145261583</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="15">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="15">
         <v>3.0</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="15">
         <v>3.0</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="15">
         <v>3.0</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="15">
         <f t="shared" si="6"/>
         <v>0.2905231659</v>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="15">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
@@ -3908,9 +3908,9 @@
         <v>Blaine</v>
       </c>
       <c r="U40" s="12"/>
-      <c r="V40" s="8"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
       <c r="Y40" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -3928,36 +3928,36 @@
       <c r="B41" s="5">
         <v>2063.0</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="15">
         <f t="shared" si="2"/>
         <v>3.031451302</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="15">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="15">
         <v>3.0</v>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="15">
         <v>3.0</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="15">
         <v>3.0</v>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="15">
         <f t="shared" si="6"/>
         <v>0.06290260374</v>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="15">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
@@ -3983,9 +3983,9 @@
         <v>Joel</v>
       </c>
       <c r="U41" s="12"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="7"/>
-      <c r="X41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="8"/>
+      <c r="X41" s="8"/>
       <c r="Y41" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4003,36 +4003,36 @@
       <c r="B42" s="23">
         <v>2048.0</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="15">
         <f t="shared" si="2"/>
         <v>2.89515157</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="15">
         <f t="shared" si="4"/>
         <v>2.916666667</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="15">
         <v>3.0</v>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="15">
         <v>2.5</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="15">
         <v>3.0</v>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="15">
         <f t="shared" si="6"/>
         <v>0.7903031391</v>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="15">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
@@ -4049,9 +4049,9 @@
       <c r="S42" s="12"/>
       <c r="T42" s="12"/>
       <c r="U42" s="12"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="8"/>
+      <c r="X42" s="8"/>
       <c r="Y42" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4069,36 +4069,36 @@
       <c r="B43" s="5">
         <v>1539.5</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="15">
         <f t="shared" si="2"/>
         <v>2.382690198</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="15">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="15">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="15">
         <v>2.5</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="15">
         <v>2.5</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="15">
         <v>2.5</v>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="15">
         <f t="shared" si="6"/>
         <v>0.7653803953</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="15">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
@@ -4115,9 +4115,9 @@
       <c r="S43" s="12"/>
       <c r="T43" s="12"/>
       <c r="U43" s="12"/>
-      <c r="V43" s="8"/>
-      <c r="W43" s="7"/>
-      <c r="X43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="8"/>
+      <c r="X43" s="8"/>
       <c r="Y43" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4135,36 +4135,36 @@
       <c r="B44" s="5">
         <v>1956.0</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="15">
         <f t="shared" si="2"/>
         <v>2.518944323</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="15">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="15">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="15">
         <v>2.5</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="15">
         <v>2.5</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="15">
         <v>2.5</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="15">
         <f t="shared" si="6"/>
         <v>0.03788864638</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="15">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
@@ -4189,9 +4189,9 @@
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
-      <c r="V44" s="8"/>
-      <c r="W44" s="7"/>
-      <c r="X44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="8"/>
+      <c r="X44" s="8"/>
       <c r="Y44" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4209,36 +4209,36 @@
       <c r="B45" s="5">
         <v>1953.0</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="15">
         <f t="shared" si="2"/>
         <v>2.446750784</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="15">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="15">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="15">
         <v>2.5</v>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="15">
         <v>2.5</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="15">
         <v>2.5</v>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="15">
         <f t="shared" si="6"/>
         <v>0.893501569</v>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="15">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
@@ -4257,7 +4257,7 @@
 </f>
         <v>1</v>
       </c>
-      <c r="Q45" s="16">
+      <c r="Q45" s="15">
         <f t="shared" ref="Q45:Q116" si="20">INDEX($P$2:$AA$7,O45,P45)*$AD$1</f>
         <v>134.5</v>
       </c>
@@ -4279,9 +4279,9 @@
       <c r="S45" s="12"/>
       <c r="T45" s="12"/>
       <c r="U45" s="12"/>
-      <c r="V45" s="8"/>
-      <c r="W45" s="7"/>
-      <c r="X45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="8"/>
+      <c r="X45" s="8"/>
       <c r="Y45" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4299,36 +4299,36 @@
       <c r="B46" s="5">
         <v>1945.0</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="15">
         <f t="shared" si="2"/>
         <v>2.179728789</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="15">
         <v>2.0</v>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="15">
         <v>2.0</v>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="15">
         <v>2.0</v>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J46" s="16">
+      <c r="J46" s="15">
         <f t="shared" si="6"/>
         <v>0.3594575775</v>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4346,7 +4346,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q46" s="16">
+      <c r="Q46" s="15">
         <f t="shared" si="20"/>
         <v>100.5</v>
       </c>
@@ -4357,9 +4357,9 @@
       <c r="S46" s="12"/>
       <c r="T46" s="12"/>
       <c r="U46" s="12"/>
-      <c r="V46" s="8"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="8"/>
+      <c r="X46" s="8"/>
       <c r="Y46" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4377,36 +4377,36 @@
       <c r="B47" s="5">
         <v>1938.0</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="15">
         <f t="shared" si="2"/>
         <v>2.117023349</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="15">
         <v>2.0</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="15">
         <v>2.0</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="15">
         <v>2.0</v>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="15">
         <f t="shared" si="6"/>
         <v>0.2340466986</v>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4424,7 +4424,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q47" s="16">
+      <c r="Q47" s="15">
         <f t="shared" si="20"/>
         <v>93</v>
       </c>
@@ -4435,9 +4435,9 @@
       <c r="S47" s="12"/>
       <c r="T47" s="12"/>
       <c r="U47" s="12"/>
-      <c r="V47" s="8"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="8"/>
+      <c r="X47" s="8"/>
       <c r="Y47" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4455,36 +4455,36 @@
       <c r="B48" s="5">
         <v>1926.0</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="15">
         <f t="shared" si="2"/>
         <v>2.057608058</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="15">
         <v>2.0</v>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="15">
         <v>2.0</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="15">
         <v>2.0</v>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="15">
         <f t="shared" si="6"/>
         <v>0.1152161166</v>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4502,7 +4502,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q48" s="16">
+      <c r="Q48" s="15">
         <f t="shared" si="20"/>
         <v>80.5</v>
       </c>
@@ -4513,9 +4513,9 @@
       <c r="S48" s="12"/>
       <c r="T48" s="12"/>
       <c r="U48" s="12"/>
-      <c r="V48" s="8"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="8"/>
+      <c r="X48" s="8"/>
       <c r="Y48" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4533,36 +4533,36 @@
       <c r="B49" s="5">
         <v>1917.0</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="15">
         <f t="shared" si="2"/>
         <v>2.004014444</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="15">
         <v>2.0</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="15">
         <v>2.0</v>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="15">
         <v>2.0</v>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="15">
         <f t="shared" si="6"/>
         <v>0.008028888223</v>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4580,7 +4580,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q49" s="16">
+      <c r="Q49" s="15">
         <f t="shared" si="20"/>
         <v>75.5</v>
       </c>
@@ -4591,9 +4591,9 @@
       <c r="S49" s="12"/>
       <c r="T49" s="12"/>
       <c r="U49" s="12"/>
-      <c r="V49" s="8"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="8"/>
+      <c r="X49" s="8"/>
       <c r="Y49" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4611,36 +4611,36 @@
       <c r="B50" s="5">
         <v>1917.0</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="15">
         <f t="shared" si="2"/>
         <v>2.957381425</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="15">
         <v>2.0</v>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="15">
         <v>2.0</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="15">
         <v>2.0</v>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="15">
         <f t="shared" si="6"/>
         <v>0.9147628497</v>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4658,7 +4658,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q50" s="16">
+      <c r="Q50" s="15">
         <f t="shared" si="20"/>
         <v>68.5</v>
       </c>
@@ -4669,9 +4669,9 @@
       <c r="S50" s="12"/>
       <c r="T50" s="12"/>
       <c r="U50" s="12"/>
-      <c r="V50" s="8"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7"/>
+      <c r="V50" s="7"/>
+      <c r="W50" s="8"/>
+      <c r="X50" s="8"/>
       <c r="Y50" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4689,36 +4689,36 @@
       <c r="B51" s="5">
         <v>1916.0</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="15">
         <f t="shared" si="2"/>
         <v>2.914055633</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="15">
         <v>2.0</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="15">
         <v>2.0</v>
       </c>
-      <c r="H51" s="16">
+      <c r="H51" s="15">
         <v>2.0</v>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J51" s="16">
+      <c r="J51" s="15">
         <f t="shared" si="6"/>
         <v>0.8281112665</v>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4736,7 +4736,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q51" s="16">
+      <c r="Q51" s="15">
         <f t="shared" si="20"/>
         <v>54.5</v>
       </c>
@@ -4747,9 +4747,9 @@
       <c r="S51" s="12"/>
       <c r="T51" s="12"/>
       <c r="U51" s="12"/>
-      <c r="V51" s="8"/>
-      <c r="W51" s="7"/>
-      <c r="X51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="8"/>
+      <c r="X51" s="8"/>
       <c r="Y51" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4767,36 +4767,36 @@
       <c r="B52" s="5">
         <v>1647.5</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="15">
         <f t="shared" si="2"/>
         <v>2.807418289</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="15">
         <v>2.0</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="15">
         <v>2.0</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="15">
         <v>2.0</v>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J52" s="15">
         <f t="shared" si="6"/>
         <v>0.6148365775</v>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4814,7 +4814,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q52" s="16">
+      <c r="Q52" s="15">
         <f t="shared" si="20"/>
         <v>53.5</v>
       </c>
@@ -4825,9 +4825,9 @@
       <c r="S52" s="12"/>
       <c r="T52" s="12"/>
       <c r="U52" s="12"/>
-      <c r="V52" s="8"/>
-      <c r="W52" s="7"/>
-      <c r="X52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="8"/>
+      <c r="X52" s="8"/>
       <c r="Y52" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4845,36 +4845,36 @@
       <c r="B53" s="5">
         <v>1374.0</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="15">
         <f t="shared" si="2"/>
         <v>2.712960983</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="15">
         <v>2.0</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="15">
         <v>2.0</v>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="15">
         <v>2.0</v>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J53" s="16">
+      <c r="J53" s="15">
         <f t="shared" si="6"/>
         <v>0.4259219666</v>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4892,7 +4892,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q53" s="16">
+      <c r="Q53" s="15">
         <f t="shared" si="20"/>
         <v>46</v>
       </c>
@@ -4903,9 +4903,9 @@
       <c r="S53" s="12"/>
       <c r="T53" s="12"/>
       <c r="U53" s="12"/>
-      <c r="V53" s="8"/>
-      <c r="W53" s="7"/>
-      <c r="X53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="8"/>
+      <c r="X53" s="8"/>
       <c r="Y53" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -4923,36 +4923,36 @@
       <c r="B54" s="5">
         <v>1424.0</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="15">
         <f t="shared" si="2"/>
         <v>2.699292805</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="15">
         <v>2.0</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="15">
         <v>2.0</v>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="15">
         <v>2.0</v>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J54" s="16">
+      <c r="J54" s="15">
         <f t="shared" si="6"/>
         <v>0.3985856107</v>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -4970,7 +4970,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q54" s="16">
+      <c r="Q54" s="15">
         <f t="shared" si="20"/>
         <v>44.5</v>
       </c>
@@ -4981,9 +4981,9 @@
       <c r="S54" s="12"/>
       <c r="T54" s="12"/>
       <c r="U54" s="12"/>
-      <c r="V54" s="8"/>
-      <c r="W54" s="7"/>
-      <c r="X54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="8"/>
+      <c r="X54" s="8"/>
       <c r="Y54" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5001,36 +5001,36 @@
       <c r="B55" s="5">
         <v>1370.5</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="15">
         <f t="shared" si="2"/>
         <v>2.665566784</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="15">
         <v>2.0</v>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="15">
         <v>2.0</v>
       </c>
-      <c r="H55" s="16">
+      <c r="H55" s="15">
         <v>2.0</v>
       </c>
-      <c r="I55" s="16">
+      <c r="I55" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J55" s="16">
+      <c r="J55" s="15">
         <f t="shared" si="6"/>
         <v>0.331133568</v>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5048,7 +5048,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q55" s="16">
+      <c r="Q55" s="15">
         <f t="shared" si="20"/>
         <v>41</v>
       </c>
@@ -5059,9 +5059,9 @@
       <c r="S55" s="12"/>
       <c r="T55" s="12"/>
       <c r="U55" s="12"/>
-      <c r="V55" s="8"/>
-      <c r="W55" s="7"/>
-      <c r="X55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="8"/>
+      <c r="X55" s="8"/>
       <c r="Y55" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5079,36 +5079,36 @@
       <c r="B56" s="5">
         <v>1643.0</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="15">
         <f t="shared" si="2"/>
         <v>2.69423619</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="15">
         <v>2.0</v>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="15">
         <v>2.0</v>
       </c>
-      <c r="H56" s="16">
+      <c r="H56" s="15">
         <v>2.0</v>
       </c>
-      <c r="I56" s="16">
+      <c r="I56" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J56" s="16">
+      <c r="J56" s="15">
         <f t="shared" si="6"/>
         <v>0.3884723806</v>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5126,7 +5126,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q56" s="16">
+      <c r="Q56" s="15">
         <f t="shared" si="20"/>
         <v>35.5</v>
       </c>
@@ -5137,9 +5137,9 @@
       <c r="S56" s="12"/>
       <c r="T56" s="12"/>
       <c r="U56" s="12"/>
-      <c r="V56" s="8"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="W56" s="8"/>
+      <c r="X56" s="8"/>
       <c r="Y56" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5157,36 +5157,36 @@
       <c r="B57" s="5">
         <v>1628.0</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="15">
         <f t="shared" si="2"/>
         <v>2.668878462</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="15">
         <v>2.0</v>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="15">
         <v>2.0</v>
       </c>
-      <c r="H57" s="16">
+      <c r="H57" s="15">
         <v>2.0</v>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J57" s="16">
+      <c r="J57" s="15">
         <f t="shared" si="6"/>
         <v>0.3377569237</v>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5204,7 +5204,7 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q57" s="16">
+      <c r="Q57" s="15">
         <f t="shared" si="20"/>
         <v>29.5</v>
       </c>
@@ -5215,9 +5215,9 @@
       <c r="S57" s="12"/>
       <c r="T57" s="12"/>
       <c r="U57" s="12"/>
-      <c r="V57" s="8"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="8"/>
+      <c r="X57" s="8"/>
       <c r="Y57" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5235,36 +5235,36 @@
       <c r="B58" s="5">
         <v>1302.0</v>
       </c>
-      <c r="C58" s="16">
+      <c r="C58" s="15">
         <f t="shared" si="2"/>
         <v>2.597695614</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="15">
         <v>2.0</v>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="15">
         <v>2.0</v>
       </c>
-      <c r="H58" s="16">
+      <c r="H58" s="15">
         <v>2.0</v>
       </c>
-      <c r="I58" s="16">
+      <c r="I58" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J58" s="16">
+      <c r="J58" s="15">
         <f t="shared" si="6"/>
         <v>0.1953912284</v>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5282,7 +5282,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q58" s="16">
+      <c r="Q58" s="15">
         <f t="shared" si="20"/>
         <v>28.5</v>
       </c>
@@ -5295,7 +5295,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="23"/>
       <c r="W58" s="23"/>
-      <c r="X58" s="7"/>
+      <c r="X58" s="8"/>
       <c r="Y58" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5313,36 +5313,36 @@
       <c r="B59" s="5">
         <v>1284.0</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="15">
         <f t="shared" si="2"/>
         <v>2.579699096</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="15">
         <v>2.0</v>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="15">
         <v>2.0</v>
       </c>
-      <c r="H59" s="16">
+      <c r="H59" s="15">
         <v>2.0</v>
       </c>
-      <c r="I59" s="16">
+      <c r="I59" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J59" s="16">
+      <c r="J59" s="15">
         <f t="shared" si="6"/>
         <v>0.1593981921</v>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5360,7 +5360,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q59" s="16">
+      <c r="Q59" s="15">
         <f t="shared" si="20"/>
         <v>26.5</v>
       </c>
@@ -5373,7 +5373,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="23"/>
       <c r="W59" s="23"/>
-      <c r="X59" s="7"/>
+      <c r="X59" s="8"/>
       <c r="Y59" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5391,36 +5391,36 @@
       <c r="B60" s="5">
         <v>1254.0</v>
       </c>
-      <c r="C60" s="16">
+      <c r="C60" s="15">
         <f t="shared" si="2"/>
         <v>2.561705025</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="15">
         <v>2.0</v>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="15">
         <v>2.0</v>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="15">
         <v>2.0</v>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J60" s="16">
+      <c r="J60" s="15">
         <f t="shared" si="6"/>
         <v>0.1234100499</v>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5438,7 +5438,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q60" s="16">
+      <c r="Q60" s="15">
         <f t="shared" si="20"/>
         <v>24</v>
       </c>
@@ -5451,7 +5451,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="23"/>
       <c r="W60" s="23"/>
-      <c r="X60" s="7"/>
+      <c r="X60" s="8"/>
       <c r="Y60" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5469,36 +5469,36 @@
       <c r="B61" s="5">
         <v>1253.0</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="15">
         <f t="shared" si="2"/>
         <v>2.548915241</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="15">
         <v>2.0</v>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="15">
         <v>2.0</v>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="15">
         <v>2.0</v>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="15">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="J61" s="16">
+      <c r="J61" s="15">
         <f t="shared" si="6"/>
         <v>0.09783048196</v>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="15">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
@@ -5516,7 +5516,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q61" s="16">
+      <c r="Q61" s="15">
         <f t="shared" si="20"/>
         <v>21.5</v>
       </c>
@@ -5527,9 +5527,9 @@
       <c r="S61" s="12"/>
       <c r="T61" s="12"/>
       <c r="U61" s="12"/>
-      <c r="V61" s="8"/>
-      <c r="W61" s="7"/>
-      <c r="X61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="8"/>
+      <c r="X61" s="8"/>
       <c r="Y61" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5547,36 +5547,36 @@
       <c r="B62" s="5">
         <v>1251.0</v>
       </c>
-      <c r="C62" s="16">
+      <c r="C62" s="15">
         <f t="shared" si="2"/>
         <v>1.140117313</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="15">
         <v>1.0</v>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="15">
         <v>1.0</v>
       </c>
-      <c r="H62" s="16">
+      <c r="H62" s="15">
         <v>1.0</v>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J62" s="16">
+      <c r="J62" s="15">
         <f t="shared" si="6"/>
         <v>0.2802346254</v>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -5594,7 +5594,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q62" s="16">
+      <c r="Q62" s="15">
         <f t="shared" si="20"/>
         <v>19</v>
       </c>
@@ -5609,9 +5609,9 @@
       <c r="U62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
+      <c r="X62" s="8"/>
       <c r="Y62" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5629,36 +5629,36 @@
       <c r="B63" s="5">
         <v>1250.0</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="15">
         <f t="shared" si="2"/>
         <v>1.129243371</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="15">
         <v>1.0</v>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="15">
         <v>1.0</v>
       </c>
-      <c r="H63" s="16">
+      <c r="H63" s="15">
         <v>1.0</v>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J63" s="16">
+      <c r="J63" s="15">
         <f t="shared" si="6"/>
         <v>0.2584867427</v>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -5676,7 +5676,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q63" s="16">
+      <c r="Q63" s="15">
         <f t="shared" si="20"/>
         <v>17.5</v>
       </c>
@@ -5688,13 +5688,13 @@
       <c r="T63" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="U63" s="16">
+      <c r="U63" s="15">
         <f t="shared" ref="U63:U74" si="22">SUMIF($R$45:$R$116, T63, $Q$45:$Q$116)</f>
         <v>180</v>
       </c>
-      <c r="V63" s="7"/>
-      <c r="W63" s="7"/>
-      <c r="X63" s="7"/>
+      <c r="V63" s="8"/>
+      <c r="W63" s="8"/>
+      <c r="X63" s="8"/>
       <c r="Y63" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5712,36 +5712,36 @@
       <c r="B64" s="5">
         <v>1249.0</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="15">
         <f t="shared" si="2"/>
         <v>1.119213009</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="15">
         <v>1.0</v>
       </c>
-      <c r="G64" s="16">
+      <c r="G64" s="15">
         <v>1.0</v>
       </c>
-      <c r="H64" s="16">
+      <c r="H64" s="15">
         <v>1.0</v>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J64" s="16">
+      <c r="J64" s="15">
         <f t="shared" si="6"/>
         <v>0.2384260178</v>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -5759,7 +5759,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q64" s="16">
+      <c r="Q64" s="15">
         <f t="shared" si="20"/>
         <v>16</v>
       </c>
@@ -5771,13 +5771,13 @@
       <c r="T64" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="U64" s="16">
+      <c r="U64" s="15">
         <f t="shared" si="22"/>
         <v>144.5</v>
       </c>
       <c r="V64" s="23"/>
       <c r="W64" s="23"/>
-      <c r="X64" s="7"/>
+      <c r="X64" s="8"/>
       <c r="Y64" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5795,36 +5795,36 @@
       <c r="B65" s="5">
         <v>1246.0</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="15">
         <f t="shared" si="2"/>
         <v>1.10978461</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="15">
         <v>1.0</v>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="15">
         <v>1.0</v>
       </c>
-      <c r="H65" s="16">
+      <c r="H65" s="15">
         <v>1.0</v>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J65" s="16">
+      <c r="J65" s="15">
         <f t="shared" si="6"/>
         <v>0.2195692202</v>
       </c>
-      <c r="K65" s="16">
+      <c r="K65" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -5842,7 +5842,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q65" s="16">
+      <c r="Q65" s="15">
         <f t="shared" si="20"/>
         <v>14</v>
       </c>
@@ -5854,13 +5854,13 @@
       <c r="T65" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="U65" s="16">
+      <c r="U65" s="15">
         <f t="shared" si="22"/>
         <v>132.5</v>
       </c>
-      <c r="V65" s="7"/>
-      <c r="W65" s="7"/>
-      <c r="X65" s="7"/>
+      <c r="V65" s="8"/>
+      <c r="W65" s="8"/>
+      <c r="X65" s="8"/>
       <c r="Y65" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5878,36 +5878,36 @@
       <c r="B66" s="5">
         <v>1245.0</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="15">
         <f t="shared" si="2"/>
         <v>1.101263826</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="15">
         <v>1.0</v>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="15">
         <v>1.0</v>
       </c>
-      <c r="H66" s="16">
+      <c r="H66" s="15">
         <v>1.0</v>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J66" s="16">
+      <c r="J66" s="15">
         <f t="shared" si="6"/>
         <v>0.2025276514</v>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -5925,7 +5925,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q66" s="16">
+      <c r="Q66" s="15">
         <f t="shared" si="20"/>
         <v>13.5</v>
       </c>
@@ -5937,13 +5937,13 @@
       <c r="T66" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="U66" s="16">
+      <c r="U66" s="15">
         <f t="shared" si="22"/>
         <v>117.5</v>
       </c>
-      <c r="V66" s="8"/>
-      <c r="W66" s="7"/>
-      <c r="X66" s="7"/>
+      <c r="V66" s="7"/>
+      <c r="W66" s="8"/>
+      <c r="X66" s="8"/>
       <c r="Y66" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -5961,36 +5961,36 @@
       <c r="B67" s="5">
         <v>1244.0</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="15">
         <f t="shared" si="2"/>
         <v>1.093404186</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="15">
         <v>1.0</v>
       </c>
-      <c r="G67" s="16">
+      <c r="G67" s="15">
         <v>1.0</v>
       </c>
-      <c r="H67" s="16">
+      <c r="H67" s="15">
         <v>1.0</v>
       </c>
-      <c r="I67" s="16">
+      <c r="I67" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J67" s="16">
+      <c r="J67" s="15">
         <f t="shared" si="6"/>
         <v>0.1868083716</v>
       </c>
-      <c r="K67" s="16">
+      <c r="K67" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6008,7 +6008,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q67" s="16">
+      <c r="Q67" s="15">
         <f t="shared" si="20"/>
         <v>11</v>
       </c>
@@ -6020,13 +6020,13 @@
       <c r="T67" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="U67" s="16">
+      <c r="U67" s="15">
         <f t="shared" si="22"/>
         <v>109.5</v>
       </c>
-      <c r="V67" s="8"/>
-      <c r="W67" s="7"/>
-      <c r="X67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="8"/>
+      <c r="X67" s="8"/>
       <c r="Y67" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6044,36 +6044,36 @@
       <c r="B68" s="5">
         <v>1243.0</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="15">
         <f t="shared" si="2"/>
         <v>1.086154418</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="15">
         <v>1.0</v>
       </c>
-      <c r="G68" s="16">
+      <c r="G68" s="15">
         <v>1.0</v>
       </c>
-      <c r="H68" s="16">
+      <c r="H68" s="15">
         <v>1.0</v>
       </c>
-      <c r="I68" s="16">
+      <c r="I68" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J68" s="16">
+      <c r="J68" s="15">
         <f t="shared" si="6"/>
         <v>0.1723088363</v>
       </c>
-      <c r="K68" s="16">
+      <c r="K68" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6091,7 +6091,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q68" s="16">
+      <c r="Q68" s="15">
         <f t="shared" si="20"/>
         <v>10</v>
       </c>
@@ -6103,13 +6103,13 @@
       <c r="T68" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="U68" s="16">
+      <c r="U68" s="15">
         <f t="shared" si="22"/>
         <v>99.5</v>
       </c>
-      <c r="V68" s="8"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
+      <c r="V68" s="7"/>
+      <c r="W68" s="8"/>
+      <c r="X68" s="8"/>
       <c r="Y68" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6127,36 +6127,36 @@
       <c r="B69" s="23">
         <v>1242.0</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="15">
         <f t="shared" si="2"/>
         <v>1.079467222</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="15">
         <v>1.0</v>
       </c>
-      <c r="G69" s="16">
+      <c r="G69" s="15">
         <v>1.0</v>
       </c>
-      <c r="H69" s="16">
+      <c r="H69" s="15">
         <v>1.0</v>
       </c>
-      <c r="I69" s="16">
+      <c r="I69" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J69" s="16">
+      <c r="J69" s="15">
         <f t="shared" si="6"/>
         <v>0.1589344442</v>
       </c>
-      <c r="K69" s="16">
+      <c r="K69" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6174,7 +6174,7 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q69" s="16">
+      <c r="Q69" s="15">
         <f t="shared" si="20"/>
         <v>9.5</v>
       </c>
@@ -6186,13 +6186,13 @@
       <c r="T69" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="U69" s="16">
+      <c r="U69" s="15">
         <f t="shared" si="22"/>
         <v>83</v>
       </c>
       <c r="V69" s="23"/>
       <c r="W69" s="23"/>
-      <c r="X69" s="7"/>
+      <c r="X69" s="8"/>
       <c r="Y69" s="12" t="str">
         <f t="shared" si="17"/>
         <v>0|</v>
@@ -6210,36 +6210,36 @@
       <c r="B70" s="5">
         <v>1234.0</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="15">
         <f t="shared" si="2"/>
         <v>1.072885511</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="15">
         <v>1.0</v>
       </c>
-      <c r="G70" s="16">
+      <c r="G70" s="15">
         <v>1.0</v>
       </c>
-      <c r="H70" s="16">
+      <c r="H70" s="15">
         <v>1.0</v>
       </c>
-      <c r="I70" s="16">
+      <c r="I70" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J70" s="16">
+      <c r="J70" s="15">
         <f t="shared" si="6"/>
         <v>0.145771022</v>
       </c>
-      <c r="K70" s="16">
+      <c r="K70" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6257,7 +6257,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q70" s="16">
+      <c r="Q70" s="15">
         <f t="shared" si="20"/>
         <v>9</v>
       </c>
@@ -6269,7 +6269,7 @@
       <c r="T70" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="U70" s="16">
+      <c r="U70" s="15">
         <f t="shared" si="22"/>
         <v>80.5</v>
       </c>
@@ -6293,36 +6293,36 @@
       <c r="B71" s="5">
         <v>1223.0</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="15">
         <f t="shared" si="2"/>
         <v>1.066682481</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="15">
         <v>1.0</v>
       </c>
-      <c r="G71" s="16">
+      <c r="G71" s="15">
         <v>1.0</v>
       </c>
-      <c r="H71" s="16">
+      <c r="H71" s="15">
         <v>1.0</v>
       </c>
-      <c r="I71" s="16">
+      <c r="I71" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J71" s="16">
+      <c r="J71" s="15">
         <f t="shared" si="6"/>
         <v>0.1333649619</v>
       </c>
-      <c r="K71" s="16">
+      <c r="K71" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6340,7 +6340,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q71" s="16">
+      <c r="Q71" s="15">
         <f t="shared" si="20"/>
         <v>7</v>
       </c>
@@ -6352,7 +6352,7 @@
       <c r="T71" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="U71" s="16">
+      <c r="U71" s="15">
         <f t="shared" si="22"/>
         <v>69.5</v>
       </c>
@@ -6376,36 +6376,36 @@
       <c r="B72" s="23">
         <v>1190.0</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="15">
         <f t="shared" si="2"/>
         <v>1.059895085</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="15">
         <v>1.0</v>
       </c>
-      <c r="G72" s="16">
+      <c r="G72" s="15">
         <v>1.0</v>
       </c>
-      <c r="H72" s="16">
+      <c r="H72" s="15">
         <v>1.0</v>
       </c>
-      <c r="I72" s="16">
+      <c r="I72" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J72" s="16">
+      <c r="J72" s="15">
         <f t="shared" si="6"/>
         <v>0.1197901701</v>
       </c>
-      <c r="K72" s="16">
+      <c r="K72" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6423,7 +6423,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q72" s="16">
+      <c r="Q72" s="15">
         <f t="shared" si="20"/>
         <v>7</v>
       </c>
@@ -6435,7 +6435,7 @@
       <c r="T72" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="U72" s="16">
+      <c r="U72" s="15">
         <f t="shared" si="22"/>
         <v>67.5</v>
       </c>
@@ -6459,36 +6459,36 @@
       <c r="B73" s="5">
         <v>1166.0</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="15">
         <f t="shared" si="2"/>
         <v>1.054175312</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="15">
         <v>1.0</v>
       </c>
-      <c r="G73" s="16">
+      <c r="G73" s="15">
         <v>1.0</v>
       </c>
-      <c r="H73" s="16">
+      <c r="H73" s="15">
         <v>1.0</v>
       </c>
-      <c r="I73" s="16">
+      <c r="I73" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="J73" s="16">
+      <c r="J73" s="15">
         <f t="shared" si="6"/>
         <v>0.108350625</v>
       </c>
-      <c r="K73" s="16">
+      <c r="K73" s="15">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
@@ -6506,7 +6506,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q73" s="16">
+      <c r="Q73" s="15">
         <f t="shared" si="20"/>
         <v>6.5</v>
       </c>
@@ -6518,7 +6518,7 @@
       <c r="T73" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="U73" s="16">
+      <c r="U73" s="15">
         <f t="shared" si="22"/>
         <v>61.5</v>
       </c>
@@ -6538,18 +6538,18 @@
     <row r="74">
       <c r="A74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="16">
+      <c r="D74" s="15">
         <f>Sum(D2:D73)</f>
         <v>1200</v>
       </c>
       <c r="E74" s="4"/>
-      <c r="F74" s="16">
+      <c r="F74" s="15">
         <v>1200.0</v>
       </c>
-      <c r="G74" s="16">
+      <c r="G74" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H74" s="16">
+      <c r="H74" s="15">
         <v>1200.0</v>
       </c>
       <c r="I74" s="4"/>
@@ -6569,7 +6569,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q74" s="16">
+      <c r="Q74" s="15">
         <f t="shared" si="20"/>
         <v>6.5</v>
       </c>
@@ -6581,7 +6581,7 @@
       <c r="T74" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="U74" s="16">
+      <c r="U74" s="15">
         <f t="shared" si="22"/>
         <v>54.5</v>
       </c>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="75">
       <c r="A75" s="4"/>
-      <c r="B75" s="7"/>
+      <c r="B75" s="8"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -6621,7 +6621,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q75" s="16">
+      <c r="Q75" s="15">
         <f t="shared" si="20"/>
         <v>5.5</v>
       </c>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="S75" s="12"/>
       <c r="T75" s="12"/>
-      <c r="U75" s="16">
+      <c r="U75" s="15">
         <f>SUM(U30:U74)</f>
         <v>1200</v>
       </c>
@@ -6670,7 +6670,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q76" s="16">
+      <c r="Q76" s="15">
         <f t="shared" si="20"/>
         <v>5.5</v>
       </c>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4"/>
-      <c r="B77" s="7"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -6717,7 +6717,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q77" s="16">
+      <c r="Q77" s="15">
         <f t="shared" si="20"/>
         <v>4.5</v>
       </c>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="78">
       <c r="A78" s="4"/>
-      <c r="B78" s="7"/>
+      <c r="B78" s="8"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -6764,7 +6764,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q78" s="16">
+      <c r="Q78" s="15">
         <f t="shared" si="20"/>
         <v>4.5</v>
       </c>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="79">
       <c r="A79" s="4"/>
-      <c r="B79" s="7"/>
+      <c r="B79" s="8"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -6811,7 +6811,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q79" s="16">
+      <c r="Q79" s="15">
         <f t="shared" si="20"/>
         <v>4.5</v>
       </c>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="S79" s="12"/>
       <c r="T79" s="12"/>
-      <c r="U79" s="16"/>
+      <c r="U79" s="15"/>
       <c r="V79" s="12"/>
       <c r="W79" s="12"/>
       <c r="X79" s="12"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4"/>
-      <c r="B80" s="7"/>
+      <c r="B80" s="8"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -6858,7 +6858,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q80" s="16">
+      <c r="Q80" s="15">
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="S80" s="12"/>
       <c r="T80" s="12"/>
-      <c r="U80" s="16"/>
+      <c r="U80" s="15"/>
       <c r="V80" s="12"/>
       <c r="W80" s="12"/>
       <c r="X80" s="12"/>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4"/>
-      <c r="B81" s="7"/>
+      <c r="B81" s="8"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -6905,7 +6905,7 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q81" s="16">
+      <c r="Q81" s="15">
         <f t="shared" si="20"/>
         <v>3.5</v>
       </c>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="S81" s="12"/>
       <c r="T81" s="12"/>
-      <c r="U81" s="16"/>
+      <c r="U81" s="15"/>
       <c r="V81" s="12"/>
       <c r="W81" s="12"/>
       <c r="X81" s="12"/>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4"/>
-      <c r="B82" s="7"/>
+      <c r="B82" s="8"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -6952,7 +6952,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q82" s="16">
+      <c r="Q82" s="15">
         <f t="shared" si="20"/>
         <v>3.5</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="S82" s="12"/>
       <c r="T82" s="12"/>
-      <c r="U82" s="16"/>
+      <c r="U82" s="15"/>
       <c r="V82" s="12"/>
       <c r="W82" s="12"/>
       <c r="X82" s="12"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="83">
       <c r="A83" s="12"/>
-      <c r="B83" s="7"/>
+      <c r="B83" s="8"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -6996,7 +6996,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q83" s="16">
+      <c r="Q83" s="15">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="S83" s="12"/>
       <c r="T83" s="12"/>
-      <c r="U83" s="16"/>
+      <c r="U83" s="15"/>
       <c r="V83" s="12"/>
       <c r="W83" s="12"/>
       <c r="X83" s="12"/>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="84">
       <c r="A84" s="12"/>
-      <c r="B84" s="7"/>
+      <c r="B84" s="8"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -7040,7 +7040,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q84" s="16">
+      <c r="Q84" s="15">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="S84" s="12"/>
       <c r="T84" s="12"/>
-      <c r="U84" s="16"/>
+      <c r="U84" s="15"/>
       <c r="V84" s="12"/>
       <c r="W84" s="12"/>
       <c r="X84" s="12"/>
@@ -7083,7 +7083,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q85" s="16">
+      <c r="Q85" s="15">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="S85" s="12"/>
       <c r="T85" s="12"/>
-      <c r="U85" s="16"/>
+      <c r="U85" s="15"/>
       <c r="V85" s="12"/>
       <c r="W85" s="12"/>
       <c r="X85" s="12"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="86">
       <c r="A86" s="12"/>
-      <c r="B86" s="7"/>
+      <c r="B86" s="8"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -7127,7 +7127,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q86" s="16">
+      <c r="Q86" s="15">
         <f t="shared" si="20"/>
         <v>2.5</v>
       </c>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="S86" s="12"/>
       <c r="T86" s="12"/>
-      <c r="U86" s="16"/>
+      <c r="U86" s="15"/>
       <c r="V86" s="12"/>
       <c r="W86" s="12"/>
       <c r="X86" s="12"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="87">
       <c r="A87" s="12"/>
-      <c r="B87" s="7"/>
+      <c r="B87" s="8"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -7171,7 +7171,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q87" s="16">
+      <c r="Q87" s="15">
         <f t="shared" si="20"/>
         <v>2.5</v>
       </c>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="S87" s="12"/>
       <c r="T87" s="12"/>
-      <c r="U87" s="16"/>
+      <c r="U87" s="15"/>
       <c r="V87" s="12"/>
       <c r="W87" s="12"/>
       <c r="X87" s="12"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="88">
       <c r="A88" s="12"/>
-      <c r="B88" s="7"/>
+      <c r="B88" s="8"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -7215,7 +7215,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q88" s="16">
+      <c r="Q88" s="15">
         <f t="shared" si="20"/>
         <v>2.5</v>
       </c>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="S88" s="12"/>
       <c r="T88" s="12"/>
-      <c r="U88" s="16"/>
+      <c r="U88" s="15"/>
       <c r="V88" s="12"/>
       <c r="W88" s="12"/>
       <c r="X88" s="12"/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="89">
       <c r="A89" s="12"/>
-      <c r="B89" s="7"/>
+      <c r="B89" s="8"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -7259,7 +7259,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q89" s="16">
+      <c r="Q89" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
-      <c r="U89" s="16"/>
+      <c r="U89" s="15"/>
       <c r="V89" s="12"/>
       <c r="W89" s="12"/>
       <c r="X89" s="12"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="90">
       <c r="A90" s="4"/>
-      <c r="B90" s="7"/>
+      <c r="B90" s="8"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -7303,7 +7303,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q90" s="16">
+      <c r="Q90" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="S90" s="12"/>
       <c r="T90" s="12"/>
-      <c r="U90" s="16"/>
+      <c r="U90" s="15"/>
       <c r="V90" s="12"/>
       <c r="W90" s="12"/>
       <c r="X90" s="12"/>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="91">
       <c r="A91" s="4"/>
-      <c r="B91" s="7"/>
+      <c r="B91" s="8"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -7347,7 +7347,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q91" s="16">
+      <c r="Q91" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="92">
       <c r="A92" s="4"/>
-      <c r="B92" s="7"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -7391,7 +7391,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q92" s="16">
+      <c r="Q92" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="93">
       <c r="A93" s="4"/>
-      <c r="B93" s="7"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -7435,7 +7435,7 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q93" s="16">
+      <c r="Q93" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="94">
       <c r="A94" s="12"/>
-      <c r="B94" s="7"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -7479,7 +7479,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q94" s="16">
+      <c r="Q94" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="95">
       <c r="A95" s="12"/>
-      <c r="B95" s="7"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -7523,7 +7523,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q95" s="16">
+      <c r="Q95" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="96">
       <c r="A96" s="12"/>
-      <c r="B96" s="7"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -7567,7 +7567,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q96" s="16">
+      <c r="Q96" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="97">
       <c r="A97" s="12"/>
-      <c r="B97" s="7"/>
+      <c r="B97" s="8"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -7611,7 +7611,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q97" s="16">
+      <c r="Q97" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="12"/>
-      <c r="B98" s="7"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -7655,7 +7655,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q98" s="16">
+      <c r="Q98" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="99">
       <c r="A99" s="12"/>
-      <c r="B99" s="7"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -7699,7 +7699,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q99" s="16">
+      <c r="Q99" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="100">
       <c r="A100" s="12"/>
-      <c r="B100" s="7"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -7743,7 +7743,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q100" s="16">
+      <c r="Q100" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="101">
       <c r="A101" s="4"/>
-      <c r="B101" s="7"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -7787,7 +7787,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q101" s="16">
+      <c r="Q101" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="102">
       <c r="A102" s="4"/>
-      <c r="B102" s="7"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -7831,7 +7831,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q102" s="16">
+      <c r="Q102" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7875,7 +7875,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q103" s="16">
+      <c r="Q103" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7919,7 +7919,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q104" s="16">
+      <c r="Q104" s="15">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -7963,7 +7963,7 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q105" s="16">
+      <c r="Q105" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8007,7 +8007,7 @@
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="Q106" s="16">
+      <c r="Q106" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8051,7 +8051,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Q107" s="16">
+      <c r="Q107" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8095,7 +8095,7 @@
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="Q108" s="16">
+      <c r="Q108" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8139,7 +8139,7 @@
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="Q109" s="16">
+      <c r="Q109" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8183,7 +8183,7 @@
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="Q110" s="16">
+      <c r="Q110" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8227,7 +8227,7 @@
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="Q111" s="16">
+      <c r="Q111" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8271,7 +8271,7 @@
         <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="Q112" s="16">
+      <c r="Q112" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8315,7 +8315,7 @@
         <f t="shared" si="19"/>
         <v>9</v>
       </c>
-      <c r="Q113" s="16">
+      <c r="Q113" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8359,7 +8359,7 @@
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="Q114" s="16">
+      <c r="Q114" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8403,7 +8403,7 @@
         <f t="shared" si="19"/>
         <v>11</v>
       </c>
-      <c r="Q115" s="16">
+      <c r="Q115" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8447,7 +8447,7 @@
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="Q116" s="16">
+      <c r="Q116" s="15">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -8485,7 +8485,7 @@
       <c r="N117" s="12"/>
       <c r="O117" s="12"/>
       <c r="P117" s="12"/>
-      <c r="Q117" s="16">
+      <c r="Q117" s="15">
         <f>SUM(Q30:Q116)</f>
         <v>1200</v>
       </c>
@@ -9146,7 +9146,7 @@
       <c r="W137" s="12"/>
       <c r="X137" s="12"/>
       <c r="Y137" s="12"/>
-      <c r="Z137" s="7" t="s">
+      <c r="Z137" s="8" t="s">
         <v>137</v>
       </c>
       <c r="AA137" s="12"/>
@@ -9180,7 +9180,7 @@
       <c r="W138" s="12"/>
       <c r="X138" s="12"/>
       <c r="Y138" s="12"/>
-      <c r="Z138" s="7">
+      <c r="Z138" s="8">
         <v>6817.0</v>
       </c>
       <c r="AA138" s="12"/>
@@ -9211,16 +9211,16 @@
       <c r="T139" s="12"/>
       <c r="U139" s="12"/>
       <c r="V139" s="12"/>
-      <c r="W139" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="X139" s="7" t="s">
+      <c r="W139" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="X139" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="Y139" s="7" t="s">
+      <c r="Y139" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="Z139" s="7">
+      <c r="Z139" s="8">
         <v>5203.0</v>
       </c>
       <c r="AA139" s="12"/>
@@ -9251,16 +9251,16 @@
       <c r="T140" s="12"/>
       <c r="U140" s="12"/>
       <c r="V140" s="12"/>
-      <c r="W140" s="7">
+      <c r="W140" s="8">
         <v>1.0</v>
       </c>
-      <c r="X140" s="7" t="s">
+      <c r="X140" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Y140" s="7" t="s">
+      <c r="Y140" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z140" s="7">
+      <c r="Z140" s="8">
         <v>5103.0</v>
       </c>
       <c r="AA140" s="12"/>
@@ -9291,16 +9291,16 @@
       <c r="T141" s="12"/>
       <c r="U141" s="12"/>
       <c r="V141" s="12"/>
-      <c r="W141" s="7">
+      <c r="W141" s="8">
         <v>3.0</v>
       </c>
-      <c r="X141" s="7" t="s">
+      <c r="X141" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Y141" s="7" t="s">
+      <c r="Y141" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z141" s="7">
+      <c r="Z141" s="8">
         <v>5020.0</v>
       </c>
       <c r="AA141" s="12"/>
@@ -9331,16 +9331,16 @@
       <c r="T142" s="12"/>
       <c r="U142" s="12"/>
       <c r="V142" s="12"/>
-      <c r="W142" s="7">
+      <c r="W142" s="8">
         <v>4.0</v>
       </c>
-      <c r="X142" s="7" t="s">
+      <c r="X142" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Y142" s="7" t="s">
+      <c r="Y142" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z142" s="7">
+      <c r="Z142" s="8">
         <v>4517.0</v>
       </c>
       <c r="AA142" s="12"/>
@@ -9371,16 +9371,16 @@
       <c r="T143" s="12"/>
       <c r="U143" s="12"/>
       <c r="V143" s="12"/>
-      <c r="W143" s="7">
+      <c r="W143" s="8">
         <v>5.0</v>
       </c>
-      <c r="X143" s="7" t="s">
+      <c r="X143" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="Y143" s="7" t="s">
+      <c r="Y143" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z143" s="7">
+      <c r="Z143" s="8">
         <v>4164.0</v>
       </c>
       <c r="AA143" s="12"/>
@@ -9411,16 +9411,16 @@
       <c r="T144" s="12"/>
       <c r="U144" s="12"/>
       <c r="V144" s="12"/>
-      <c r="W144" s="7">
+      <c r="W144" s="8">
         <v>6.0</v>
       </c>
-      <c r="X144" s="7" t="s">
+      <c r="X144" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="Y144" s="7" t="s">
+      <c r="Y144" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z144" s="7">
+      <c r="Z144" s="8">
         <v>4025.0</v>
       </c>
       <c r="AA144" s="12"/>
@@ -9451,16 +9451,16 @@
       <c r="T145" s="12"/>
       <c r="U145" s="12"/>
       <c r="V145" s="12"/>
-      <c r="W145" s="7">
+      <c r="W145" s="8">
         <v>7.0</v>
       </c>
-      <c r="X145" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y145" s="7" t="s">
+      <c r="X145" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y145" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z145" s="7">
+      <c r="Z145" s="8">
         <v>3650.0</v>
       </c>
       <c r="AA145" s="12"/>
@@ -9491,16 +9491,16 @@
       <c r="T146" s="12"/>
       <c r="U146" s="12"/>
       <c r="V146" s="12"/>
-      <c r="W146" s="7">
+      <c r="W146" s="8">
         <v>8.0</v>
       </c>
-      <c r="X146" s="7" t="s">
+      <c r="X146" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="Y146" s="7" t="s">
+      <c r="Y146" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z146" s="7">
+      <c r="Z146" s="8">
         <v>3611.0</v>
       </c>
       <c r="AA146" s="12"/>
@@ -9531,16 +9531,16 @@
       <c r="T147" s="12"/>
       <c r="U147" s="12"/>
       <c r="V147" s="12"/>
-      <c r="W147" s="7">
+      <c r="W147" s="8">
         <v>9.0</v>
       </c>
-      <c r="X147" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y147" s="7" t="s">
+      <c r="X147" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y147" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z147" s="7">
+      <c r="Z147" s="8">
         <v>3608.0</v>
       </c>
       <c r="AA147" s="12"/>
@@ -9571,16 +9571,16 @@
       <c r="T148" s="12"/>
       <c r="U148" s="12"/>
       <c r="V148" s="12"/>
-      <c r="W148" s="7">
+      <c r="W148" s="8">
         <v>10.0</v>
       </c>
-      <c r="X148" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y148" s="7" t="s">
+      <c r="X148" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y148" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="Z148" s="7">
+      <c r="Z148" s="8">
         <v>3596.0</v>
       </c>
       <c r="AA148" s="12"/>
@@ -9611,16 +9611,16 @@
       <c r="T149" s="12"/>
       <c r="U149" s="12"/>
       <c r="V149" s="12"/>
-      <c r="W149" s="7">
+      <c r="W149" s="8">
         <v>11.0</v>
       </c>
-      <c r="X149" s="7" t="s">
+      <c r="X149" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="Y149" s="7" t="s">
+      <c r="Y149" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z149" s="7">
+      <c r="Z149" s="8">
         <v>3426.0</v>
       </c>
       <c r="AA149" s="12"/>
@@ -9651,16 +9651,16 @@
       <c r="T150" s="12"/>
       <c r="U150" s="12"/>
       <c r="V150" s="12"/>
-      <c r="W150" s="7">
+      <c r="W150" s="8">
         <v>12.0</v>
       </c>
-      <c r="X150" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y150" s="7" t="s">
+      <c r="X150" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y150" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="Z150" s="7">
+      <c r="Z150" s="8">
         <v>3264.0</v>
       </c>
       <c r="AA150" s="12"/>
@@ -9691,16 +9691,16 @@
       <c r="T151" s="12"/>
       <c r="U151" s="12"/>
       <c r="V151" s="12"/>
-      <c r="W151" s="7">
+      <c r="W151" s="8">
         <v>13.0</v>
       </c>
-      <c r="X151" s="7" t="s">
+      <c r="X151" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="Y151" s="7" t="s">
+      <c r="Y151" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="Z151" s="7">
+      <c r="Z151" s="8">
         <v>3179.0</v>
       </c>
       <c r="AA151" s="12"/>
@@ -9731,16 +9731,16 @@
       <c r="T152" s="12"/>
       <c r="U152" s="12"/>
       <c r="V152" s="12"/>
-      <c r="W152" s="7">
+      <c r="W152" s="8">
         <v>14.0</v>
       </c>
-      <c r="X152" s="7" t="s">
+      <c r="X152" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="Y152" s="7" t="s">
+      <c r="Y152" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z152" s="7">
+      <c r="Z152" s="8">
         <v>3162.0</v>
       </c>
       <c r="AA152" s="12"/>
@@ -9771,16 +9771,16 @@
       <c r="T153" s="12"/>
       <c r="U153" s="12"/>
       <c r="V153" s="12"/>
-      <c r="W153" s="7">
+      <c r="W153" s="8">
         <v>15.0</v>
       </c>
-      <c r="X153" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y153" s="7" t="s">
+      <c r="X153" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y153" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z153" s="7">
+      <c r="Z153" s="8">
         <v>3125.0</v>
       </c>
       <c r="AA153" s="12"/>
@@ -9811,16 +9811,16 @@
       <c r="T154" s="12"/>
       <c r="U154" s="12"/>
       <c r="V154" s="12"/>
-      <c r="W154" s="7">
+      <c r="W154" s="8">
         <v>16.0</v>
       </c>
-      <c r="X154" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y154" s="7" t="s">
+      <c r="X154" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y154" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z154" s="7">
+      <c r="Z154" s="8">
         <v>2971.0</v>
       </c>
       <c r="AA154" s="12"/>
@@ -9851,16 +9851,16 @@
       <c r="T155" s="12"/>
       <c r="U155" s="12"/>
       <c r="V155" s="12"/>
-      <c r="W155" s="7">
+      <c r="W155" s="8">
         <v>17.0</v>
       </c>
-      <c r="X155" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y155" s="7" t="s">
+      <c r="X155" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y155" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z155" s="7">
+      <c r="Z155" s="8">
         <v>2963.0</v>
       </c>
       <c r="AA155" s="12"/>
@@ -9891,16 +9891,16 @@
       <c r="T156" s="12"/>
       <c r="U156" s="12"/>
       <c r="V156" s="12"/>
-      <c r="W156" s="7">
+      <c r="W156" s="8">
         <v>18.0</v>
       </c>
-      <c r="X156" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y156" s="7" t="s">
+      <c r="X156" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y156" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="Z156" s="7">
+      <c r="Z156" s="8">
         <v>2953.0</v>
       </c>
       <c r="AA156" s="12"/>
@@ -9931,16 +9931,16 @@
       <c r="T157" s="12"/>
       <c r="U157" s="12"/>
       <c r="V157" s="12"/>
-      <c r="W157" s="7">
+      <c r="W157" s="8">
         <v>19.0</v>
       </c>
-      <c r="X157" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y157" s="7" t="s">
+      <c r="X157" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y157" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="Z157" s="7">
+      <c r="Z157" s="8">
         <v>2807.0</v>
       </c>
       <c r="AA157" s="12"/>
@@ -9971,16 +9971,16 @@
       <c r="T158" s="12"/>
       <c r="U158" s="12"/>
       <c r="V158" s="12"/>
-      <c r="W158" s="7">
+      <c r="W158" s="8">
         <v>20.0</v>
       </c>
-      <c r="X158" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y158" s="7" t="s">
+      <c r="X158" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y158" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z158" s="7">
+      <c r="Z158" s="8">
         <v>2696.0</v>
       </c>
       <c r="AA158" s="12"/>
@@ -10011,16 +10011,16 @@
       <c r="T159" s="12"/>
       <c r="U159" s="12"/>
       <c r="V159" s="12"/>
-      <c r="W159" s="7">
+      <c r="W159" s="8">
         <v>21.0</v>
       </c>
-      <c r="X159" s="7" t="s">
+      <c r="X159" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="Y159" s="7" t="s">
+      <c r="Y159" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z159" s="7">
+      <c r="Z159" s="8">
         <v>2672.0</v>
       </c>
       <c r="AA159" s="12"/>
@@ -10051,16 +10051,16 @@
       <c r="T160" s="12"/>
       <c r="U160" s="12"/>
       <c r="V160" s="12"/>
-      <c r="W160" s="7">
+      <c r="W160" s="8">
         <v>22.0</v>
       </c>
-      <c r="X160" s="7" t="s">
+      <c r="X160" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Y160" s="7" t="s">
+      <c r="Y160" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z160" s="7">
+      <c r="Z160" s="8">
         <v>2480.0</v>
       </c>
       <c r="AA160" s="12"/>
@@ -10091,16 +10091,16 @@
       <c r="T161" s="12"/>
       <c r="U161" s="12"/>
       <c r="V161" s="12"/>
-      <c r="W161" s="7">
+      <c r="W161" s="8">
         <v>23.0</v>
       </c>
-      <c r="X161" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y161" s="7" t="s">
+      <c r="X161" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y161" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z161" s="7">
+      <c r="Z161" s="8">
         <v>2416.0</v>
       </c>
       <c r="AA161" s="12"/>
@@ -10131,16 +10131,16 @@
       <c r="T162" s="12"/>
       <c r="U162" s="12"/>
       <c r="V162" s="12"/>
-      <c r="W162" s="7">
+      <c r="W162" s="8">
         <v>24.0</v>
       </c>
-      <c r="X162" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y162" s="7" t="s">
+      <c r="X162" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y162" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z162" s="7">
+      <c r="Z162" s="8">
         <v>2416.0</v>
       </c>
       <c r="AA162" s="12"/>
@@ -10171,16 +10171,16 @@
       <c r="T163" s="12"/>
       <c r="U163" s="12"/>
       <c r="V163" s="12"/>
-      <c r="W163" s="7">
+      <c r="W163" s="8">
         <v>25.0</v>
       </c>
-      <c r="X163" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y163" s="7" t="s">
+      <c r="X163" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y163" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z163" s="7">
+      <c r="Z163" s="8">
         <v>2109.0</v>
       </c>
       <c r="AA163" s="12"/>
@@ -10211,16 +10211,16 @@
       <c r="T164" s="12"/>
       <c r="U164" s="12"/>
       <c r="V164" s="12"/>
-      <c r="W164" s="7">
+      <c r="W164" s="8">
         <v>26.0</v>
       </c>
-      <c r="X164" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y164" s="7" t="s">
+      <c r="X164" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y164" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z164" s="7">
+      <c r="Z164" s="8">
         <v>2106.0</v>
       </c>
       <c r="AA164" s="12"/>
@@ -10251,16 +10251,16 @@
       <c r="T165" s="12"/>
       <c r="U165" s="12"/>
       <c r="V165" s="12"/>
-      <c r="W165" s="7">
+      <c r="W165" s="8">
         <v>27.0</v>
       </c>
-      <c r="X165" s="7" t="s">
+      <c r="X165" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="Y165" s="7" t="s">
+      <c r="Y165" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z165" s="7">
+      <c r="Z165" s="8">
         <v>2098.0</v>
       </c>
       <c r="AA165" s="12"/>
@@ -10291,16 +10291,16 @@
       <c r="T166" s="12"/>
       <c r="U166" s="12"/>
       <c r="V166" s="12"/>
-      <c r="W166" s="7">
+      <c r="W166" s="8">
         <v>28.0</v>
       </c>
-      <c r="X166" s="7" t="s">
+      <c r="X166" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="Y166" s="7" t="s">
+      <c r="Y166" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z166" s="7">
+      <c r="Z166" s="8">
         <v>2078.0</v>
       </c>
       <c r="AA166" s="12"/>
@@ -10331,16 +10331,16 @@
       <c r="T167" s="12"/>
       <c r="U167" s="12"/>
       <c r="V167" s="12"/>
-      <c r="W167" s="7">
+      <c r="W167" s="8">
         <v>29.0</v>
       </c>
-      <c r="X167" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y167" s="7" t="s">
+      <c r="X167" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y167" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z167" s="7">
+      <c r="Z167" s="8">
         <v>2074.0</v>
       </c>
       <c r="AA167" s="12"/>
@@ -10371,16 +10371,16 @@
       <c r="T168" s="12"/>
       <c r="U168" s="12"/>
       <c r="V168" s="12"/>
-      <c r="W168" s="7">
+      <c r="W168" s="8">
         <v>30.0</v>
       </c>
-      <c r="X168" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y168" s="7" t="s">
+      <c r="X168" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y168" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z168" s="7">
+      <c r="Z168" s="8">
         <v>2066.0</v>
       </c>
       <c r="AA168" s="12"/>
@@ -10411,16 +10411,16 @@
       <c r="T169" s="12"/>
       <c r="U169" s="12"/>
       <c r="V169" s="12"/>
-      <c r="W169" s="7">
+      <c r="W169" s="8">
         <v>31.0</v>
       </c>
-      <c r="X169" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y169" s="7" t="s">
+      <c r="X169" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y169" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z169" s="7">
+      <c r="Z169" s="8">
         <v>2045.0</v>
       </c>
       <c r="AA169" s="12"/>
@@ -10451,16 +10451,16 @@
       <c r="T170" s="12"/>
       <c r="U170" s="12"/>
       <c r="V170" s="12"/>
-      <c r="W170" s="7">
+      <c r="W170" s="8">
         <v>32.0</v>
       </c>
-      <c r="X170" s="7" t="s">
+      <c r="X170" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="Y170" s="7" t="s">
+      <c r="Y170" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z170" s="7">
+      <c r="Z170" s="8">
         <v>1977.0</v>
       </c>
       <c r="AA170" s="12"/>
@@ -10491,16 +10491,16 @@
       <c r="T171" s="12"/>
       <c r="U171" s="12"/>
       <c r="V171" s="12"/>
-      <c r="W171" s="7">
+      <c r="W171" s="8">
         <v>33.0</v>
       </c>
-      <c r="X171" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y171" s="7" t="s">
+      <c r="X171" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y171" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z171" s="7">
+      <c r="Z171" s="8">
         <v>1967.0</v>
       </c>
       <c r="AA171" s="12"/>
@@ -10531,16 +10531,16 @@
       <c r="T172" s="12"/>
       <c r="U172" s="12"/>
       <c r="V172" s="12"/>
-      <c r="W172" s="7">
+      <c r="W172" s="8">
         <v>34.0</v>
       </c>
-      <c r="X172" s="7" t="s">
+      <c r="X172" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="Y172" s="7" t="s">
+      <c r="Y172" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="Z172" s="7">
+      <c r="Z172" s="8">
         <v>1962.0</v>
       </c>
       <c r="AA172" s="12"/>
@@ -10571,16 +10571,16 @@
       <c r="T173" s="12"/>
       <c r="U173" s="12"/>
       <c r="V173" s="12"/>
-      <c r="W173" s="7">
+      <c r="W173" s="8">
         <v>35.0</v>
       </c>
-      <c r="X173" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y173" s="7" t="s">
+      <c r="X173" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y173" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z173" s="7">
+      <c r="Z173" s="8">
         <v>1961.0</v>
       </c>
       <c r="AA173" s="12"/>
@@ -10611,16 +10611,16 @@
       <c r="T174" s="12"/>
       <c r="U174" s="12"/>
       <c r="V174" s="12"/>
-      <c r="W174" s="7">
+      <c r="W174" s="8">
         <v>36.0</v>
       </c>
-      <c r="X174" s="7" t="s">
+      <c r="X174" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="Y174" s="7" t="s">
+      <c r="Y174" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z174" s="7">
+      <c r="Z174" s="8">
         <v>1910.0</v>
       </c>
       <c r="AA174" s="12"/>
@@ -10651,16 +10651,16 @@
       <c r="T175" s="12"/>
       <c r="U175" s="12"/>
       <c r="V175" s="12"/>
-      <c r="W175" s="7">
+      <c r="W175" s="8">
         <v>37.0</v>
       </c>
-      <c r="X175" s="7" t="s">
+      <c r="X175" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="Y175" s="7" t="s">
+      <c r="Y175" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z175" s="7">
+      <c r="Z175" s="8">
         <v>1873.0</v>
       </c>
       <c r="AA175" s="12"/>
@@ -10691,16 +10691,16 @@
       <c r="T176" s="12"/>
       <c r="U176" s="12"/>
       <c r="V176" s="12"/>
-      <c r="W176" s="7">
+      <c r="W176" s="8">
         <v>38.0</v>
       </c>
-      <c r="X176" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y176" s="7" t="s">
+      <c r="X176" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y176" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z176" s="7">
+      <c r="Z176" s="8">
         <v>1822.0</v>
       </c>
       <c r="AA176" s="12"/>
@@ -10731,16 +10731,16 @@
       <c r="T177" s="12"/>
       <c r="U177" s="12"/>
       <c r="V177" s="12"/>
-      <c r="W177" s="7">
+      <c r="W177" s="8">
         <v>39.0</v>
       </c>
-      <c r="X177" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y177" s="7" t="s">
+      <c r="X177" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y177" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z177" s="7">
+      <c r="Z177" s="8">
         <v>1741.0</v>
       </c>
       <c r="AA177" s="12"/>
@@ -10771,16 +10771,16 @@
       <c r="T178" s="12"/>
       <c r="U178" s="12"/>
       <c r="V178" s="12"/>
-      <c r="W178" s="7">
+      <c r="W178" s="8">
         <v>40.0</v>
       </c>
-      <c r="X178" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y178" s="7" t="s">
+      <c r="X178" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y178" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z178" s="7">
+      <c r="Z178" s="8">
         <v>1724.0</v>
       </c>
       <c r="AA178" s="12"/>
@@ -10811,16 +10811,16 @@
       <c r="T179" s="12"/>
       <c r="U179" s="12"/>
       <c r="V179" s="12"/>
-      <c r="W179" s="7">
+      <c r="W179" s="8">
         <v>41.0</v>
       </c>
-      <c r="X179" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y179" s="7" t="s">
+      <c r="X179" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y179" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z179" s="7">
+      <c r="Z179" s="8">
         <v>1660.0</v>
       </c>
       <c r="AA179" s="12"/>
@@ -10851,16 +10851,16 @@
       <c r="T180" s="12"/>
       <c r="U180" s="12"/>
       <c r="V180" s="12"/>
-      <c r="W180" s="7">
+      <c r="W180" s="8">
         <v>42.0</v>
       </c>
-      <c r="X180" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y180" s="7" t="s">
+      <c r="X180" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y180" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z180" s="7">
+      <c r="Z180" s="8">
         <v>1640.0</v>
       </c>
       <c r="AA180" s="12"/>
@@ -10891,16 +10891,16 @@
       <c r="T181" s="12"/>
       <c r="U181" s="12"/>
       <c r="V181" s="12"/>
-      <c r="W181" s="7">
+      <c r="W181" s="8">
         <v>43.0</v>
       </c>
-      <c r="X181" s="7" t="s">
+      <c r="X181" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="Y181" s="7" t="s">
+      <c r="Y181" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z181" s="7">
+      <c r="Z181" s="8">
         <v>1577.0</v>
       </c>
       <c r="AA181" s="12"/>
@@ -10931,16 +10931,16 @@
       <c r="T182" s="12"/>
       <c r="U182" s="12"/>
       <c r="V182" s="12"/>
-      <c r="W182" s="7">
+      <c r="W182" s="8">
         <v>44.0</v>
       </c>
-      <c r="X182" s="7" t="s">
+      <c r="X182" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Y182" s="7" t="s">
+      <c r="Y182" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z182" s="7">
+      <c r="Z182" s="8">
         <v>1565.0</v>
       </c>
       <c r="AA182" s="12"/>
@@ -10971,16 +10971,16 @@
       <c r="T183" s="12"/>
       <c r="U183" s="12"/>
       <c r="V183" s="12"/>
-      <c r="W183" s="7">
+      <c r="W183" s="8">
         <v>45.0</v>
       </c>
-      <c r="X183" s="7" t="s">
+      <c r="X183" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="Y183" s="7" t="s">
+      <c r="Y183" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z183" s="7">
+      <c r="Z183" s="8">
         <v>1552.0</v>
       </c>
       <c r="AA183" s="12"/>
@@ -11011,16 +11011,16 @@
       <c r="T184" s="12"/>
       <c r="U184" s="12"/>
       <c r="V184" s="12"/>
-      <c r="W184" s="7">
+      <c r="W184" s="8">
         <v>46.0</v>
       </c>
-      <c r="X184" s="7" t="s">
+      <c r="X184" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="Y184" s="7" t="s">
+      <c r="Y184" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z184" s="7">
+      <c r="Z184" s="8">
         <v>1404.0</v>
       </c>
       <c r="AA184" s="12"/>
@@ -11051,16 +11051,16 @@
       <c r="T185" s="12"/>
       <c r="U185" s="12"/>
       <c r="V185" s="12"/>
-      <c r="W185" s="7">
+      <c r="W185" s="8">
         <v>47.0</v>
       </c>
-      <c r="X185" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y185" s="7" t="s">
+      <c r="X185" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y185" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z185" s="7">
+      <c r="Z185" s="8">
         <v>1351.0</v>
       </c>
       <c r="AA185" s="12"/>
@@ -11091,16 +11091,16 @@
       <c r="T186" s="12"/>
       <c r="U186" s="12"/>
       <c r="V186" s="12"/>
-      <c r="W186" s="7">
+      <c r="W186" s="8">
         <v>48.0</v>
       </c>
-      <c r="X186" s="7" t="s">
+      <c r="X186" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="Y186" s="7" t="s">
+      <c r="Y186" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z186" s="7">
+      <c r="Z186" s="8">
         <v>1344.0</v>
       </c>
       <c r="AA186" s="12"/>
@@ -11131,16 +11131,16 @@
       <c r="T187" s="12"/>
       <c r="U187" s="12"/>
       <c r="V187" s="12"/>
-      <c r="W187" s="7">
+      <c r="W187" s="8">
         <v>49.0</v>
       </c>
-      <c r="X187" s="7" t="s">
+      <c r="X187" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="Y187" s="7" t="s">
+      <c r="Y187" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z187" s="7">
+      <c r="Z187" s="8">
         <v>1299.0</v>
       </c>
       <c r="AA187" s="12"/>
@@ -11171,16 +11171,16 @@
       <c r="T188" s="12"/>
       <c r="U188" s="12"/>
       <c r="V188" s="12"/>
-      <c r="W188" s="7">
+      <c r="W188" s="8">
         <v>50.0</v>
       </c>
-      <c r="X188" s="7" t="s">
+      <c r="X188" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Y188" s="7" t="s">
+      <c r="Y188" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z188" s="7">
+      <c r="Z188" s="8">
         <v>1261.0</v>
       </c>
       <c r="AA188" s="12"/>
@@ -11211,16 +11211,16 @@
       <c r="T189" s="12"/>
       <c r="U189" s="12"/>
       <c r="V189" s="12"/>
-      <c r="W189" s="7">
+      <c r="W189" s="8">
         <v>51.0</v>
       </c>
-      <c r="X189" s="7" t="s">
+      <c r="X189" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="Y189" s="7" t="s">
+      <c r="Y189" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z189" s="7">
+      <c r="Z189" s="8">
         <v>1247.0</v>
       </c>
       <c r="AA189" s="12"/>
@@ -11251,16 +11251,16 @@
       <c r="T190" s="12"/>
       <c r="U190" s="12"/>
       <c r="V190" s="12"/>
-      <c r="W190" s="7">
+      <c r="W190" s="8">
         <v>52.0</v>
       </c>
-      <c r="X190" s="7" t="s">
+      <c r="X190" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Y190" s="7" t="s">
+      <c r="Y190" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z190" s="7">
+      <c r="Z190" s="8">
         <v>1226.0</v>
       </c>
       <c r="AA190" s="12"/>
@@ -11291,16 +11291,16 @@
       <c r="T191" s="12"/>
       <c r="U191" s="12"/>
       <c r="V191" s="12"/>
-      <c r="W191" s="7">
+      <c r="W191" s="8">
         <v>53.0</v>
       </c>
-      <c r="X191" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y191" s="7" t="s">
+      <c r="X191" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y191" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z191" s="7">
+      <c r="Z191" s="8">
         <v>1211.0</v>
       </c>
       <c r="AA191" s="12"/>
@@ -11331,16 +11331,16 @@
       <c r="T192" s="12"/>
       <c r="U192" s="12"/>
       <c r="V192" s="12"/>
-      <c r="W192" s="7">
+      <c r="W192" s="8">
         <v>54.0</v>
       </c>
-      <c r="X192" s="7" t="s">
+      <c r="X192" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="Y192" s="7" t="s">
+      <c r="Y192" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z192" s="7">
+      <c r="Z192" s="8">
         <v>1197.0</v>
       </c>
       <c r="AA192" s="12"/>
@@ -11371,16 +11371,16 @@
       <c r="T193" s="12"/>
       <c r="U193" s="12"/>
       <c r="V193" s="12"/>
-      <c r="W193" s="7">
+      <c r="W193" s="8">
         <v>55.0</v>
       </c>
-      <c r="X193" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y193" s="7" t="s">
+      <c r="X193" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y193" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z193" s="7">
+      <c r="Z193" s="8">
         <v>1184.0</v>
       </c>
       <c r="AA193" s="12"/>
@@ -11411,16 +11411,16 @@
       <c r="T194" s="12"/>
       <c r="U194" s="12"/>
       <c r="V194" s="12"/>
-      <c r="W194" s="7">
+      <c r="W194" s="8">
         <v>56.0</v>
       </c>
-      <c r="X194" s="7" t="s">
+      <c r="X194" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="Y194" s="7" t="s">
+      <c r="Y194" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z194" s="7">
+      <c r="Z194" s="8">
         <v>1157.0</v>
       </c>
       <c r="AA194" s="12"/>
@@ -11451,16 +11451,16 @@
       <c r="T195" s="12"/>
       <c r="U195" s="12"/>
       <c r="V195" s="12"/>
-      <c r="W195" s="7">
+      <c r="W195" s="8">
         <v>57.0</v>
       </c>
-      <c r="X195" s="7" t="s">
+      <c r="X195" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="Y195" s="7" t="s">
+      <c r="Y195" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z195" s="7">
+      <c r="Z195" s="8">
         <v>1143.0</v>
       </c>
       <c r="AA195" s="12"/>
@@ -11491,16 +11491,16 @@
       <c r="T196" s="12"/>
       <c r="U196" s="12"/>
       <c r="V196" s="12"/>
-      <c r="W196" s="7">
+      <c r="W196" s="8">
         <v>58.0</v>
       </c>
-      <c r="X196" s="7" t="s">
+      <c r="X196" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="Y196" s="7" t="s">
+      <c r="Y196" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z196" s="7">
+      <c r="Z196" s="8">
         <v>1078.0</v>
       </c>
       <c r="AA196" s="12"/>
@@ -11531,16 +11531,16 @@
       <c r="T197" s="12"/>
       <c r="U197" s="12"/>
       <c r="V197" s="12"/>
-      <c r="W197" s="7">
+      <c r="W197" s="8">
         <v>59.0</v>
       </c>
-      <c r="X197" s="7" t="s">
+      <c r="X197" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="Y197" s="7" t="s">
+      <c r="Y197" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z197" s="7">
+      <c r="Z197" s="8">
         <v>1069.0</v>
       </c>
       <c r="AA197" s="12"/>
@@ -11571,16 +11571,16 @@
       <c r="T198" s="12"/>
       <c r="U198" s="12"/>
       <c r="V198" s="12"/>
-      <c r="W198" s="7">
+      <c r="W198" s="8">
         <v>60.0</v>
       </c>
-      <c r="X198" s="7" t="s">
+      <c r="X198" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="Y198" s="7" t="s">
+      <c r="Y198" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z198" s="7">
+      <c r="Z198" s="8">
         <v>1000.0</v>
       </c>
       <c r="AA198" s="12"/>
@@ -11611,16 +11611,16 @@
       <c r="T199" s="12"/>
       <c r="U199" s="12"/>
       <c r="V199" s="12"/>
-      <c r="W199" s="7">
+      <c r="W199" s="8">
         <v>61.0</v>
       </c>
-      <c r="X199" s="7" t="s">
+      <c r="X199" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="Y199" s="7" t="s">
+      <c r="Y199" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z199" s="7">
+      <c r="Z199" s="8">
         <v>987.0</v>
       </c>
       <c r="AA199" s="12"/>
@@ -11651,16 +11651,16 @@
       <c r="T200" s="12"/>
       <c r="U200" s="12"/>
       <c r="V200" s="12"/>
-      <c r="W200" s="7">
+      <c r="W200" s="8">
         <v>62.0</v>
       </c>
-      <c r="X200" s="7" t="s">
+      <c r="X200" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="Y200" s="7" t="s">
+      <c r="Y200" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z200" s="7">
+      <c r="Z200" s="8">
         <v>952.0</v>
       </c>
       <c r="AA200" s="12"/>
@@ -11691,16 +11691,16 @@
       <c r="T201" s="12"/>
       <c r="U201" s="12"/>
       <c r="V201" s="12"/>
-      <c r="W201" s="7">
+      <c r="W201" s="8">
         <v>63.0</v>
       </c>
-      <c r="X201" s="7" t="s">
+      <c r="X201" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Y201" s="7" t="s">
+      <c r="Y201" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z201" s="7">
+      <c r="Z201" s="8">
         <v>913.0</v>
       </c>
       <c r="AA201" s="12"/>
@@ -11731,16 +11731,16 @@
       <c r="T202" s="12"/>
       <c r="U202" s="12"/>
       <c r="V202" s="12"/>
-      <c r="W202" s="7">
+      <c r="W202" s="8">
         <v>64.0</v>
       </c>
-      <c r="X202" s="7" t="s">
+      <c r="X202" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="Y202" s="7" t="s">
+      <c r="Y202" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z202" s="7">
+      <c r="Z202" s="8">
         <v>905.0</v>
       </c>
       <c r="AA202" s="12"/>
@@ -11771,16 +11771,16 @@
       <c r="T203" s="12"/>
       <c r="U203" s="12"/>
       <c r="V203" s="12"/>
-      <c r="W203" s="7">
+      <c r="W203" s="8">
         <v>65.0</v>
       </c>
-      <c r="X203" s="7" t="s">
+      <c r="X203" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="Y203" s="7" t="s">
+      <c r="Y203" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z203" s="7">
+      <c r="Z203" s="8">
         <v>842.0</v>
       </c>
       <c r="AA203" s="12"/>
@@ -11811,16 +11811,16 @@
       <c r="T204" s="12"/>
       <c r="U204" s="12"/>
       <c r="V204" s="12"/>
-      <c r="W204" s="7">
+      <c r="W204" s="8">
         <v>66.0</v>
       </c>
-      <c r="X204" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y204" s="7" t="s">
+      <c r="X204" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y204" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z204" s="7">
+      <c r="Z204" s="8">
         <v>823.0</v>
       </c>
       <c r="AA204" s="12"/>
@@ -11851,16 +11851,16 @@
       <c r="T205" s="12"/>
       <c r="U205" s="12"/>
       <c r="V205" s="12"/>
-      <c r="W205" s="7">
+      <c r="W205" s="8">
         <v>67.0</v>
       </c>
-      <c r="X205" s="7" t="s">
+      <c r="X205" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="Y205" s="7" t="s">
+      <c r="Y205" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z205" s="7">
+      <c r="Z205" s="8">
         <v>820.0</v>
       </c>
       <c r="AA205" s="12"/>
@@ -11891,16 +11891,16 @@
       <c r="T206" s="12"/>
       <c r="U206" s="12"/>
       <c r="V206" s="12"/>
-      <c r="W206" s="7">
+      <c r="W206" s="8">
         <v>68.0</v>
       </c>
-      <c r="X206" s="7" t="s">
+      <c r="X206" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="Y206" s="7" t="s">
+      <c r="Y206" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="Z206" s="7">
+      <c r="Z206" s="8">
         <v>805.0</v>
       </c>
       <c r="AA206" s="12"/>
@@ -11931,16 +11931,16 @@
       <c r="T207" s="12"/>
       <c r="U207" s="12"/>
       <c r="V207" s="12"/>
-      <c r="W207" s="7">
+      <c r="W207" s="8">
         <v>69.0</v>
       </c>
-      <c r="X207" s="7" t="s">
+      <c r="X207" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="Y207" s="7" t="s">
+      <c r="Y207" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="Z207" s="7">
+      <c r="Z207" s="8">
         <v>782.0</v>
       </c>
       <c r="AA207" s="12"/>
@@ -11971,16 +11971,16 @@
       <c r="T208" s="12"/>
       <c r="U208" s="12"/>
       <c r="V208" s="12"/>
-      <c r="W208" s="7">
+      <c r="W208" s="8">
         <v>70.0</v>
       </c>
-      <c r="X208" s="7" t="s">
+      <c r="X208" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="Y208" s="7" t="s">
+      <c r="Y208" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z208" s="7">
+      <c r="Z208" s="8">
         <v>736.0</v>
       </c>
       <c r="AA208" s="12"/>
@@ -12011,16 +12011,16 @@
       <c r="T209" s="12"/>
       <c r="U209" s="12"/>
       <c r="V209" s="12"/>
-      <c r="W209" s="7">
+      <c r="W209" s="8">
         <v>71.0</v>
       </c>
-      <c r="X209" s="7" t="s">
+      <c r="X209" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="Y209" s="7" t="s">
+      <c r="Y209" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z209" s="7">
+      <c r="Z209" s="8">
         <v>733.0</v>
       </c>
       <c r="AA209" s="12"/>
@@ -12051,16 +12051,16 @@
       <c r="T210" s="12"/>
       <c r="U210" s="12"/>
       <c r="V210" s="12"/>
-      <c r="W210" s="7">
+      <c r="W210" s="8">
         <v>72.0</v>
       </c>
-      <c r="X210" s="7" t="s">
+      <c r="X210" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="Y210" s="7" t="s">
+      <c r="Y210" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z210" s="7">
+      <c r="Z210" s="8">
         <v>700.0</v>
       </c>
       <c r="AA210" s="12"/>
@@ -12091,16 +12091,16 @@
       <c r="T211" s="12"/>
       <c r="U211" s="12"/>
       <c r="V211" s="12"/>
-      <c r="W211" s="7">
+      <c r="W211" s="8">
         <v>73.0</v>
       </c>
-      <c r="X211" s="7" t="s">
+      <c r="X211" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="Y211" s="7" t="s">
+      <c r="Y211" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z211" s="7">
+      <c r="Z211" s="8">
         <v>649.0</v>
       </c>
       <c r="AA211" s="12"/>
@@ -12131,16 +12131,16 @@
       <c r="T212" s="12"/>
       <c r="U212" s="12"/>
       <c r="V212" s="12"/>
-      <c r="W212" s="7">
+      <c r="W212" s="8">
         <v>74.0</v>
       </c>
-      <c r="X212" s="7" t="s">
+      <c r="X212" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="Y212" s="7" t="s">
+      <c r="Y212" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z212" s="7">
+      <c r="Z212" s="8">
         <v>636.0</v>
       </c>
       <c r="AA212" s="12"/>
@@ -12171,16 +12171,16 @@
       <c r="T213" s="12"/>
       <c r="U213" s="12"/>
       <c r="V213" s="12"/>
-      <c r="W213" s="7">
+      <c r="W213" s="8">
         <v>75.0</v>
       </c>
-      <c r="X213" s="7" t="s">
+      <c r="X213" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="Y213" s="7" t="s">
+      <c r="Y213" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z213" s="7">
+      <c r="Z213" s="8">
         <v>528.0</v>
       </c>
       <c r="AA213" s="12"/>
@@ -12211,16 +12211,16 @@
       <c r="T214" s="12"/>
       <c r="U214" s="12"/>
       <c r="V214" s="12"/>
-      <c r="W214" s="7">
+      <c r="W214" s="8">
         <v>76.0</v>
       </c>
-      <c r="X214" s="7" t="s">
+      <c r="X214" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="Y214" s="7" t="s">
+      <c r="Y214" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Z214" s="7">
+      <c r="Z214" s="8">
         <v>473.0</v>
       </c>
       <c r="AA214" s="12"/>
@@ -12251,16 +12251,16 @@
       <c r="T215" s="12"/>
       <c r="U215" s="12"/>
       <c r="V215" s="12"/>
-      <c r="W215" s="7">
+      <c r="W215" s="8">
         <v>78.0</v>
       </c>
-      <c r="X215" s="7" t="s">
+      <c r="X215" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="Y215" s="7" t="s">
+      <c r="Y215" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Z215" s="7">
+      <c r="Z215" s="8">
         <v>435.0</v>
       </c>
       <c r="AA215" s="12"/>
@@ -12291,13 +12291,13 @@
       <c r="T216" s="12"/>
       <c r="U216" s="12"/>
       <c r="V216" s="12"/>
-      <c r="W216" s="7">
+      <c r="W216" s="8">
         <v>79.0</v>
       </c>
-      <c r="X216" s="7" t="s">
+      <c r="X216" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="Y216" s="7" t="s">
+      <c r="Y216" s="8" t="s">
         <v>140</v>
       </c>
       <c r="Z216" s="12"/>
@@ -12329,13 +12329,13 @@
       <c r="T217" s="12"/>
       <c r="U217" s="12"/>
       <c r="V217" s="12"/>
-      <c r="W217" s="7">
+      <c r="W217" s="8">
         <v>80.0</v>
       </c>
-      <c r="X217" s="7" t="s">
+      <c r="X217" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="Y217" s="7" t="s">
+      <c r="Y217" s="8" t="s">
         <v>140</v>
       </c>
       <c r="Z217" s="12"/>
@@ -37444,31 +37444,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -37478,7 +37478,7 @@
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="9">
@@ -37507,7 +37507,7 @@
 </f>
         <v>111.2</v>
       </c>
-      <c r="I2" s="15" t="str">
+      <c r="I2" s="16" t="str">
         <f>IF($D2="","",
    IF($C2=0,"",
       IF(($D2-$C2)/$C2&lt;=-0.3,"Extreme Value",
@@ -37533,7 +37533,7 @@
       <c r="A3" s="1">
         <v>2.0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="9">
@@ -37555,7 +37555,7 @@
         <f t="shared" si="3"/>
         <v>85.2</v>
       </c>
-      <c r="I3" s="15" t="str">
+      <c r="I3" s="16" t="str">
         <f t="shared" ref="I3:I73" si="4">IF($D3="","",
    IF(ABS($D3-$C3*$L$14)&lt;=2,"Fair",
       IF($D3&lt;$C3*$L$14,"Value","Overpay")
@@ -37575,7 +37575,7 @@
       <c r="A4" s="1">
         <v>3.0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="9">
@@ -37597,7 +37597,7 @@
         <f t="shared" si="3"/>
         <v>74.4</v>
       </c>
-      <c r="I4" s="15" t="str">
+      <c r="I4" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37613,7 +37613,7 @@
       <c r="A5" s="1">
         <v>4.0</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="9">
@@ -37634,7 +37634,7 @@
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
-      <c r="I5" s="15" t="str">
+      <c r="I5" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37651,7 +37651,7 @@
       <c r="A6" s="1">
         <v>5.0</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="9">
@@ -37672,7 +37672,7 @@
         <f t="shared" si="3"/>
         <v>60.8</v>
       </c>
-      <c r="I6" s="15" t="str">
+      <c r="I6" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37689,7 +37689,7 @@
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="9">
@@ -37710,7 +37710,7 @@
         <f t="shared" si="3"/>
         <v>53.2</v>
       </c>
-      <c r="I7" s="15" t="str">
+      <c r="I7" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37726,8 +37726,8 @@
       <c r="A8" s="1">
         <v>7.0</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>32</v>
+      <c r="B8" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="C8" s="9">
         <v>57.5</v>
@@ -37747,12 +37747,12 @@
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="I8" s="15" t="str">
+      <c r="I8" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="9">
         <f>L4-L7
@@ -37764,8 +37764,8 @@
       <c r="A9" s="1">
         <v>8.0</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>34</v>
+      <c r="B9" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="C9" s="9">
         <v>53.0</v>
@@ -37785,12 +37785,12 @@
         <f t="shared" si="3"/>
         <v>42.4</v>
       </c>
-      <c r="I9" s="15" t="str">
+      <c r="I9" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L9" s="9">
         <f>L6-L8
@@ -37802,8 +37802,8 @@
       <c r="A10" s="1">
         <v>9.0</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>36</v>
+      <c r="B10" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="9">
         <v>48.0</v>
@@ -37823,12 +37823,12 @@
         <f t="shared" si="3"/>
         <v>38.4</v>
       </c>
-      <c r="I10" s="15" t="str">
+      <c r="I10" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="9">
         <f>IF(L3&gt;1,L9/(L3-1),0)</f>
@@ -37839,7 +37839,7 @@
       <c r="A11" s="1">
         <v>10.0</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="9">
@@ -37860,7 +37860,7 @@
         <f t="shared" si="3"/>
         <v>34.4</v>
       </c>
-      <c r="I11" s="15" t="str">
+      <c r="I11" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37876,7 +37876,7 @@
       <c r="A12" s="1">
         <v>11.0</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="9">
@@ -37897,7 +37897,7 @@
         <f t="shared" si="3"/>
         <v>31.2</v>
       </c>
-      <c r="I12" s="15" t="str">
+      <c r="I12" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37906,7 +37906,7 @@
       <c r="A13" s="1">
         <v>12.0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="9">
@@ -37927,7 +37927,7 @@
         <f t="shared" si="3"/>
         <v>27.2</v>
       </c>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -37943,7 +37943,7 @@
       <c r="A14" s="1">
         <v>13.0</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="9">
@@ -37964,12 +37964,12 @@
         <f t="shared" si="3"/>
         <v>24.4</v>
       </c>
-      <c r="I14" s="15" t="str">
+      <c r="I14" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37980,8 +37980,8 @@
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>46</v>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C15" s="9">
         <v>27.5</v>
@@ -38001,7 +38001,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I15" s="15" t="str">
+      <c r="I15" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38010,8 +38010,8 @@
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>47</v>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="C16" s="9">
         <v>25.5</v>
@@ -38031,12 +38031,12 @@
         <f t="shared" si="3"/>
         <v>20.4</v>
       </c>
-      <c r="I16" s="15" t="str">
+      <c r="I16" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="1">
         <f>IF($L$18&lt;0.3,
@@ -38057,8 +38057,8 @@
       <c r="A17" s="1">
         <v>16.0</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>49</v>
+      <c r="B17" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C17" s="9">
         <v>22.5</v>
@@ -38078,7 +38078,7 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="I17" s="15" t="str">
+      <c r="I17" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38087,8 +38087,8 @@
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>51</v>
+      <c r="B18" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C18" s="9">
         <v>20.0</v>
@@ -38108,12 +38108,12 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="I18" s="15" t="str">
+      <c r="I18" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K18" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38124,8 +38124,8 @@
       <c r="A19" s="1">
         <v>18.0</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>53</v>
+      <c r="B19" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="C19" s="9">
         <v>18.5</v>
@@ -38145,7 +38145,7 @@
         <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
-      <c r="I19" s="15" t="str">
+      <c r="I19" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38154,8 +38154,8 @@
       <c r="A20" s="1">
         <v>19.0</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>54</v>
+      <c r="B20" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="9">
         <v>16.5</v>
@@ -38175,7 +38175,7 @@
         <f t="shared" si="3"/>
         <v>13.2</v>
       </c>
-      <c r="I20" s="15" t="str">
+      <c r="I20" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38184,8 +38184,8 @@
       <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>55</v>
+      <c r="B21" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="9">
         <v>14.5</v>
@@ -38205,7 +38205,7 @@
         <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
-      <c r="I21" s="15" t="str">
+      <c r="I21" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38214,8 +38214,8 @@
       <c r="A22" s="1">
         <v>21.0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>56</v>
+      <c r="B22" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="9">
         <v>13.5</v>
@@ -38235,7 +38235,7 @@
         <f t="shared" si="3"/>
         <v>10.8</v>
       </c>
-      <c r="I22" s="15" t="str">
+      <c r="I22" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38244,8 +38244,8 @@
       <c r="A23" s="1">
         <v>22.0</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>57</v>
+      <c r="B23" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="C23" s="9">
         <v>12.0</v>
@@ -38265,7 +38265,7 @@
         <f t="shared" si="3"/>
         <v>9.6</v>
       </c>
-      <c r="I23" s="15" t="str">
+      <c r="I23" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38274,8 +38274,8 @@
       <c r="A24" s="1">
         <v>23.0</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>58</v>
+      <c r="B24" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C24" s="9">
         <v>11.0</v>
@@ -38295,7 +38295,7 @@
         <f t="shared" si="3"/>
         <v>8.8</v>
       </c>
-      <c r="I24" s="15" t="str">
+      <c r="I24" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38304,8 +38304,8 @@
       <c r="A25" s="1">
         <v>24.0</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>59</v>
+      <c r="B25" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C25" s="9">
         <v>10.0</v>
@@ -38325,7 +38325,7 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="I25" s="15" t="str">
+      <c r="I25" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38334,8 +38334,8 @@
       <c r="A26" s="1">
         <v>25.0</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>60</v>
+      <c r="B26" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="C26" s="9">
         <v>9.5</v>
@@ -38355,7 +38355,7 @@
         <f t="shared" si="3"/>
         <v>7.6</v>
       </c>
-      <c r="I26" s="15" t="str">
+      <c r="I26" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38364,8 +38364,8 @@
       <c r="A27" s="1">
         <v>26.0</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>61</v>
+      <c r="B27" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="C27" s="9">
         <v>8.5</v>
@@ -38385,12 +38385,12 @@
         <f t="shared" si="3"/>
         <v>6.8</v>
       </c>
-      <c r="I27" s="15" t="str">
+      <c r="I27" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K27" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L27" s="1">
         <v>0.8</v>
@@ -38400,8 +38400,8 @@
       <c r="A28" s="1">
         <v>27.0</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>64</v>
+      <c r="B28" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="C28" s="9">
         <v>8.0</v>
@@ -38421,7 +38421,7 @@
         <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
-      <c r="I28" s="15" t="str">
+      <c r="I28" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38430,8 +38430,8 @@
       <c r="A29" s="1">
         <v>28.0</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>65</v>
+      <c r="B29" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C29" s="9">
         <v>7.0</v>
@@ -38451,7 +38451,7 @@
         <f t="shared" si="3"/>
         <v>5.6</v>
       </c>
-      <c r="I29" s="15" t="str">
+      <c r="I29" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38460,8 +38460,8 @@
       <c r="A30" s="1">
         <v>29.0</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>66</v>
+      <c r="B30" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C30" s="9">
         <v>6.5</v>
@@ -38481,7 +38481,7 @@
         <f t="shared" si="3"/>
         <v>5.2</v>
       </c>
-      <c r="I30" s="15" t="str">
+      <c r="I30" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38490,8 +38490,8 @@
       <c r="A31" s="1">
         <v>30.0</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>67</v>
+      <c r="B31" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C31" s="9">
         <v>6.0</v>
@@ -38511,7 +38511,7 @@
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
-      <c r="I31" s="15" t="str">
+      <c r="I31" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38520,8 +38520,8 @@
       <c r="A32" s="1">
         <v>31.0</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>68</v>
+      <c r="B32" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C32" s="9">
         <v>5.5</v>
@@ -38541,7 +38541,7 @@
         <f t="shared" si="3"/>
         <v>4.4</v>
       </c>
-      <c r="I32" s="15" t="str">
+      <c r="I32" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38550,8 +38550,8 @@
       <c r="A33" s="1">
         <v>32.0</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>69</v>
+      <c r="B33" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C33" s="9">
         <v>5.0</v>
@@ -38571,7 +38571,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I33" s="15" t="str">
+      <c r="I33" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38580,8 +38580,8 @@
       <c r="A34" s="1">
         <v>33.0</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>70</v>
+      <c r="B34" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="9">
         <v>4.5</v>
@@ -38601,7 +38601,7 @@
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
-      <c r="I34" s="15" t="str">
+      <c r="I34" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38610,8 +38610,8 @@
       <c r="A35" s="1">
         <v>34.0</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>72</v>
+      <c r="B35" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C35" s="9">
         <v>4.5</v>
@@ -38631,7 +38631,7 @@
         <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
-      <c r="I35" s="15" t="str">
+      <c r="I35" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38640,8 +38640,8 @@
       <c r="A36" s="1">
         <v>35.0</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>73</v>
+      <c r="B36" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C36" s="9">
         <v>4.0</v>
@@ -38661,7 +38661,7 @@
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
-      <c r="I36" s="15" t="str">
+      <c r="I36" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38670,8 +38670,8 @@
       <c r="A37" s="1">
         <v>36.0</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>74</v>
+      <c r="B37" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C37" s="9">
         <v>4.0</v>
@@ -38691,7 +38691,7 @@
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
-      <c r="I37" s="15" t="str">
+      <c r="I37" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38700,8 +38700,8 @@
       <c r="A38" s="1">
         <v>37.0</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>75</v>
+      <c r="B38" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C38" s="9">
         <v>3.5</v>
@@ -38721,7 +38721,7 @@
         <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
-      <c r="I38" s="15" t="str">
+      <c r="I38" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38730,8 +38730,8 @@
       <c r="A39" s="1">
         <v>38.0</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>76</v>
+      <c r="B39" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C39" s="9">
         <v>3.5</v>
@@ -38751,7 +38751,7 @@
         <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
-      <c r="I39" s="15" t="str">
+      <c r="I39" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38760,8 +38760,8 @@
       <c r="A40" s="1">
         <v>39.0</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>77</v>
+      <c r="B40" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C40" s="9">
         <v>3.0</v>
@@ -38781,7 +38781,7 @@
         <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
-      <c r="I40" s="15" t="str">
+      <c r="I40" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38790,8 +38790,8 @@
       <c r="A41" s="1">
         <v>40.0</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>78</v>
+      <c r="B41" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C41" s="9">
         <v>3.0</v>
@@ -38811,7 +38811,7 @@
         <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
-      <c r="I41" s="15" t="str">
+      <c r="I41" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38820,8 +38820,8 @@
       <c r="A42" s="1">
         <v>41.0</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>80</v>
+      <c r="B42" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C42" s="9">
         <v>2.5</v>
@@ -38841,7 +38841,7 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="I42" s="15" t="str">
+      <c r="I42" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38850,8 +38850,8 @@
       <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>81</v>
+      <c r="B43" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="C43" s="9">
         <v>2.5</v>
@@ -38871,7 +38871,7 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="I43" s="15" t="str">
+      <c r="I43" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38880,8 +38880,8 @@
       <c r="A44" s="1">
         <v>43.0</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>82</v>
+      <c r="B44" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="C44" s="9">
         <v>2.5</v>
@@ -38901,7 +38901,7 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="I44" s="15" t="str">
+      <c r="I44" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38910,8 +38910,8 @@
       <c r="A45" s="1">
         <v>44.0</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>83</v>
+      <c r="B45" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C45" s="9">
         <v>2.5</v>
@@ -38931,7 +38931,7 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="I45" s="15" t="str">
+      <c r="I45" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38940,8 +38940,8 @@
       <c r="A46" s="1">
         <v>45.0</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>84</v>
+      <c r="B46" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="C46" s="9">
         <v>2.0</v>
@@ -38961,7 +38961,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I46" s="15" t="str">
+      <c r="I46" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -38970,8 +38970,8 @@
       <c r="A47" s="1">
         <v>46.0</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>85</v>
+      <c r="B47" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="C47" s="9">
         <v>2.0</v>
@@ -38991,7 +38991,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I47" s="15" t="str">
+      <c r="I47" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39000,7 +39000,7 @@
       <c r="A48" s="1">
         <v>47.0</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="9">
@@ -39021,7 +39021,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I48" s="15" t="str">
+      <c r="I48" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39030,7 +39030,7 @@
       <c r="A49" s="1">
         <v>48.0</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="9">
@@ -39051,7 +39051,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I49" s="15" t="str">
+      <c r="I49" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39060,7 +39060,7 @@
       <c r="A50" s="1">
         <v>49.0</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="9">
@@ -39081,7 +39081,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I50" s="15" t="str">
+      <c r="I50" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39090,7 +39090,7 @@
       <c r="A51" s="1">
         <v>50.0</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="9">
@@ -39111,7 +39111,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I51" s="15" t="str">
+      <c r="I51" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39120,7 +39120,7 @@
       <c r="A52" s="1">
         <v>51.0</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="8" t="s">
         <v>91</v>
       </c>
       <c r="C52" s="9">
@@ -39141,7 +39141,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I52" s="15" t="str">
+      <c r="I52" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39150,7 +39150,7 @@
       <c r="A53" s="1">
         <v>52.0</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="8" t="s">
         <v>92</v>
       </c>
       <c r="C53" s="9">
@@ -39171,7 +39171,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I53" s="15" t="str">
+      <c r="I53" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39180,7 +39180,7 @@
       <c r="A54" s="1">
         <v>53.0</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C54" s="9">
@@ -39201,7 +39201,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I54" s="15" t="str">
+      <c r="I54" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39210,7 +39210,7 @@
       <c r="A55" s="1">
         <v>54.0</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="8" t="s">
         <v>94</v>
       </c>
       <c r="C55" s="9">
@@ -39231,7 +39231,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I55" s="15" t="str">
+      <c r="I55" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39240,7 +39240,7 @@
       <c r="A56" s="1">
         <v>55.0</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="9">
@@ -39261,7 +39261,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I56" s="15" t="str">
+      <c r="I56" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39270,7 +39270,7 @@
       <c r="A57" s="1">
         <v>56.0</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="8" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="9">
@@ -39291,7 +39291,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I57" s="15" t="str">
+      <c r="I57" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39300,7 +39300,7 @@
       <c r="A58" s="1">
         <v>57.0</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="9">
@@ -39321,7 +39321,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I58" s="15" t="str">
+      <c r="I58" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39330,7 +39330,7 @@
       <c r="A59" s="1">
         <v>58.0</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="8" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="9">
@@ -39351,7 +39351,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I59" s="15" t="str">
+      <c r="I59" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39360,7 +39360,7 @@
       <c r="A60" s="1">
         <v>59.0</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C60" s="9">
@@ -39381,7 +39381,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I60" s="15" t="str">
+      <c r="I60" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39390,7 +39390,7 @@
       <c r="A61" s="1">
         <v>60.0</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="8" t="s">
         <v>100</v>
       </c>
       <c r="C61" s="9">
@@ -39411,7 +39411,7 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="I61" s="15" t="str">
+      <c r="I61" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39420,7 +39420,7 @@
       <c r="A62" s="1">
         <v>61.0</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="9">
@@ -39441,7 +39441,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I62" s="15" t="str">
+      <c r="I62" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39450,7 +39450,7 @@
       <c r="A63" s="1">
         <v>62.0</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="8" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="9">
@@ -39471,7 +39471,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I63" s="15" t="str">
+      <c r="I63" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39480,7 +39480,7 @@
       <c r="A64" s="1">
         <v>63.0</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="8" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="9">
@@ -39501,7 +39501,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I64" s="15" t="str">
+      <c r="I64" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39510,7 +39510,7 @@
       <c r="A65" s="1">
         <v>64.0</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="9">
@@ -39531,7 +39531,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I65" s="15" t="str">
+      <c r="I65" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39540,7 +39540,7 @@
       <c r="A66" s="1">
         <v>65.0</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="8" t="s">
         <v>105</v>
       </c>
       <c r="C66" s="9">
@@ -39561,7 +39561,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I66" s="15" t="str">
+      <c r="I66" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39570,7 +39570,7 @@
       <c r="A67" s="1">
         <v>66.0</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="8" t="s">
         <v>106</v>
       </c>
       <c r="C67" s="9">
@@ -39591,7 +39591,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I67" s="15" t="str">
+      <c r="I67" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39600,7 +39600,7 @@
       <c r="A68" s="1">
         <v>67.0</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="8" t="s">
         <v>107</v>
       </c>
       <c r="C68" s="9">
@@ -39621,7 +39621,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I68" s="15" t="str">
+      <c r="I68" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39630,7 +39630,7 @@
       <c r="A69" s="1">
         <v>68.0</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="8" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="9">
@@ -39651,7 +39651,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I69" s="15" t="str">
+      <c r="I69" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39660,7 +39660,7 @@
       <c r="A70" s="1">
         <v>69.0</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="8" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="9">
@@ -39681,7 +39681,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I70" s="15" t="str">
+      <c r="I70" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39690,7 +39690,7 @@
       <c r="A71" s="1">
         <v>70.0</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C71" s="9">
@@ -39711,7 +39711,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I71" s="15" t="str">
+      <c r="I71" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39720,7 +39720,7 @@
       <c r="A72" s="1">
         <v>71.0</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="8" t="s">
         <v>111</v>
       </c>
       <c r="C72" s="9">
@@ -39741,7 +39741,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I72" s="15" t="str">
+      <c r="I72" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -39771,7 +39771,7 @@
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="I73" s="15" t="str">
+      <c r="I73" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>

--- a/CSVs/Draft Data.xlsx
+++ b/CSVs/Draft Data.xlsx
@@ -38,13 +38,13 @@
     <t>Mine?</t>
   </si>
   <si>
-    <t>Inflated Fair Price</t>
-  </si>
-  <si>
     <t>New Values</t>
   </si>
   <si>
     <t>Spine</t>
+  </si>
+  <si>
+    <t>Inflated Fair Price</t>
   </si>
   <si>
     <t>My Max Bid</t>
@@ -56,19 +56,19 @@
     <t>Value vs Fair</t>
   </si>
   <si>
-    <t>Settings</t>
+    <t>Floors</t>
   </si>
   <si>
-    <t>Floors</t>
+    <t>Settings</t>
   </si>
   <si>
     <t>Fractions</t>
   </si>
   <si>
-    <t>Jeremiyah Love</t>
+    <t>Monotone Rounded</t>
   </si>
   <si>
-    <t>Monotone Rounded</t>
+    <t>Jeremiyah Love</t>
   </si>
   <si>
     <t>Final Dollar Per Pick</t>
@@ -116,9 +116,6 @@
     <t>Sonny Styles</t>
   </si>
   <si>
-    <t>Round 2</t>
-  </si>
-  <si>
     <t>My Remaining</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
   </si>
   <si>
     <t>Other Teams Remaining</t>
+  </si>
+  <si>
+    <t>Round 2</t>
   </si>
   <si>
     <t>Jadarian Price</t>
@@ -137,19 +137,16 @@
     <t>Eli Stowers</t>
   </si>
   <si>
-    <t>Round 3</t>
+    <t>Budget Advantage Factor</t>
   </si>
   <si>
-    <t>Budget Advantage Factor</t>
+    <t>Round 3</t>
   </si>
   <si>
     <t>Omar Cooper</t>
   </si>
   <si>
     <t>CJ Allen</t>
-  </si>
-  <si>
-    <t>Round 4</t>
   </si>
   <si>
     <t>Undrafted Predraft$</t>
@@ -161,10 +158,10 @@
     <t>Inflation Factor</t>
   </si>
   <si>
-    <t>Round 5</t>
+    <t>Ty Simpson</t>
   </si>
   <si>
-    <t>Ty Simpson</t>
+    <t>Round 4</t>
   </si>
   <si>
     <t>Denzel Boston</t>
@@ -173,13 +170,13 @@
     <t>Aggression</t>
   </si>
   <si>
-    <t>Round 6</t>
-  </si>
-  <si>
     <t>Caleb Downs</t>
   </si>
   <si>
     <t>David Bailey</t>
+  </si>
+  <si>
+    <t>Round 5</t>
   </si>
   <si>
     <t>League Spent %</t>
@@ -195,6 +192,9 @@
   </si>
   <si>
     <t>Dillon Thieneman</t>
+  </si>
+  <si>
+    <t>Round 6</t>
   </si>
   <si>
     <t>Rueben Bain</t>
@@ -341,6 +341,18 @@
     <t>Kevin Coleman</t>
   </si>
   <si>
+    <t>Garrett Nussmeier</t>
+  </si>
+  <si>
+    <t>Nate Boerkircher</t>
+  </si>
+  <si>
+    <t>Will Kacmarek</t>
+  </si>
+  <si>
+    <t>Noah Whittington</t>
+  </si>
+  <si>
     <t>Standings</t>
   </si>
   <si>
@@ -368,19 +380,7 @@
     <t>Key</t>
   </si>
   <si>
-    <t>Garrett Nussmeier</t>
-  </si>
-  <si>
-    <t>Nate Boerkircher</t>
-  </si>
-  <si>
     <t>Ed</t>
-  </si>
-  <si>
-    <t>Will Kacmarek</t>
-  </si>
-  <si>
-    <t>Noah Whittington</t>
   </si>
   <si>
     <t>Brent</t>
@@ -923,10 +923,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="F1" s="6">
         <v>2025.0</v>
@@ -938,13 +938,13 @@
         <v>2026.0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>19</v>
@@ -1180,7 +1180,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P3" s="15">
         <f t="shared" ref="P3:AA3" si="8">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1284,7 +1284,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P4" s="15">
         <f t="shared" ref="P4:AA4" si="11">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1388,7 +1388,7 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P5" s="15">
         <f t="shared" ref="P5:AA5" si="12">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1492,7 +1492,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P6" s="15">
         <f t="shared" ref="P6:AA6" si="13">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -1596,7 +1596,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="P7" s="15">
         <f t="shared" ref="P7:AA7" si="14">INDEX($L$1:$L$73, 2 + (ROW()-ROW($P$2))*12 + (COLUMN()-COLUMN($P$2)))</f>
@@ -3062,33 +3062,33 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="12"/>
       <c r="R29" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="U29" s="12"/>
       <c r="V29" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -3146,7 +3146,7 @@
         <v>1.0</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="12"/>
       <c r="R30" s="6">
@@ -4175,7 +4175,7 @@
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P44" s="8" t="s">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>134</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="S44" s="12"/>
       <c r="T44" s="12"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="S74" s="12"/>
       <c r="T74" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="U74" s="15">
         <f t="shared" si="22"/>
@@ -9255,7 +9255,7 @@
         <v>1.0</v>
       </c>
       <c r="X140" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y140" s="9" t="s">
         <v>140</v>
@@ -9535,7 +9535,7 @@
         <v>9.0</v>
       </c>
       <c r="X147" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y147" s="9" t="s">
         <v>141</v>
@@ -9575,7 +9575,7 @@
         <v>10.0</v>
       </c>
       <c r="X148" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Y148" s="9" t="s">
         <v>145</v>
@@ -9615,7 +9615,7 @@
         <v>11.0</v>
       </c>
       <c r="X149" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y149" s="9" t="s">
         <v>143</v>
@@ -9655,7 +9655,7 @@
         <v>12.0</v>
       </c>
       <c r="X150" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Y150" s="9" t="s">
         <v>146</v>
@@ -9775,7 +9775,7 @@
         <v>15.0</v>
       </c>
       <c r="X153" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y153" s="9" t="s">
         <v>141</v>
@@ -9815,7 +9815,7 @@
         <v>16.0</v>
       </c>
       <c r="X154" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y154" s="9" t="s">
         <v>143</v>
@@ -9855,7 +9855,7 @@
         <v>17.0</v>
       </c>
       <c r="X155" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y155" s="9" t="s">
         <v>140</v>
@@ -9895,7 +9895,7 @@
         <v>18.0</v>
       </c>
       <c r="X156" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y156" s="9" t="s">
         <v>145</v>
@@ -10095,7 +10095,7 @@
         <v>23.0</v>
       </c>
       <c r="X161" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y161" s="9" t="s">
         <v>142</v>
@@ -10335,7 +10335,7 @@
         <v>29.0</v>
       </c>
       <c r="X167" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Y167" s="9" t="s">
         <v>143</v>
@@ -10935,7 +10935,7 @@
         <v>44.0</v>
       </c>
       <c r="X182" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="Y182" s="9" t="s">
         <v>142</v>
@@ -37459,7 +37459,7 @@
         <v>7</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>11</v>
@@ -37471,7 +37471,7 @@
         <v>13</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
@@ -37479,7 +37479,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="11">
         <v>139.0</v>
@@ -37752,7 +37752,7 @@
         <v/>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L8" s="11">
         <f>L4-L7
@@ -37765,7 +37765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="11">
         <v>53.0</v>
@@ -37790,7 +37790,7 @@
         <v/>
       </c>
       <c r="K9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L9" s="11">
         <f>L6-L8
@@ -37865,7 +37865,7 @@
         <v/>
       </c>
       <c r="K11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L11" s="19">
         <f>IF(L10&gt;0,L8/L10,1)</f>
@@ -37932,7 +37932,7 @@
         <v/>
       </c>
       <c r="K13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L13" s="18">
         <f>SUMIF($D$2:$D$73,"",$C$2:$C$73)</f>
@@ -37944,7 +37944,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="11">
         <v>30.5</v>
@@ -37969,7 +37969,7 @@
         <v/>
       </c>
       <c r="K14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L14" s="19">
         <f>IF(L13&gt;0,L6/L13,1)</f>
@@ -37981,7 +37981,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="11">
         <v>27.5</v>
@@ -38011,7 +38011,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="11">
         <v>25.5</v>
@@ -38036,7 +38036,7 @@
         <v/>
       </c>
       <c r="K16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2">
         <f>IF($L$18&lt;0.3,
@@ -38058,7 +38058,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" s="11">
         <v>22.5</v>
@@ -38088,7 +38088,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="11">
         <v>20.0</v>
@@ -38113,7 +38113,7 @@
         <v/>
       </c>
       <c r="K18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L18" s="20">
         <f>L5/L2</f>
@@ -38125,7 +38125,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="11">
         <v>18.5</v>
@@ -38155,7 +38155,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="11">
         <v>16.5</v>
@@ -38185,7 +38185,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="11">
         <v>14.5</v>
@@ -38215,7 +38215,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="11">
         <v>13.5</v>
@@ -39661,7 +39661,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C70" s="11">
         <v>1.0</v>
@@ -39691,7 +39691,7 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C71" s="11">
         <v>1.0</v>
@@ -39721,7 +39721,7 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C72" s="11">
         <v>1.0</v>
@@ -39751,7 +39751,7 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C73" s="11">
         <v>1.0</v>
